--- a/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
+++ b/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
@@ -17,11 +17,18 @@
     <sheet name="T07_velikost_fo" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="T08_velikost_po" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="T09_vekova_struktura" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="T10_zaniky_po" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="T11_dynamika_csu" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="T12_demografie_cr" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Metodika" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Zdroj a licence" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="T13_bench_fo_po" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="T14_bench_pravni_forma" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="T15_bench_velikost_fo" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="T16_bench_velikost_po" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="T17_bench_vekova_struktura" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="T10_zaniky_po" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="T18_mira_zaniku_po" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="T11_dynamika_csu" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="T12_demografie_cr" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="T19_zjisteni" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Metodika" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Zdroj a licence" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -693,36 +700,120 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T10_zaniky_po</t>
+          <t>T13_bench_fo_po</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES, od 2023)</t>
+          <t>Typ osoby – srovnání s ČR a se srovnávacími kraji (podíl, %)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T11_dynamika_csu</t>
+          <t>T14_bench_pravni_forma</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
+          <t>Právní forma – srovnání s ČR a se srovnávacími kraji (podíl z celku, %)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>T15_bench_velikost_fo</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Velikostní profil FO – srovnání s ČR a se srovnávacími kraji (podíl z FO, %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T16_bench_velikost_po</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Velikostní profil PO – srovnání s ČR a se srovnávacími kraji (podíl z PO, %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T17_bench_vekova_struktura</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Věková struktura existujících subjektů – srovnání s ČR a se srovnávacími kraji (podíl, %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T10_zaniky_po</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES, od 2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T18_mira_zaniku_po</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Míra zániku právnických osob v oboru (RES, 2023–2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T11_dynamika_csu</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>T12_demografie_cr</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T19_zjisteni</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Zjištění detektoru (seřazeno podle síly)</t>
         </is>
       </c>
     </row>
@@ -898,6 +989,1156 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Typ osoby – srovnání s ČR a se srovnávacími kraji (podíl, %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Liberecký kraj (%)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Česko (%)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj (%)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Rozdíl proti ČR (p. b.)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>fyzické osoby (FO)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>právnické osoby a ostatní (PO)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-5.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>celkem</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Týž obor ve všech sloupcích. Položky jsou dané zkoumaným územím; co je v něm sloučeno do „ostatní“, je sloučeno i v ostatních sloupcích. Práh a slučování platí pro každé území zvlášť.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Právní forma – srovnání s ČR a se srovnávacími kraji (podíl z celku, %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Liberecký kraj (%)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Česko (%)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj (%)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Rozdíl proti ČR (p. b.)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>101 Fyzická osoba podnikající dle živnostenského zákona</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D6" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>424 Zahraniční fyzická osoba</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ostatní formy FO</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>FO celkem</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>112 Společnost s ručením omezeným</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>121 Akciová společnost</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>111 Veřejná obchodní společnost</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>205 Družstvo</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ostatní formy PO</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>PO celkem</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-5.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>celkem</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Týž obor ve všech sloupcích. Položky jsou dané zkoumaným územím; co je v něm sloučeno do „ostatní“, je sloučeno i v ostatních sloupcích. Práh a slučování platí pro každé území zvlášť.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj: některá položka zveřejněná ve zkoumaném území je zde pod prahem a je sloučena do „ostatní“ (v tomto sloupci pomlčka).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Velikostní profil FO – srovnání s ČR a se srovnávacími kraji (podíl z FO, %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Liberecký kraj (%)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Česko (%)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj (%)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Rozdíl proti ČR (p. b.)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bez zaměstnanců</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E6" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1–9 zaměstnanců</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10–49 zaměstnanců</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Neuvedeno</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>44</v>
+      </c>
+      <c r="D9" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>52</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ostatní (sloučené malé položky)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ve zkoumaném území žádné</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>celkem</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Týž obor ve všech sloupcích. Položky jsou dané zkoumaným územím; co je v něm sloučeno do „ostatní“, je sloučeno i v ostatních sloupcích. Práh a slučování platí pro každé území zvlášť.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>„Neuvedeno“ (KATPO 000) je samostatný řádek, nesčítá se s „bez zaměstnanců“.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj, Česko: některá položka zveřejněná ve zkoumaném území je zde pod prahem a je sloučena do „ostatní“ (v tomto sloupci pomlčka).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Velikostní profil PO – srovnání s ČR a se srovnávacími kraji (podíl z PO, %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Liberecký kraj (%)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Česko (%)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj (%)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Rozdíl proti ČR (p. b.)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1–9 zaměstnanců</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10–49 zaměstnanců</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Neuvedeno</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-5.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ostatní (sloučené malé položky)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>celkem</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Týž obor ve všech sloupcích. Položky jsou dané zkoumaným územím; co je v něm sloučeno do „ostatní“, je sloučeno i v ostatních sloupcích. Práh a slučování platí pro každé území zvlášť.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>„Neuvedeno“ (KATPO 000) je samostatný řádek, nesčítá se s „bez zaměstnanců“.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Věková struktura existujících subjektů – srovnání s ČR a se srovnávacími kraji (podíl, %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Liberecký kraj (%)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Česko (%)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj (%)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Rozdíl proti ČR (p. b.)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>méně než 3 roky</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3–5 let</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="C7" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6–10 let</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>11–20 let</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>21–30 let</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>31 a více let</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>celkem</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Týž obor ve všech sloupcích. Položky jsou dané zkoumaným územím; co je v něm sloučeno do „ostatní“, je sloučeno i v ostatních sloupcích. Práh a slučování platí pro každé území zvlášť.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1006,7 +2247,458 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Míra zániku právnických osob v oboru (RES, 2023–2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Stav PO k 1. 1.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Zaniklé PO za rok</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Míra zániku za rok (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Zaniklé PO 1. 1.–15. 9.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Míra zániku 1. 1.–15. 9. (%)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2023</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1684</v>
+      </c>
+      <c r="C6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>část skryta (práh, dopočet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2024</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1740</v>
+      </c>
+      <c r="C7" t="n">
+        <v>51</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E7" t="n">
+        <v>33</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2025</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1759</v>
+      </c>
+      <c r="C8" t="n">
+        <v>103</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="E8" t="n">
+        <v>79</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2026</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1727</v>
+      </c>
+      <c r="E9" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>neúplný rok – jen srovnatelné období</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Česko – 2023</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>51800</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1333</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E10" t="n">
+        <v>927</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Česko – 2024</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>53523</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1387</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E11" t="n">
+        <v>911</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Česko – 2025</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>55375</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1454</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1017</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Česko – 2026</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>57730</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1059</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>neúplný rok – jen srovnatelné období</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2023</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1641</v>
+      </c>
+      <c r="C14" t="n">
+        <v>31</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>část skryta (práh, dopočet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2024</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C15" t="n">
+        <v>29</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>část skryta (práh, dopočet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2025</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1731</v>
+      </c>
+      <c r="C16" t="n">
+        <v>52</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>34</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2026</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1770</v>
+      </c>
+      <c r="E17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>neúplný rok – jen srovnatelné období</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2023</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>945</v>
+      </c>
+      <c r="C18" t="n">
+        <v>22</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>část skryta (práh, dopočet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2024</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>959</v>
+      </c>
+      <c r="C19" t="n">
+        <v>21</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>část skryta (práh, dopočet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2025</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>978</v>
+      </c>
+      <c r="C20" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>část skryta (práh, dopočet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E21" t="n">
+        <v>28</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>neúplný rok – jen srovnatelné období</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pomlčka = skryto: počet pod prahem nebo by z něj šlo dopočítat skrytý počet (zániky ve zbytku roku, vzniky mezi dvěma stavy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Míra zániku PO = zaniklé PO v roce / stav PO k 1. 1. téhož roku × 100. Stav je rekonstruován ze snímku RES: existující PO se vznikem před 1. 1. + PO zaniklé 1. 1. nebo později.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Rok 2026 je neúplný (snímek k 15. 9. 2026); pro srovnání se proto počítá i srovnatelné období 1. 1.–15. 9. každého roku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Omezení: jen právnické osoby – zaniklé FO mají v otevřených datech jen IČO a datum zániku. Okno 4 let (2023–2026): RES uchovává zaniklé subjekty jen 4 roky po zániku. Obor a sídlo jsou podle snímku (u zaniklých poslední známé), jejich změny v čase se nepromítají.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1225,7 +2917,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1571,2181 +3263,6 @@
       <c r="A17" t="inlineStr">
         <is>
           <t>Jiná jednotka: aktivní PODNIK ze statistiky demografie podniků, ne registrovaný ekonomický subjekt z RES; čísla nejsou srovnatelná s ostatními tabulkami. Jen za ČR.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Kód</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Název</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Typ</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Definice</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Vzorec</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Zdroj</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Úroveň</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Ošetření chybějících hodnot</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Poznámka k výkladu</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Stav</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Použit v této příloze</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>REG_POCET</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Počet registrovaných subjektů v oboru a území</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Registrované ekonomické subjekty bez data zániku s převažující činností v oboru a sídlem v území.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>count(subjekt) where ddatzan is null and nace ∈ obor and okres/kraj(sídlo) ∈ území</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data (res_data.csv), snímek k datu</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Subjekty bez NACE sekce (pseudokód 00) a subjekty zařazené jen do vyšší úrovně klasifikace se do oboru nepočítají, uvádějí se zvlášť (DOPL_OBOR_NEURCEN, DOPL_JEN_VYSSI). Zaniklé subjekty se nepočítají.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Jde o registrované subjekty; podle ČSÚ má zjištěnou aktivitu (daně, pojistné) jen asi 60 % z nich (AKTIVNI_PODIL_KRAJ).</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REG_POCET_CR</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Počet registrovaných subjektů v oboru v ČR</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>REG_POCET za celou ČR.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>count(subjekt) where ddatzan is null and nace ∈ obor</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>jako REG_POCET</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Jmenovatel podílu území na ČR.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REG_PODIL_CR</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Podíl území na registrovaných subjektech oboru v ČR (%)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Kolik procent registrovaných subjektů oboru v ČR má sídlo v území.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>100 × REG_POCET(území) / REG_POCET_CR</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>kraj, okres</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Srovnávejte s podílem území na všech subjektech (viz LQ).</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REG_POCET_VSE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Počet všech registrovaných subjektů v území</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Registrované subjekty bez data zániku se sídlem v území, všechny obory včetně pseudokódu 00.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>count(subjekt) where ddatzan is null and sídlo ∈ území</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Jmenovatel podílu oboru v území a lokalizačního koeficientu.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REG_PODIL_OBOR</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Podíl oboru na registrovaných subjektech území (%)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Kolik procent všech registrovaných subjektů území má převažující činnost v oboru.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>100 × REG_POCET / REG_POCET_VSE</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Jmenovatel obsahuje i subjekty s pseudokódem 00 (obor neurčen), shodně v čitateli ČR i území.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LQ</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Lokalizační koeficient</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Podíl oboru na subjektech území dělený podílem oboru na subjektech ČR.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>(REG_POCET / REG_POCET_VSE) / (REG_POCET_CR / REG_POCET_VSE(ČR))</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>kraj, okres</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>&gt;1 = obor je v území zastoupen víc než v průměru ČR. Počítá registrované subjekty, ne zaměstnanost ani výkon.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>OBYVATELE</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Počet obyvatel území</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Počet obyvatel k 31. 12. posledního zveřejněného roku.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>převzato</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada OBY02A (ukazatel 2406K2)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Praha nemá okres v datech obyvatelstva; okres Praha (CZ0100) = kraj Hlavní město Praha.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Rok stavu obyvatel se liší od data snímku RES.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HUSTOTA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Registrované subjekty oboru na 1 000 obyvatel</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Počet registrovaných subjektů oboru na 1 000 obyvatel území.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1000 × REG_POCET / OBYVATELE</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>odvozeno z RES a ČSÚ OBY02A</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sídlo subjektu nemusí být místem činnosti; v Praze je hustota zvýšena sídly bez činnosti v Praze.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PORADI_POCET</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Pořadí podle počtu registrovaných subjektů oboru</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>poradi</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Pořadí kraje mezi 14 kraji (u okresu mezi okresy téhož kraje) podle REG_POCET, 1 = nejvíce.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>rank() over (order by REG_POCET desc)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>kraj, okres</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Pořadí se počítá ze skutečných počtů všech území; zveřejní se jen u zveřejněných počtů.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Automaticky se srovnává jen s ČR a pořadím mezi všemi kraji; srovnávací kraje volí člověk.</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PORADI_HUSTOTA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pořadí podle hustoty na 1 000 obyvatel</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>poradi</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Pořadí kraje mezi 14 kraji (u okresu mezi okresy téhož kraje) podle HUSTOTA, 1 = nejvyšší.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>rank() over (order by HUSTOTA desc)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>odvozeno z RES a ČSÚ OBY02A</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>kraj, okres</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>jako PORADI_POCET</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Odstraňuje vliv velikosti území.</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>FOPO_POCET</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Registrované subjekty podle typu osoby (FO/PO)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>FO = statistická právní forma (FORMA) 101–108, 424, 425 (podnikající fyzické osoby včetně zahraničních); PO = ostatní formy.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>count(subjekt) group by FO/PO</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data; vymezení FO podle metodiky ČSÚ (statistiky z RES)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Je-li FO nebo PO pod prahem, rozdělení se nezveřejní (a s ním ani velikostní profily FO/PO).</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>FO jsou většinou OSVČ; název subjektu je u nich jméno osoby.</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>FOPO_PODIL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Podíl FO/PO (%)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Podíl FO resp. PO na REG_POCET.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>100 × FOPO_POCET / REG_POCET</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>jako FOPO_POCET</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>FORMA_POCET</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Registrované subjekty podle právní formy</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Počet podle statistické právní formy (FORMA, číselník ČSÚ 56).</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>count(subjekt) group by forma</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data; číselník 56</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Formy pod prahem se slučují do „ostatní formy FO“ / „ostatní formy PO“ (v rámci skupiny); je-li skryté rozdělení FO/PO, do jednoho „ostatní“.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>FORMA_PODIL</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Podíl právní formy (%)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Podíl na REG_POCET.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>100 × FORMA_POCET / REG_POCET</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>jako FORMA_POCET</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>VEL_FO_POCET</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Velikostní profil FO – počet podle kategorie zaměstnanců</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>FO podle KATPO (číselník 579) seskupené do pásem: bez zaměstnanců (110), 1–9 (120, 130), 10–49 (210–230), 50–249 (240–320), 250 a více (330–510), Neuvedeno (000).</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>count(subjekt FO) group by pásmo(KATPO)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data; číselník 579</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>„Neuvedeno“ (000) je vždy samostatný řádek, nikdy se neslučuje s „bez zaměstnanců“; pásma pod prahem se slučují do „ostatní“.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>U FO znamená 110 bez zaměstnanců; od 7/2024 se do zaměstnanců počítají i DPP.</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>VEL_FO_PODIL</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Velikostní profil FO – podíl (%)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Podíl pásma na FO celkem; podíl „Neuvedeno“ se zobrazuje vždy (je-li zveřejnitelný).</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>100 × VEL_FO_POCET / FOPO_POCET(FO)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>jako VEL_FO_POCET</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>VEL_PO_POCET</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Velikostní profil PO – počet podle kategorie zaměstnanců</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>PO podle KATPO v týchž pásmech jako VEL_FO_POCET.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>count(subjekt PO) group by pásmo(KATPO)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data; číselník 579</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>jako VEL_FO_POCET</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>U PO se kód 110 prakticky nepoužívá; PO bez hlášených zaměstnanců mají „Neuvedeno“ (000). Neuvedeno ≠ bez zaměstnanců.</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>VEL_PO_PODIL</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Velikostní profil PO – podíl (%)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Podíl pásma na PO celkem.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>100 × VEL_PO_POCET / FOPO_POCET(PO)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>jako VEL_PO_POCET</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>VEK_PRUMER</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Průměrný věk existujících subjektů (roky)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>prumer</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Průměr (datum snímku − datum vzniku) v letech u registrovaných subjektů oboru v území.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>avg((datum_snimku − ddatvzn) / 365.25)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Věková struktura existujících subjektů, ne dynamika vzniku (zaniklé subjekty nejsou zahrnuty).</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>VEK_MEDIAN</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Mediánový věk existujících subjektů (roky)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>prumer</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Medián (datum snímku − datum vzniku) v letech.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>percentile_cont(0.5)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>jako VEK_PRUMER</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>jako VEK_PRUMER</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>VEK_PASMO_POCET</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Věková struktura existujících subjektů – počet v pásmu</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Pásma věku: méně než 3 roky, 3–5, 6–10, 11–20, 21–30, 31 a více let.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>count(subjekt) group by pásmo(věk)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Pásma pod prahem se slučují do „ostatní“.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Není to počet vzniků v jednotlivých letech.</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>VEK_PASMO_PODIL</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Věková struktura existujících subjektů – podíl pásma (%)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Podíl pásma na REG_POCET.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>100 × VEK_PASMO_POCET / REG_POCET</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>jako VEK_PASMO_POCET</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>DOPL_JEN_VYSSI</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Zařazeno jen do vyšší úrovně klasifikace (např. „zařazeno jen do sekce“)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Registrované subjekty v území, jejichž NACE je nadřazený kód zkoumaného oboru (např. jen „J“ u oddílu 62) – do oboru mohou, ale nemusí patřit.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>count(subjekt) where nace ∈ předci(obor)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Samostatné číslo; pod prahem se nezveřejní. Jen pro obor na úrovni oddílu a nižší.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Horní mez nejistoty počtu v oboru.</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>ne</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>DOPL_OBOR_NEURCEN</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Obor neurčen (pseudokód 00)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Registrované subjekty v území s pseudokódem 00 („výroba, obchod a služby neuvedené v přílohách 1 až 3 živnostenského zákona“).</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>count(subjekt) where nace = '00'</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Samostatné číslo; pod prahem se nezveřejní.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Tyto subjekty nejde přiřadit žádnému oboru; ČSÚ je vykazuje jako „X Nezjištěno“.</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AKTIVNI_PODIL_KRAJ</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Podíl subjektů se zjištěnou aktivitou v kraji podle ČSÚ (%, všechny obory)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Počet ekonomických subjektů se zjištěnou aktivitou / počet ekonomických subjektů celkem, kraj (u okresu jeho kraj), všechny obory, poslední čtvrtletí.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>100 × 4958_akt / 4958_reg (RES02QT1, NACE celkem)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, výběr RES02QT1</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Za okres ČSÚ podíl v členění podle převažující činnosti nepublikuje; uvádí se krajský.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Jen kontext. Aktivitu po subjektech nedopočítáváme; počty v reportu jsou registrované subjekty.</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AKTIVNI_PODIL_SEKCE_KRAJ</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Podíl subjektů se zjištěnou aktivitou v sekci a kraji podle ČSÚ (%)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Jako AKTIVNI_PODIL_KRAJ, ale jen pro sekci CZ-NACE zkoumaného oboru.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>100 × 4958_akt / 4958_reg (RES02QT1, sekce)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, výběr RES02QT1</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Jen je-li obor přesně jedna sekce, kterou ČSÚ publikuje samostatně (ne B, C, D, E – ty jen jako B–E); jinak nelze naplnit.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Jen kontext.</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ZANIK_PO_RES</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>PO s datem zániku od 1. 1. 2023 do data snímku, s převažující činností v oboru a sídlem v území.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>count(subjekt PO) where ddatzan &gt;= 2023-01-01 group by year(ddatzan)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Zaniklé FO mají v otevřených datech jen IČO a datum zániku (GDPR) – do oboru ani území je přiřadit nelze. Zaniklé více než 4 roky v RES nejsou; proto jen od roku 2023. Poslední rok je neúplný.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Jen PO; nelze z toho počítat míru zániku oboru.</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>DYN_VZNIK_CSU</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Vzniklé ekonomické subjekty v území podle ČSÚ (všechny obory)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Počet vzniklých ekonomických subjektů v roce (součet čtvrtletí), FO a PO, území celkem.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>sum(4962) over čtvrtletí roku (RES05)</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada RES05</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>ČSÚ vznik a zánik v členění podle oboru (kraj × sekce ani ČR × obor) z RES nepublikuje – dynamiku oboru nelze naplnit. Poslední rok je neúplný (jen zveřejněná čtvrtletí).</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Dynamika celého území, ne oboru.</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>DYN_ZANIK_CSU</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Zaniklé ekonomické subjekty v území podle ČSÚ (všechny obory)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Počet zaniklých ekonomických subjektů v roce (součet čtvrtletí), FO a PO, území celkem.</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>sum(4963) over čtvrtletí roku (RES05)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada RES05</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>jako DYN_VZNIK_CSU. Rok 2023 u FO obsahuje mimořádný výkyv (1. čtvrtletí 2023 hromadný zánik FO, v ČR 200 977 zániků FO proti obvyklým 15–45 tis.).</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Dynamika celého území, ne oboru.</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>DYN_OBOR_CSU</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Vznik a zánik subjektů v oboru a území podle ČSÚ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Počet vzniklých a zaniklých subjektů v oboru × kraji.</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ČSÚ DataStat – tabulka v tomto členění neexistuje (RES05 jen území × FO/PO; RES06 registrace a RESDP00 demografie podniků jen za ČR podle odvětví)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Nelze naplnit.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Mimo v0 (rozhodnutí 10) – vznikne později z archivu snímků RES. Náhradou je dynamika území (RES05), kontext ČR z demografie podniků (RESDP00), ZANIK_PO_RES a věková struktura.</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>nelze naplnit</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>ne</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>SPOLEHLIVOST_JEN_SEKCE</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Spolehlivost zařazení – subjekty zařazené jen do sekce vůči počtu oboru (%)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Registrované subjekty v území s převažující činností uvedenou jen písmenem sekce oboru (např. „J“ u oddílu 62) děleno počtem oboru v území (rozhodnutí 9).</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>100 × DOPL_JEN_VYSSI(sekce) / REG_POCET</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Jen pro obor na úrovni oddílu a nižší. Nezveřejní se, je-li počet „jen do sekce“ pod prahem (pak je podíl nutně malý).</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Nad 25 % nese report varování na titulní straně i v metodické poznámce: skutečný počet oboru může být výrazně vyšší.</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>ne</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>DEMOGR_AKTIVNI</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Aktivní podniky v ČR (demografie podniků)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Počet aktivních podniků podle statistiky demografie podniků ČSÚ, FO a PO zvlášť, odvětví oboru a všechna odvětví.</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>převzato (RESDP00, ukazatel 6594_RESDP)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada RESDP00</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Odvětví jen B–R (K = peněžní zprostředkování, S = osobní služby); A, O, T, U v RESDP00 nejsou. Poslední rok bývá předběžný.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Jiná jednotka (aktivní podnik), nesrovnatelné s registrovanými subjekty RES; jen kontext za ČR (rozhodnutí 10).</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>DEMOGR_MIRA_VZNIKU</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Míra vzniků podniků v ČR (%)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Vzniklé podniky / aktivní podniky × 100 podle ČSÚ, FO a PO zvlášť.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>převzato (RESDP00, ukazatel 9507)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada RESDP00</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>jako DEMOGR_AKTIVNI</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Kontext dynamiky oboru za ČR; dynamika obor × území je mimo v0 (vznikne z archivu snímků RES).</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>DEMOGR_MIRA_ZANIKU</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Míra zániků podniků v ČR (%)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Zaniklé podniky / aktivní podniky × 100 podle ČSÚ, FO a PO zvlášť.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>převzato (RESDP00, ukazatel 9508)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada RESDP00</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Zánik se zjišťuje se zpožděním; poslední rok bez zániků se nezobrazuje.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>jako DEMOGR_MIRA_VZNIKU</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Pravidla ochrany malých buněk: buňky pod prahem se v každém členění slučují do „ostatní“; je-li „ostatní“ pod prahem, přidá se další nejmenší buňka; skryté číslo nesmí jít dopočítat ze součtů ani z jiné tabulky (ověřeno kontrolou dopočtu). Podrobnosti: docs/report_metodika.md.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="140" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Zdroj</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Označení</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Licence</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CC BY 4.0 – https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Datum snímku RES</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Soubor RES</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://opendata.csu.gov.cz/soubory/od/od_org03/res_data.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Další zdroj</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada OBY02A – počet obyvatel k 31. 12. 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Další zdroj</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, výběr RES02QT1 – podíl subjektů se zjištěnou aktivitou, 2026-Q2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Další zdroj</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada RES05 – vznik a zánik ekonomických subjektů</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Další zdroj</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada RESDP00 – demografie podniků (jednotka podnik, jen ČR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Povinnost</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Upravené nebo odvozené údaje musí být označeny jako odvozené a nesmí být prezentovány jako nezměněné oficiální statistiky ČSÚ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Vygenerováno</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-09-30T11:15:17+00:00</t>
         </is>
       </c>
     </row>
@@ -3965,6 +3482,3740 @@
       <c r="A22" t="inlineStr">
         <is>
           <t>Počty jsou registrované subjekty bez data zániku. Podíl subjektů se zjištěnou aktivitou je jen kontext z publikace ČSÚ, na subjekty oboru se nepřepočítává.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Zjištění detektoru (seřazeno podle síly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Zjištění</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Typ zjištění</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Síla</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Hodnota</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Srovnání</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Relativní rozdíl (%)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Míra zániku PO v oboru se mezi lety 2023 a 2025 změnila v Libereckém kraji z 2,08 % na 5,86 % (index 2,82), v Česku z 2,57 % na 2,63 % (index 1,02); index je relativně o 176,5 % vyšší než v Česku.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Z01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>změna trendu</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.7647</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G6" t="n">
+        <v>176.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Míra zániku PO v oboru za rok 2025 je v Libereckém kraji 5,86 %, průměr let 2023–2024 je 2,5 % (relativně o 134,4 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Z02</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>změna trendu</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>134.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Míra zániku PO v oboru za rok 2025 je v Libereckém kraji 5,86 %, v Česku 2,63 % (relativně o 122,8 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Z03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>změna trendu</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.2281</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G8" t="n">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Míra zániku PO v oboru za období 1. 1.–15. 9. 2026 je v Libereckém kraji 3,47 %, v Česku 1,83 % (relativně o 89,6 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Z04</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>změna trendu</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8962</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G9" t="n">
+        <v>89.59999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kraj je mezi 14 kraji 13. podle počtu registrovaných subjektů oboru a 2. podle hustoty na 1 000 obyvatel.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Z05</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>divergence pořadí</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8462</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Nejvyšší hustotu oboru mezi okresy kraje má okres Jablonec nad Nisou (36,1 na 1 000 obyvatel), nejnižší okres Česká Lípa (25,67); hustota v okrese Jablonec nad Nisou je relativně o 40,6 % vyšší než v okrese Česká Lípa.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Z06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="E11" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="G11" t="n">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Typ osoby – „právnické osoby a ostatní (PO)“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11,7 %, v Česku 17,5 % (relativně o 33,1 % nižší).</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Z07</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Právní forma – „112 Společnost s ručením omezeným“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11,1 %, v Česku 16,6 % (relativně o 33,1 % nižší).</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Z08</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="E13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Věk subjektu – „31 a více let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 19,4 %, v Česku 15,5 % (relativně o 25,2 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Z09</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="E14" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Česká Lípa 25,67 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 22,2 % nižší).</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Z10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.2219</v>
+      </c>
+      <c r="E15" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="F15" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G15" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Lokalizační koeficient oboru je v Libereckém kraji 1,19 proti 1 za ČR (relativně o 19 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Z11</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Věk subjektu – „méně než 3 roky“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11,4 %, v Česku 14 % (relativně o 18,6 % nižší).</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Z12</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1857</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Česká Lípa 25,67 registrovaných subjektů oboru, v Česku 31,14 (relativně o 17,6 % nižší).</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Z13</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1757</v>
+      </c>
+      <c r="E18" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="F18" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="G18" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Jablonec nad Nisou 36,1 registrovaných subjektů oboru, v Česku 31,14 (relativně o 15,9 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Z14</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="E19" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Liberec 36,08 registrovaných subjektů oboru, v Česku 31,14 (relativně o 15,9 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Z15</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="E20" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="F20" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Velikost PO – „1–9 zaměstnanců“: podíl na PO oboru je v Libereckém kraji 44,8 %, v Česku 38,8 % (relativně o 15,5 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Z16</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="E21" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="F21" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Velikost PO – „Neuvedeno“: podíl na PO oboru je v Libereckém kraji 44,9 %, v Česku 50,7 % (relativně o 11,4 % nižší).</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Z17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="E22" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G22" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Jablonec nad Nisou 36,1 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 9,4 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Z18</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.09429999999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Liberec 36,08 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 9,4 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Z19</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.09370000000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="F24" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Právní forma – „101 Fyzická osoba podnikající dle živnostenského zákona“: podíl na registrovaných subjektech oboru je v Libereckém kraji 85,9 %, v Česku 79 % (relativně o 8,7 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Z20</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0873</v>
+      </c>
+      <c r="E25" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="F25" t="n">
+        <v>79</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Míra zániku PO v oboru za období 1. 1.–15. 9. 2026 je v Libereckém kraji 3,47 %, průměr let 2024–2025 je 3,2 % (relativně o 8,4 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Z21</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>změna trendu</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0844</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Věk subjektu – „11–20 let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 22,1 %, v Česku 23,9 % (relativně o 7,5 % nižší).</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Z22</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.07530000000000001</v>
+      </c>
+      <c r="E27" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Typ osoby – „fyzické osoby (FO)“: podíl na registrovaných subjektech oboru je v Libereckém kraji 88,3 %, v Česku 82,5 % (relativně o 7 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Z23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="E28" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Podíl registrovaných subjektů se zjištěnou aktivitou je v Libereckém kraji v sekci F 62,8 %, ve všech oborech 59,1 % (ČSÚ; relativně o 6,3 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Z24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>aktivita oboru vůči kraji</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0626</v>
+      </c>
+      <c r="E29" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Věk subjektu – „3–5 let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 9,3 %, v Česku 9,9 % (relativně o 6,1 % nižší).</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Z25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0606</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v Libereckém kraji 32,99 registrovaných subjektů oboru, v Česku 31,14 (relativně o 5,9 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Z26</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="E31" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="F31" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Semily 31,61 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 4,2 % nižší).</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Z27</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="E32" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="F32" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Velikost FO – „Neuvedeno“: podíl na FO oboru je v Libereckém kraji 45,6 %, v Česku 44 % (relativně o 3,6 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Z28</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="E33" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>44</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Velikost PO – „10–49 zaměstnanců“: podíl na PO oboru je v Libereckém kraji 9,5 %, v Česku 9,2 % (relativně o 3,3 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Z29</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Síla = |hodnota / srovnání − 1|; u divergence pořadí |p1 − p2| / (počet území − 1). Rozdíly pod 3 % relativně se nehlásí. Položky struktury s podílem pod 5 % v území i v ČR se nehlásí. Popisy jsou věcné, bez interpretace.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kód</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Název</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Definice</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Vzorec</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Zdroj</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Úroveň</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Ošetření chybějících hodnot</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Poznámka k výkladu</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Stav</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Použit v této příloze</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REG_POCET</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Počet registrovaných subjektů v oboru a území</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Registrované ekonomické subjekty bez data zániku s převažující činností v oboru a sídlem v území.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>count(subjekt) where ddatzan is null and nace ∈ obor and okres/kraj(sídlo) ∈ území</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data (res_data.csv), snímek k datu</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Subjekty bez NACE sekce (pseudokód 00) a subjekty zařazené jen do vyšší úrovně klasifikace se do oboru nepočítají, uvádějí se zvlášť (DOPL_OBOR_NEURCEN, DOPL_JEN_VYSSI). Zaniklé subjekty se nepočítají.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Jde o registrované subjekty; podle ČSÚ má zjištěnou aktivitu (daně, pojistné) jen asi 60 % z nich (AKTIVNI_PODIL_KRAJ).</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REG_POCET_CR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Počet registrovaných subjektů v oboru v ČR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>REG_POCET za celou ČR.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>count(subjekt) where ddatzan is null and nace ∈ obor</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>jako REG_POCET</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Jmenovatel podílu území na ČR.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REG_PODIL_CR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Podíl území na registrovaných subjektech oboru v ČR (%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kolik procent registrovaných subjektů oboru v ČR má sídlo v území.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>100 × REG_POCET(území) / REG_POCET_CR</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>kraj, okres</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Srovnávejte s podílem území na všech subjektech (viz LQ).</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REG_POCET_VSE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Počet všech registrovaných subjektů v území</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Registrované subjekty bez data zániku se sídlem v území, všechny obory včetně pseudokódu 00.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>count(subjekt) where ddatzan is null and sídlo ∈ území</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Jmenovatel podílu oboru v území a lokalizačního koeficientu.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REG_PODIL_OBOR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Podíl oboru na registrovaných subjektech území (%)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Kolik procent všech registrovaných subjektů území má převažující činnost v oboru.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>100 × REG_POCET / REG_POCET_VSE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Jmenovatel obsahuje i subjekty s pseudokódem 00 (obor neurčen), shodně v čitateli ČR i území.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LQ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lokalizační koeficient</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Podíl oboru na subjektech území dělený podílem oboru na subjektech ČR.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>(REG_POCET / REG_POCET_VSE) / (REG_POCET_CR / REG_POCET_VSE(ČR))</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>kraj, okres</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>&gt;1 = obor je v území zastoupen víc než v průměru ČR. Počítá registrované subjekty, ne zaměstnanost ani výkon.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OBYVATELE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Počet obyvatel území</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Počet obyvatel k 31. 12. posledního zveřejněného roku.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>převzato</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada OBY02A (ukazatel 2406K2)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Praha nemá okres v datech obyvatelstva; okres Praha (CZ0100) = kraj Hlavní město Praha.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Rok stavu obyvatel se liší od data snímku RES.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HUSTOTA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Registrované subjekty oboru na 1 000 obyvatel</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Počet registrovaných subjektů oboru na 1 000 obyvatel území.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1000 × REG_POCET / OBYVATELE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>odvozeno z RES a ČSÚ OBY02A</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sídlo subjektu nemusí být místem činnosti; v Praze je hustota zvýšena sídly bez činnosti v Praze.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PORADI_POCET</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pořadí podle počtu registrovaných subjektů oboru</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>poradi</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pořadí kraje mezi 14 kraji (u okresu mezi okresy téhož kraje) podle REG_POCET, 1 = nejvíce.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>rank() over (order by REG_POCET desc)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>kraj, okres</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pořadí se počítá ze skutečných počtů všech území; zveřejní se jen u zveřejněných počtů.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Automaticky se srovnává jen s ČR a pořadím mezi všemi kraji; srovnávací kraje volí člověk.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PORADI_HUSTOTA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pořadí podle hustoty na 1 000 obyvatel</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>poradi</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Pořadí kraje mezi 14 kraji (u okresu mezi okresy téhož kraje) podle HUSTOTA, 1 = nejvyšší.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>rank() over (order by HUSTOTA desc)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>odvozeno z RES a ČSÚ OBY02A</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>kraj, okres</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>jako PORADI_POCET</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Odstraňuje vliv velikosti území.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FOPO_POCET</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Registrované subjekty podle typu osoby (FO/PO)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FO = statistická právní forma (FORMA) 101–108, 424, 425 (podnikající fyzické osoby včetně zahraničních); PO = ostatní formy.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>count(subjekt) group by FO/PO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data; vymezení FO podle metodiky ČSÚ (statistiky z RES)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Je-li FO nebo PO pod prahem, rozdělení se nezveřejní (a s ním ani velikostní profily FO/PO).</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>FO jsou většinou OSVČ; název subjektu je u nich jméno osoby.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FOPO_PODIL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Podíl FO/PO (%)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Podíl FO resp. PO na REG_POCET.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>100 × FOPO_POCET / REG_POCET</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>jako FOPO_POCET</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FORMA_POCET</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Registrované subjekty podle právní formy</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Počet podle statistické právní formy (FORMA, číselník ČSÚ 56).</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>count(subjekt) group by forma</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data; číselník 56</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Formy pod prahem se slučují do „ostatní formy FO“ / „ostatní formy PO“ (v rámci skupiny); je-li skryté rozdělení FO/PO, do jednoho „ostatní“.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FORMA_PODIL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Podíl právní formy (%)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Podíl na REG_POCET.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>100 × FORMA_POCET / REG_POCET</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>jako FORMA_POCET</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VEL_FO_POCET</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Velikostní profil FO – počet podle kategorie zaměstnanců</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FO podle KATPO (číselník 579) seskupené do pásem: bez zaměstnanců (110), 1–9 (120, 130), 10–49 (210–230), 50–249 (240–320), 250 a více (330–510), Neuvedeno (000).</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>count(subjekt FO) group by pásmo(KATPO)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data; číselník 579</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>„Neuvedeno“ (000) je vždy samostatný řádek, nikdy se neslučuje s „bez zaměstnanců“; pásma pod prahem se slučují do „ostatní“.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>U FO znamená 110 bez zaměstnanců; od 7/2024 se do zaměstnanců počítají i DPP.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>VEL_FO_PODIL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Velikostní profil FO – podíl (%)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Podíl pásma na FO celkem; podíl „Neuvedeno“ se zobrazuje vždy (je-li zveřejnitelný).</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>100 × VEL_FO_POCET / FOPO_POCET(FO)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>jako VEL_FO_POCET</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>VEL_PO_POCET</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Velikostní profil PO – počet podle kategorie zaměstnanců</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PO podle KATPO v týchž pásmech jako VEL_FO_POCET.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>count(subjekt PO) group by pásmo(KATPO)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data; číselník 579</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>jako VEL_FO_POCET</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>U PO se kód 110 prakticky nepoužívá; PO bez hlášených zaměstnanců mají „Neuvedeno“ (000). Neuvedeno ≠ bez zaměstnanců.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>VEL_PO_PODIL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Velikostní profil PO – podíl (%)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Podíl pásma na PO celkem.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>100 × VEL_PO_POCET / FOPO_POCET(PO)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>jako VEL_PO_POCET</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VEK_PRUMER</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Průměrný věk existujících subjektů (roky)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>prumer</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Průměr (datum snímku − datum vzniku) v letech u registrovaných subjektů oboru v území.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>avg((datum_snimku − ddatvzn) / 365.25)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Věková struktura existujících subjektů, ne dynamika vzniku (zaniklé subjekty nejsou zahrnuty).</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VEK_MEDIAN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mediánový věk existujících subjektů (roky)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>prumer</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Medián (datum snímku − datum vzniku) v letech.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>percentile_cont(0.5)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>jako VEK_PRUMER</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>jako VEK_PRUMER</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>VEK_PASMO_POCET</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Věková struktura existujících subjektů – počet v pásmu</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Pásma věku: méně než 3 roky, 3–5, 6–10, 11–20, 21–30, 31 a více let.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>count(subjekt) group by pásmo(věk)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Pásma pod prahem se slučují do „ostatní“.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Není to počet vzniků v jednotlivých letech.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VEK_PASMO_PODIL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Věková struktura existujících subjektů – podíl pásma (%)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Podíl pásma na REG_POCET.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>100 × VEK_PASMO_POCET / REG_POCET</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>jako VEK_PASMO_POCET</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DOPL_JEN_VYSSI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Zařazeno jen do vyšší úrovně klasifikace (např. „zařazeno jen do sekce“)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Registrované subjekty v území, jejichž NACE je nadřazený kód zkoumaného oboru (např. jen „J“ u oddílu 62) – do oboru mohou, ale nemusí patřit.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>count(subjekt) where nace ∈ předci(obor)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Samostatné číslo; pod prahem se nezveřejní. Jen pro obor na úrovni oddílu a nižší.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Horní mez nejistoty počtu v oboru.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DOPL_OBOR_NEURCEN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Obor neurčen (pseudokód 00)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Registrované subjekty v území s pseudokódem 00 („výroba, obchod a služby neuvedené v přílohách 1 až 3 živnostenského zákona“).</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>count(subjekt) where nace = '00'</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Samostatné číslo; pod prahem se nezveřejní.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Tyto subjekty nejde přiřadit žádnému oboru; ČSÚ je vykazuje jako „X Nezjištěno“.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AKTIVNI_PODIL_KRAJ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Podíl subjektů se zjištěnou aktivitou v kraji podle ČSÚ (%, všechny obory)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Počet ekonomických subjektů se zjištěnou aktivitou / počet ekonomických subjektů celkem, kraj (u okresu jeho kraj), všechny obory, poslední čtvrtletí.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>100 × 4958_akt / 4958_reg (RES02QT1, NACE celkem)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, výběr RES02QT1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Za okres ČSÚ podíl v členění podle převažující činnosti nepublikuje; uvádí se krajský.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Jen kontext. Aktivitu po subjektech nedopočítáváme; počty v reportu jsou registrované subjekty.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AKTIVNI_PODIL_SEKCE_KRAJ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Podíl subjektů se zjištěnou aktivitou v sekci a kraji podle ČSÚ (%)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Jako AKTIVNI_PODIL_KRAJ, ale jen pro sekci CZ-NACE zkoumaného oboru.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>100 × 4958_akt / 4958_reg (RES02QT1, sekce)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, výběr RES02QT1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Jen je-li obor přesně jedna sekce, kterou ČSÚ publikuje samostatně (ne B, C, D, E – ty jen jako B–E); jinak nelze naplnit.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Jen kontext.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ZANIK_PO_RES</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PO s datem zániku od 1. 1. 2023 do data snímku, s převažující činností v oboru a sídlem v území.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>count(subjekt PO) where ddatzan &gt;= 2023-01-01 group by year(ddatzan)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Zaniklé FO mají v otevřených datech jen IČO a datum zániku (GDPR) – do oboru ani území je přiřadit nelze. Zaniklé více než 4 roky v RES nejsou; proto jen od roku 2023. Poslední rok je neúplný.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Jen PO. Míru zániku (normalizovanou stavem PO) uvádí MIRA_ZANIKU_PO.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DYN_VZNIK_CSU</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Vzniklé ekonomické subjekty v území podle ČSÚ (všechny obory)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Počet vzniklých ekonomických subjektů v roce (součet čtvrtletí), FO a PO, území celkem.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>sum(4962) over čtvrtletí roku (RES05)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada RES05</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ČSÚ vznik a zánik v členění podle oboru (kraj × sekce ani ČR × obor) z RES nepublikuje – dynamiku oboru nelze naplnit. Poslední rok je neúplný (jen zveřejněná čtvrtletí).</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Dynamika celého území, ne oboru.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DYN_ZANIK_CSU</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Zaniklé ekonomické subjekty v území podle ČSÚ (všechny obory)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Počet zaniklých ekonomických subjektů v roce (součet čtvrtletí), FO a PO, území celkem.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>sum(4963) over čtvrtletí roku (RES05)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada RES05</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>jako DYN_VZNIK_CSU. Rok 2023 u FO obsahuje mimořádný výkyv (1. čtvrtletí 2023 hromadný zánik FO, v ČR 200 977 zániků FO proti obvyklým 15–45 tis.).</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Dynamika celého území, ne oboru.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DYN_OBOR_CSU</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Vznik a zánik subjektů v oboru a území podle ČSÚ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Počet vzniklých a zaniklých subjektů v oboru × kraji.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ČSÚ DataStat – tabulka v tomto členění neexistuje (RES05 jen území × FO/PO; RES06 registrace a RESDP00 demografie podniků jen za ČR podle odvětví)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Nelze naplnit.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Mimo v0 (rozhodnutí 10) – vznikne později z archivu snímků RES. Náhradou je dynamika území (RES05), kontext ČR z demografie podniků (RESDP00), ZANIK_PO_RES a věková struktura.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>nelze naplnit</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SPOLEHLIVOST_JEN_SEKCE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Spolehlivost zařazení – subjekty zařazené jen do sekce vůči počtu oboru (%)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Registrované subjekty v území s převažující činností uvedenou jen písmenem sekce oboru (např. „J“ u oddílu 62) děleno počtem oboru v území (rozhodnutí 9).</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>100 × DOPL_JEN_VYSSI(sekce) / REG_POCET</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Jen pro obor na úrovni oddílu a nižší. Nezveřejní se, je-li počet „jen do sekce“ pod prahem (pak je podíl nutně malý).</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Nad 25 % nese report varování na titulní straně i v metodické poznámce: skutečný počet oboru může být výrazně vyšší.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DEMOGR_AKTIVNI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Aktivní podniky v ČR (demografie podniků)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Počet aktivních podniků podle statistiky demografie podniků ČSÚ, FO a PO zvlášť, odvětví oboru a všechna odvětví.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>převzato (RESDP00, ukazatel 6594_RESDP)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada RESDP00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Odvětví jen B–R (K = peněžní zprostředkování, S = osobní služby); A, O, T, U v RESDP00 nejsou. Poslední rok bývá předběžný.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Jiná jednotka (aktivní podnik), nesrovnatelné s registrovanými subjekty RES; jen kontext za ČR (rozhodnutí 10).</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DEMOGR_MIRA_VZNIKU</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Míra vzniků podniků v ČR (%)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Vzniklé podniky / aktivní podniky × 100 podle ČSÚ, FO a PO zvlášť.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>převzato (RESDP00, ukazatel 9507)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada RESDP00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>jako DEMOGR_AKTIVNI</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Kontext dynamiky oboru za ČR; dynamika obor × území je mimo v0 (vznikne z archivu snímků RES).</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DEMOGR_MIRA_ZANIKU</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Míra zániků podniků v ČR (%)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Zaniklé podniky / aktivní podniky × 100 podle ČSÚ, FO a PO zvlášť.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>převzato (RESDP00, ukazatel 9508)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada RESDP00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Zánik se zjišťuje se zpožděním; poslední rok bez zániků se nezobrazuje.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>jako DEMOGR_MIRA_VZNIKU</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BENCH_PODIL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Podíl položky struktury – zkoumané území, ČR a srovnávací kraje (%)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Podíl položky (typ osoby, právní forma, velikostní pásmo, věkové pásmo, „Neuvedeno“) na registrovaných subjektech téhož oboru v daném území.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>100 × počet(položka, obor, území) / počet(obor, území); u velikosti jmenovatel FO, resp. PO</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Práh a slučování platí pro každé území zvlášť; položky sloučené ve zkoumaném území jsou předem sloučené i v ostatních sloupcích; položka pod prahem v benchmarkovém území je sloučena do „ostatní“ (pomlčka).</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Srovnává strukturu oboru, ne velikost území. Rozdíl menší než 3 % relativně se popisuje jako „srovnatelné“.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BENCH_ROZDIL_PB</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rozdíl podílu zkoumaného území proti ČR (procentní body)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Podíl položky ve zkoumaném území minus týž podíl v ČR.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BENCH_PODIL(území) − BENCH_PODIL(ČR), z hodnot zaokrouhlených na 0,1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>kraj, okres</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Jen jsou-li zveřejněné oba podíly.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Procentní body, ne procenta; relativní rozdíl uvádí detektor zjištění.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ZANIK_PO_STAV</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Stav právnických osob v oboru a území k 1. 1. (rekonstruovaný z RES)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PO s převažující činností v oboru a sídlem v území, které k 1. 1. roku existovaly.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>count(PO bez zániku, ddatvzn &lt; 1. 1. Y) + count(PO zaniklé, ddatvzn &lt; 1. 1. Y, ddatzan &gt;= 1. 1. Y)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data (jeden snímek)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Zaniklé subjekty jsou v RES jen 4 roky po zániku, proto stav lze rekonstruovat jen od 2023. Obor a sídlo podle snímku. Nezveřejní se pod prahem ani tehdy, když by z po sobě jdoucích stavů šel dopočítat počet vzniků pod prahem.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Jmenovatel míry zániku PO.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ZANIK_PO_OBD</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Zaniklé právnické osoby ve srovnatelném období roku (1. 1.–den snímku)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PO v oboru a území s datem zániku od 1. 1. do dne a měsíce snímku téhož roku.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>count(PO) where 1. 1. Y &lt;= ddatzan &lt;= (Y, měsíc a den snímku)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Nezveřejní se pod prahem ani tehdy, když by šel dopočítat zbytek roku pod prahem.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Umožňuje srovnat neúplný poslední rok s předchozími.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MIRA_ZANIKU_PO</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Míra zániku právnických osob v oboru za rok (%)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Zaniklé PO v roce / stav PO k 1. 1. téhož roku × 100.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>100 × ZANIK_PO_RES(Y) / ZANIK_PO_STAV(Y)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Jen úplné roky; jen jsou-li oba počty zveřejněné.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Jen PO, okno 4 let. Normalizuje zániky velikostí populace, takže je srovnatelná mezi územími.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MIRA_ZANIKU_PO_OBD</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Míra zániku právnických osob ve srovnatelném období (%)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Zaniklé PO od 1. 1. do dne a měsíce snímku / stav PO k 1. 1. × 100.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>100 × ZANIK_PO_OBD(Y) / ZANIK_PO_STAV(Y)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Jen jsou-li oba počty zveřejněné.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Jediná srovnatelná míra pro neúplný poslední rok.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ZJ_TYP</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Typ zjištění</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>zjisteni</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Odchylka od ČR, změna trendu, rozdíly uvnitř území, aktivita oboru vůči kraji, divergence pořadí.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>report_zjisteni</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>odvozeno z tabulek reportu</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Popis bez interpretace; „proč“ píše analytik.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ZJ_SILA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Síla zjištění</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>zjisteni</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Absolutní relativní rozdíl |a / b − 1| (u divergence pořadí |p1 − p2| / (počet území − 1)).</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>report_zjisteni</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>odvozeno ze zveřejněných čísel tabulek</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Zjištění pod 0,03 (3 %) se nehlásí.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Bezrozměrné číslo, zjištění se podle něj řadí.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ZJ_HODNOTA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Hodnota zkoumaného území ve zjištění</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>zjisteni</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Číslo z tabulky reportu, k níž zjištění odkazuje (nebo průměr čísel z ní).</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>report_zjisteni</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>tabulky reportu</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ZJ_SROVNANI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Srovnávací hodnota ve zjištění</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>zjisteni</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Číslo, s nímž se hodnota srovnává (ČR, kraj, předchozí roky – průměr, druhé pořadí).</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>report_zjisteni</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>tabulky reportu</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ZJ_ROZDIL_PCT</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Relativní rozdíl (%)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>zjisteni</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Absolutní hodnota 100 × (hodnota / srovnání − 1), zaokrouhleno na 0,1; směr (vyšší / nižší) je ve větě zjištění.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>report_zjisteni</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>odvozeno</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>U divergence pořadí se neuvádí.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Pod 3 % se rozdíl nehlásí a v textu se popisuje jako „srovnatelné“.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Pravidla ochrany malých buněk: buňky pod prahem se v každém členění slučují do „ostatní“; je-li „ostatní“ pod prahem, přidá se další nejmenší buňka; skryté číslo nesmí jít dopočítat ze součtů ani z jiné tabulky (ověřeno kontrolou dopočtu). Podrobnosti: docs/report_metodika.md.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="140" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Zdroj</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Označení</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Licence</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CC BY 4.0 – https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Datum snímku RES</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Soubor RES</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://opendata.csu.gov.cz/soubory/od/od_org03/res_data.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Další zdroj</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada OBY02A – počet obyvatel k 31. 12. 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Další zdroj</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, výběr RES02QT1 – podíl subjektů se zjištěnou aktivitou, 2026-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Další zdroj</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada RES05 – vznik a zánik ekonomických subjektů</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Další zdroj</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada RESDP00 – demografie podniků (jednotka podnik, jen ČR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Povinnost</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Upravené nebo odvozené údaje musí být označeny jako odvozené a nesmí být prezentovány jako nezměněné oficiální statistiky ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Vygenerováno</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-01T09:24:46+00:00</t>
         </is>
       </c>
     </row>

--- a/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
+++ b/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
@@ -7215,7 +7215,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-01T09:24:46+00:00</t>
+          <t>2026-10-01T10:27:48+00:00</t>
         </is>
       </c>
     </row>

--- a/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
+++ b/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
@@ -7215,7 +7215,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-01T10:27:48+00:00</t>
+          <t>2026-10-01T10:33:20+00:00</t>
         </is>
       </c>
     </row>

--- a/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
+++ b/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
@@ -7215,7 +7215,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-01T10:33:20+00:00</t>
+          <t>2026-10-01T10:58:04+00:00</t>
         </is>
       </c>
     </row>

--- a/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
+++ b/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
@@ -22,13 +22,15 @@
     <sheet name="T15_bench_velikost_fo" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="T16_bench_velikost_po" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="T17_bench_vekova_struktura" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="T10_zaniky_po" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="T18_mira_zaniku_po" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="T11_dynamika_csu" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="T12_demografie_cr" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="T19_zjisteni" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Metodika" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Zdroj a licence" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="T20_mzdy_obor" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="T21_mzdy_aktualni" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="T10_zaniky_po" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="T18_mira_zaniku_po" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="T11_dynamika_csu" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="T12_demografie_cr" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="T19_zjisteni" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Metodika" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Zdroj a licence" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -760,58 +762,82 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>T10_zaniky_po</t>
+          <t>T20_mzdy_obor</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES, od 2023)</t>
+          <t>Zaměstnanci a průměrné mzdy v oboru – kraje a ČR (ČSÚ, roční zjišťování)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>T18_mira_zaniku_po</t>
+          <t>T21_mzdy_aktualni</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Míra zániku právnických osob v oboru (RES, 2023–2026)</t>
+          <t>Zaměstnanci a průměrné mzdy – novější roky v nejbližších publikovaných úrovních (ČSÚ, čtvrtletní zjišťování)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T11_dynamika_csu</t>
+          <t>T10_zaniky_po</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
+          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES, od 2023)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>T12_demografie_cr</t>
+          <t>T18_mira_zaniku_po</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+          <t>Míra zániku právnických osob v oboru (RES, 2023–2026)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>T11_dynamika_csu</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T12_demografie_cr</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>T19_zjisteni</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Zjištění detektoru (seřazeno podle síly)</t>
         </is>
@@ -2139,6 +2165,901 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Zaměstnanci a průměrné mzdy v oboru – kraje a ČR (ČSÚ, roční zjišťování)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Zaměstnanci v oboru (tis., přepočtené)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Podíl na zaměstnancích oboru v ČR (%)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Podíl oboru na zaměstnancích území (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Průměrná mzda v oboru (Kč)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Mzda proti oboru v ČR (ČR = 100)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Mzda proti všem odvětvím území (= 100)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2018</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>27419</v>
+      </c>
+      <c r="F6" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>91.59999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2019</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="E7" t="n">
+        <v>29459</v>
+      </c>
+      <c r="F7" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>91.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2020</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>30489</v>
+      </c>
+      <c r="F8" t="n">
+        <v>97</v>
+      </c>
+      <c r="G8" t="n">
+        <v>91.90000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2021</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>31437</v>
+      </c>
+      <c r="F9" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>90.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2022</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="E10" t="n">
+        <v>33623</v>
+      </c>
+      <c r="F10" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Česko – 2018</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>207.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>28298</v>
+      </c>
+      <c r="G11" t="n">
+        <v>88.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Česko – 2019</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="E12" t="n">
+        <v>30187</v>
+      </c>
+      <c r="G12" t="n">
+        <v>87.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Česko – 2020</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>209.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="E13" t="n">
+        <v>31444</v>
+      </c>
+      <c r="G13" t="n">
+        <v>86.90000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Česko – 2021</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="E14" t="n">
+        <v>32582</v>
+      </c>
+      <c r="G14" t="n">
+        <v>85.09999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Česko – 2022</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>214.9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="E15" t="n">
+        <v>34840</v>
+      </c>
+      <c r="G15" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2018</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E16" t="n">
+        <v>26064</v>
+      </c>
+      <c r="F16" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>87.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2019</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="E17" t="n">
+        <v>28413</v>
+      </c>
+      <c r="F17" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>87.40000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2020</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E18" t="n">
+        <v>29419</v>
+      </c>
+      <c r="F18" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>86.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2021</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="E19" t="n">
+        <v>30779</v>
+      </c>
+      <c r="F19" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>85.40000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2022</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="E20" t="n">
+        <v>33274</v>
+      </c>
+      <c r="F20" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2018</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="E21" t="n">
+        <v>24923</v>
+      </c>
+      <c r="F21" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2019</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="E22" t="n">
+        <v>27237</v>
+      </c>
+      <c r="F22" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>90.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2020</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="E23" t="n">
+        <v>28492</v>
+      </c>
+      <c r="F23" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>91.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2021</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="E24" t="n">
+        <v>29271</v>
+      </c>
+      <c r="F24" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>88.09999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2022</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="E25" t="n">
+        <v>31502</v>
+      </c>
+      <c r="F25" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Zdroj: ČSÚ, DataStat, výběry MZDCRRT2 (kraje × sekce CZ-NACE) a MZDCRRT1 (ČR × sekce) – roční zjišťování, pracovištní metoda (kraj podle místa pracoviště). ČSÚ je publikuje za roky 2010–2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Zaměstnanci = průměrný evidenční počet zaměstnanců přepočtený na plný úvazek; mzda = průměrná hrubá měsíční mzda na přepočtené počty. Nezahrnuje podnikající fyzické osoby bez pracovního poměru, proto se nesrovnává s počty registrovaných subjektů.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Průměr, ne medián: medián mezd ČSÚ za kraje publikuje jen podle pohlaví a bez členění podle odvětví.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Zaměstnanci a průměrné mzdy – novější roky v nejbližších publikovaných úrovních (ČSÚ, čtvrtletní zjišťování)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Zaměstnanci (tis., přepočtené)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Průměrná mzda (Kč)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – všechna odvětví – 2023</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>143.3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>38599</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – všechna odvětví – 2024</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>41450</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – všechna odvětví – 2025</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>148.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>44006</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – všechna odvětví – 2023</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>197.4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>39788</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – všechna odvětví – 2024</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>196.7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>42122</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – všechna odvětví – 2025</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>44862</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – všechna odvětví – 2023</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>37041</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – všechna odvětví – 2024</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>39257</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – všechna odvětví – 2025</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>41903</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Česko – všechna odvětví – 2023</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4047.6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>42801</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Česko – všechna odvětví – 2024</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4048.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>45643</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Česko – všechna odvětví – 2025</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4034.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>48670</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Česko – sekce F – 2023</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>217.4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>36084</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Česko – sekce F – 2024</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>39153</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Česko – sekce F – 2025</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>216.8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>42337</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Obor × kraj ČSÚ za roky po 2022 nepublikuje: roční zjišťování podle krajů a sekcí končí rokem 2022 a čtvrtletní zjišťování kombinaci kraj × odvětví nepublikuje. Uvádějí se proto nejbližší publikované úrovně: kraje za všechna odvětví a ČR za sekci F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Zdroj: ČSÚ, DataStat, výběry MZDRT5 (ČR a kraje, pracovištní metoda) a MZDRT2 (ČR × sekce) – čtvrtletní zjišťování, kumulace za rok. Hodnoty se od ročního zjišťování mírně liší; obě řady se nespojují.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2247,7 +3168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2690,579 +3611,6 @@
       <c r="A26" t="inlineStr">
         <is>
           <t>Omezení: jen právnické osoby – zaniklé FO mají v otevřených datech jen IČO a datum zániku. Okno 4 let (2023–2026): RES uchovává zaniklé subjekty jen 4 roky po zániku. Obor a sídlo jsou podle snímku (u zaniklých poslední známé), jejich změny v čase se nepromítají.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Položka</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>FO</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>PO</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Celkem</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Poznámka</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2023 – vzniklé</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2859</v>
-      </c>
-      <c r="C6" t="n">
-        <v>785</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3644</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2023 – zaniklé</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>13252</v>
-      </c>
-      <c r="C7" t="n">
-        <v>483</v>
-      </c>
-      <c r="D7" t="n">
-        <v>13735</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>mimořádný výkyv: hromadný zánik FO v 1. čtvrtletí 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2024 – vzniklé</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3326</v>
-      </c>
-      <c r="C8" t="n">
-        <v>768</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4094</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2024 – zaniklé</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3390</v>
-      </c>
-      <c r="C9" t="n">
-        <v>582</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3972</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2025 – vzniklé</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3239</v>
-      </c>
-      <c r="C10" t="n">
-        <v>766</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4005</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2025 – zaniklé</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2003</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1221</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3224</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026 – vzniklé</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1880</v>
-      </c>
-      <c r="C12" t="n">
-        <v>425</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2305</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2 čtvrtletí</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026 – zaniklé</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>850</v>
-      </c>
-      <c r="C13" t="n">
-        <v>516</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1366</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2 čtvrtletí</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ČSÚ nepublikuje vznik a zánik v členění podle oboru (kraj × sekce); jde o celé území. Čísla FO a PO pod prahem se nezveřejňují (zůstává jen celkem).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Položka</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Stavebnictví: aktivní podniky</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Stavebnictví: míra vzniků (%)</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Stavebnictví: míra zániků (%)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Všechna odvětví: aktivní podniky</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Všechna odvětví: míra vzniků (%)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Všechna odvětví: míra zániků (%)</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Poznámka</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2019 – podniky FO</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>151021</v>
-      </c>
-      <c r="C6" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7.44</v>
-      </c>
-      <c r="E6" t="n">
-        <v>903037</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7.84</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2019 – podniky PO</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>32611</v>
-      </c>
-      <c r="C7" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E7" t="n">
-        <v>306300</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2020 – podniky FO</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>151683</v>
-      </c>
-      <c r="C8" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="E8" t="n">
-        <v>906249</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="G8" t="n">
-        <v>7.69</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2020 – podniky PO</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>34021</v>
-      </c>
-      <c r="C9" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="E9" t="n">
-        <v>315010</v>
-      </c>
-      <c r="F9" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2021 – podniky FO</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>154046</v>
-      </c>
-      <c r="C10" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="E10" t="n">
-        <v>918884</v>
-      </c>
-      <c r="F10" t="n">
-        <v>9.07</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2021 – podniky PO</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>35822</v>
-      </c>
-      <c r="C11" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="E11" t="n">
-        <v>334396</v>
-      </c>
-      <c r="F11" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2022 – podniky FO</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>158250</v>
-      </c>
-      <c r="C12" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="D12" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="E12" t="n">
-        <v>946485</v>
-      </c>
-      <c r="F12" t="n">
-        <v>9.69</v>
-      </c>
-      <c r="G12" t="n">
-        <v>7.71</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2022 – podniky PO</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>37480</v>
-      </c>
-      <c r="C13" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="E13" t="n">
-        <v>344989</v>
-      </c>
-      <c r="F13" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.96</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2023 – podniky FO</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>162083</v>
-      </c>
-      <c r="C14" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="D14" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>968178</v>
-      </c>
-      <c r="F14" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="G14" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>předběžné hodnoty</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2023 – podniky PO</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>39445</v>
-      </c>
-      <c r="C15" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="E15" t="n">
-        <v>353778</v>
-      </c>
-      <c r="F15" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>předběžné hodnoty</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Jiná jednotka: aktivní PODNIK ze statistiky demografie podniků, ne registrovaný ekonomický subjekt z RES; čísla nejsou srovnatelná s ostatními tabulkami. Jen za ČR.</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3844,226 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>FO</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Celkem</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2023 – vzniklé</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2859</v>
+      </c>
+      <c r="C6" t="n">
+        <v>785</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3644</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2023 – zaniklé</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>13252</v>
+      </c>
+      <c r="C7" t="n">
+        <v>483</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13735</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mimořádný výkyv: hromadný zánik FO v 1. čtvrtletí 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024 – vzniklé</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3326</v>
+      </c>
+      <c r="C8" t="n">
+        <v>768</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4094</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024 – zaniklé</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3390</v>
+      </c>
+      <c r="C9" t="n">
+        <v>582</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3972</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025 – vzniklé</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3239</v>
+      </c>
+      <c r="C10" t="n">
+        <v>766</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025 – zaniklé</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2003</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3224</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026 – vzniklé</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1880</v>
+      </c>
+      <c r="C12" t="n">
+        <v>425</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2305</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2 čtvrtletí</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026 – zaniklé</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>850</v>
+      </c>
+      <c r="C13" t="n">
+        <v>516</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1366</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2 čtvrtletí</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ČSÚ nepublikuje vznik a zánik v členění podle oboru (kraj × sekce); jde o celé území. Čísla FO a PO pod prahem se nezveřejňují (zůstává jen celkem).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3512,7 +4079,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zjištění detektoru (seřazeno podle síly)</t>
+          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
         </is>
       </c>
     </row>
@@ -3538,32 +4105,32 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Zjištění</t>
+          <t>Stavebnictví: aktivní podniky</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Typ zjištění</t>
+          <t>Stavebnictví: míra vzniků (%)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Síla</t>
+          <t>Stavebnictví: míra zániků (%)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hodnota</t>
+          <t>Všechna odvětví: aktivní podniky</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Srovnání</t>
+          <t>Všechna odvětví: míra vzniků (%)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Relativní rozdíl (%)</t>
+          <t>Všechna odvětví: míra zániků (%)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -3575,845 +4142,267 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Míra zániku PO v oboru se mezi lety 2023 a 2025 změnila v Libereckém kraji z 2,08 % na 5,86 % (index 2,82), v Česku z 2,57 % na 2,63 % (index 1,02); index je relativně o 176,5 % vyšší než v Česku.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Z01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>změna trendu</t>
-        </is>
+          <t>2019 – podniky FO</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>151021</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7.81</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7647</v>
+        <v>7.44</v>
       </c>
       <c r="E6" t="n">
-        <v>2.82</v>
+        <v>903037</v>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>176.5</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Míra zániku PO v oboru za rok 2025 je v Libereckém kraji 5,86 %, průměr let 2023–2024 je 2,5 % (relativně o 134,4 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Z02</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>změna trendu</t>
-        </is>
+          <t>2019 – podniky PO</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>32611</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8.25</v>
       </c>
       <c r="D7" t="n">
-        <v>1.344</v>
+        <v>2.91</v>
       </c>
       <c r="E7" t="n">
-        <v>5.86</v>
+        <v>306300</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>8.26</v>
       </c>
       <c r="G7" t="n">
-        <v>134.4</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Míra zániku PO v oboru za rok 2025 je v Libereckém kraji 5,86 %, v Česku 2,63 % (relativně o 122,8 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Z03</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>změna trendu</t>
-        </is>
+          <t>2020 – podniky FO</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>151683</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7.42</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2281</v>
+        <v>6.89</v>
       </c>
       <c r="E8" t="n">
-        <v>5.86</v>
+        <v>906249</v>
       </c>
       <c r="F8" t="n">
-        <v>2.63</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>122.8</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Míra zániku PO v oboru za období 1. 1.–15. 9. 2026 je v Libereckém kraji 3,47 %, v Česku 1,83 % (relativně o 89,6 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Z04</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>změna trendu</t>
-        </is>
+          <t>2020 – podniky PO</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>34021</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7.15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8962</v>
+        <v>3.25</v>
       </c>
       <c r="E9" t="n">
-        <v>3.47</v>
+        <v>315010</v>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>7.42</v>
       </c>
       <c r="G9" t="n">
-        <v>89.59999999999999</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kraj je mezi 14 kraji 13. podle počtu registrovaných subjektů oboru a 2. podle hustoty na 1 000 obyvatel.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Z05</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>divergence pořadí</t>
-        </is>
+          <t>2021 – podniky FO</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>154046</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7.82</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8462</v>
+        <v>6.46</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>918884</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>9.07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nejvyšší hustotu oboru mezi okresy kraje má okres Jablonec nad Nisou (36,1 na 1 000 obyvatel), nejnižší okres Česká Lípa (25,67); hustota v okrese Jablonec nad Nisou je relativně o 40,6 % vyšší než v okrese Česká Lípa.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Z06</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
+          <t>2021 – podniky PO</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>35822</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7.52</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4063</v>
+        <v>3.42</v>
       </c>
       <c r="E11" t="n">
-        <v>36.1</v>
+        <v>334396</v>
       </c>
       <c r="F11" t="n">
-        <v>25.67</v>
+        <v>7.98</v>
       </c>
       <c r="G11" t="n">
-        <v>40.6</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Typ osoby – „právnické osoby a ostatní (PO)“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11,7 %, v Česku 17,5 % (relativně o 33,1 % nižší).</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Z07</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
+          <t>2022 – podniky FO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>158250</v>
+      </c>
+      <c r="C12" t="n">
+        <v>8.85</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3314</v>
+        <v>7.75</v>
       </c>
       <c r="E12" t="n">
-        <v>11.7</v>
+        <v>946485</v>
       </c>
       <c r="F12" t="n">
-        <v>17.5</v>
+        <v>9.69</v>
       </c>
       <c r="G12" t="n">
-        <v>33.1</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Právní forma – „112 Společnost s ručením omezeným“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11,1 %, v Česku 16,6 % (relativně o 33,1 % nižší).</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Z08</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
+          <t>2022 – podniky PO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>37480</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7.22</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3313</v>
+        <v>3.43</v>
       </c>
       <c r="E13" t="n">
-        <v>11.1</v>
+        <v>344989</v>
       </c>
       <c r="F13" t="n">
-        <v>16.6</v>
+        <v>7.21</v>
       </c>
       <c r="G13" t="n">
-        <v>33.1</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Věk subjektu – „31 a více let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 19,4 %, v Česku 15,5 % (relativně o 25,2 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Z09</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
+          <t>2023 – podniky FO</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>162083</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9.59</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2516</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>19.4</v>
+        <v>968178</v>
       </c>
       <c r="F14" t="n">
-        <v>15.5</v>
+        <v>9.83</v>
       </c>
       <c r="G14" t="n">
-        <v>25.2</v>
+        <v>8.789999999999999</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Na 1 000 obyvatel připadá v okrese Česká Lípa 25,67 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 22,2 % nižší).</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Z10</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
+          <t>2023 – podniky PO</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>39445</v>
+      </c>
+      <c r="C15" t="n">
+        <v>7.36</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2219</v>
+        <v>4.55</v>
       </c>
       <c r="E15" t="n">
-        <v>25.67</v>
+        <v>353778</v>
       </c>
       <c r="F15" t="n">
-        <v>32.99</v>
+        <v>7.02</v>
       </c>
       <c r="G15" t="n">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Lokalizační koeficient oboru je v Libereckém kraji 1,19 proti 1 za ČR (relativně o 19 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Z11</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>19</v>
+        <v>5.08</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Věk subjektu – „méně než 3 roky“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11,4 %, v Česku 14 % (relativně o 18,6 % nižší).</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Z12</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0.1857</v>
-      </c>
-      <c r="E17" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F17" t="n">
-        <v>14</v>
-      </c>
-      <c r="G17" t="n">
-        <v>18.6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Na 1 000 obyvatel připadá v okrese Česká Lípa 25,67 registrovaných subjektů oboru, v Česku 31,14 (relativně o 17,6 % nižší).</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Z13</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.1757</v>
-      </c>
-      <c r="E18" t="n">
-        <v>25.67</v>
-      </c>
-      <c r="F18" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="G18" t="n">
-        <v>17.6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Na 1 000 obyvatel připadá v okrese Jablonec nad Nisou 36,1 registrovaných subjektů oboru, v Česku 31,14 (relativně o 15,9 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Z14</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.1593</v>
-      </c>
-      <c r="E19" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="G19" t="n">
-        <v>15.9</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Na 1 000 obyvatel připadá v okrese Liberec 36,08 registrovaných subjektů oboru, v Česku 31,14 (relativně o 15,9 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Z15</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.1586</v>
-      </c>
-      <c r="E20" t="n">
-        <v>36.08</v>
-      </c>
-      <c r="F20" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="G20" t="n">
-        <v>15.9</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Velikost PO – „1–9 zaměstnanců“: podíl na PO oboru je v Libereckém kraji 44,8 %, v Česku 38,8 % (relativně o 15,5 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Z16</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.1546</v>
-      </c>
-      <c r="E21" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="F21" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="G21" t="n">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Velikost PO – „Neuvedeno“: podíl na PO oboru je v Libereckém kraji 44,9 %, v Česku 50,7 % (relativně o 11,4 % nižší).</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Z17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0.1144</v>
-      </c>
-      <c r="E22" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="F22" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="G22" t="n">
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Na 1 000 obyvatel připadá v okrese Jablonec nad Nisou 36,1 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 9,4 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Z18</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.09429999999999999</v>
-      </c>
-      <c r="E23" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="G23" t="n">
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Na 1 000 obyvatel připadá v okrese Liberec 36,08 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 9,4 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Z19</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.09370000000000001</v>
-      </c>
-      <c r="E24" t="n">
-        <v>36.08</v>
-      </c>
-      <c r="F24" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="G24" t="n">
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Právní forma – „101 Fyzická osoba podnikající dle živnostenského zákona“: podíl na registrovaných subjektech oboru je v Libereckém kraji 85,9 %, v Česku 79 % (relativně o 8,7 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Z20</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0.0873</v>
-      </c>
-      <c r="E25" t="n">
-        <v>85.90000000000001</v>
-      </c>
-      <c r="F25" t="n">
-        <v>79</v>
-      </c>
-      <c r="G25" t="n">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Míra zániku PO v oboru za období 1. 1.–15. 9. 2026 je v Libereckém kraji 3,47 %, průměr let 2024–2025 je 3,2 % (relativně o 8,4 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Z21</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>změna trendu</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0844</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="F26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G26" t="n">
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Věk subjektu – „11–20 let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 22,1 %, v Česku 23,9 % (relativně o 7,5 % nižší).</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Z22</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0.07530000000000001</v>
-      </c>
-      <c r="E27" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G27" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Typ osoby – „fyzické osoby (FO)“: podíl na registrovaných subjektech oboru je v Libereckém kraji 88,3 %, v Česku 82,5 % (relativně o 7 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Z23</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0.0703</v>
-      </c>
-      <c r="E28" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="F28" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="G28" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Podíl registrovaných subjektů se zjištěnou aktivitou je v Libereckém kraji v sekci F 62,8 %, ve všech oborech 59,1 % (ČSÚ; relativně o 6,3 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Z24</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>aktivita oboru vůči kraji</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0.0626</v>
-      </c>
-      <c r="E29" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="F29" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Věk subjektu – „3–5 let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 9,3 %, v Česku 9,9 % (relativně o 6,1 % nižší).</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Z25</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0606</v>
-      </c>
-      <c r="E30" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="F30" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="G30" t="n">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Na 1 000 obyvatel připadá v Libereckém kraji 32,99 registrovaných subjektů oboru, v Česku 31,14 (relativně o 5,9 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Z26</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.0594</v>
-      </c>
-      <c r="E31" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="F31" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="G31" t="n">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Na 1 000 obyvatel připadá v okrese Semily 31,61 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 4,2 % nižší).</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Z27</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>rozdíly uvnitř území</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0.0418</v>
-      </c>
-      <c r="E32" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="F32" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="G32" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Velikost FO – „Neuvedeno“: podíl na FO oboru je v Libereckém kraji 45,6 %, v Česku 44 % (relativně o 3,6 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Z28</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0.0364</v>
-      </c>
-      <c r="E33" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="F33" t="n">
-        <v>44</v>
-      </c>
-      <c r="G33" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Velikost PO – „10–49 zaměstnanců“: podíl na PO oboru je v Libereckém kraji 9,5 %, v Česku 9,2 % (relativně o 3,3 % vyšší).</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Z29</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>odchylka od ČR</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0.0326</v>
-      </c>
-      <c r="E34" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F34" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G34" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Síla = |hodnota / srovnání − 1|; u divergence pořadí |p1 − p2| / (počet území − 1). Rozdíly pod 3 % relativně se nehlásí. Položky struktury s podílem pod 5 % v území i v ČR se nehlásí. Popisy jsou věcné, bez interpretace.</t>
+          <t>Jiná jednotka: aktivní PODNIK ze statistiky demografie podniků, ne registrovaný ekonomický subjekt z RES; čísla nejsou srovnatelná s ostatními tabulkami. Jen za ČR.</t>
         </is>
       </c>
     </row>
@@ -4422,13 +4411,1061 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Zjištění detektoru (seřazeno podle síly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Zjištění</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Typ zjištění</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Síla</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Hodnota</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Srovnání</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Relativní rozdíl (%)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Míra zániku PO v oboru se mezi lety 2023 a 2025 změnila v Libereckém kraji z 2,08 % na 5,86 % (index 2,82), v Česku z 2,57 % na 2,63 % (index 1,02); index je relativně o 176,5 % vyšší než v Česku.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Z01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>změna trendu</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.7647</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G6" t="n">
+        <v>176.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Míra zániku PO v oboru za rok 2025 je v Libereckém kraji 5,86 %, průměr let 2023–2024 je 2,5 % (relativně o 134,4 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Z02</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>změna trendu</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>134.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Míra zániku PO v oboru za rok 2025 je v Libereckém kraji 5,86 %, v Česku 2,63 % (relativně o 122,8 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Z03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>změna trendu</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.2281</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G8" t="n">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Míra zániku PO v oboru za období 1. 1.–15. 9. 2026 je v Libereckém kraji 3,47 %, v Česku 1,83 % (relativně o 89,6 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Z04</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>změna trendu</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8962</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G9" t="n">
+        <v>89.59999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kraj je mezi 14 kraji 13. podle počtu registrovaných subjektů oboru a 2. podle hustoty na 1 000 obyvatel.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Z05</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>divergence pořadí</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8462</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Nejvyšší hustotu oboru mezi okresy kraje má okres Jablonec nad Nisou (36,1 na 1 000 obyvatel), nejnižší okres Česká Lípa (25,67); hustota v okrese Jablonec nad Nisou je relativně o 40,6 % vyšší než v okrese Česká Lípa.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Z06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="E11" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="G11" t="n">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Typ osoby – „právnické osoby a ostatní (PO)“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11,7 %, v Česku 17,5 % (relativně o 33,1 % nižší).</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Z07</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Právní forma – „112 Společnost s ručením omezeným“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11,1 %, v Česku 16,6 % (relativně o 33,1 % nižší).</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Z08</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="E13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Věk subjektu – „31 a více let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 19,4 %, v Česku 15,5 % (relativně o 25,2 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Z09</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="E14" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Česká Lípa 25,67 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 22,2 % nižší).</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Z10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.2219</v>
+      </c>
+      <c r="E15" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="F15" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G15" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Lokalizační koeficient oboru je v Libereckém kraji 1,19 proti 1 za ČR (relativně o 19 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Z11</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Věk subjektu – „méně než 3 roky“: podíl na registrovaných subjektech oboru je v Libereckém kraji 11,4 %, v Česku 14 % (relativně o 18,6 % nižší).</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Z12</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1857</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Česká Lípa 25,67 registrovaných subjektů oboru, v Česku 31,14 (relativně o 17,6 % nižší).</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Z13</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1757</v>
+      </c>
+      <c r="E18" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="F18" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="G18" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sekce F tvořila v roce 2022 v Libereckém kraji 4,44 % zaměstnanců (přepočtené počty), v Česku 5,33 % (relativně o 16,7 % nižší).</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Z14</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>mzdy a zaměstnanost</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="G19" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Jablonec nad Nisou 36,1 registrovaných subjektů oboru, v Česku 31,14 (relativně o 15,9 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Z15</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="E20" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Liberec 36,08 registrovaných subjektů oboru, v Česku 31,14 (relativně o 15,9 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Z16</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="E21" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="F21" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="G21" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Velikost PO – „1–9 zaměstnanců“: podíl na PO oboru je v Libereckém kraji 44,8 %, v Česku 38,8 % (relativně o 15,5 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Z17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="E22" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="F22" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Velikost PO – „Neuvedeno“: podíl na PO oboru je v Libereckém kraji 44,9 %, v Česku 50,7 % (relativně o 11,4 % nižší).</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Z18</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="E23" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Jablonec nad Nisou 36,1 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 9,4 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Z19</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.09429999999999999</v>
+      </c>
+      <c r="E24" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Liberec 36,08 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 9,4 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Z20</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.09370000000000001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="F25" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Právní forma – „101 Fyzická osoba podnikající dle živnostenského zákona“: podíl na registrovaných subjektech oboru je v Libereckém kraji 85,9 %, v Česku 79 % (relativně o 8,7 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Z21</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0873</v>
+      </c>
+      <c r="E26" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="F26" t="n">
+        <v>79</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Míra zániku PO v oboru za období 1. 1.–15. 9. 2026 je v Libereckém kraji 3,47 %, průměr let 2024–2025 je 3,2 % (relativně o 8,4 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Z22</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>změna trendu</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0844</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Věk subjektu – „11–20 let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 22,1 %, v Česku 23,9 % (relativně o 7,5 % nižší).</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Z23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.07530000000000001</v>
+      </c>
+      <c r="E28" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Typ osoby – „fyzické osoby (FO)“: podíl na registrovaných subjektech oboru je v Libereckém kraji 88,3 %, v Česku 82,5 % (relativně o 7 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Z24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="E29" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Průměrná mzda v sekci F dosahovala v roce 2022 v Libereckém kraji 91,5 % průměrné mzdy všech odvětví kraje, v Česku 85,8 % (relativně o 6,6 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Z25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mzdy a zaměstnanost</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="E30" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Podíl registrovaných subjektů se zjištěnou aktivitou je v Libereckém kraji v sekci F 62,8 %, ve všech oborech 59,1 % (ČSÚ; relativně o 6,3 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Z26</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>aktivita oboru vůči kraji</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0626</v>
+      </c>
+      <c r="E31" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Věk subjektu – „3–5 let“: podíl na registrovaných subjektech oboru je v Libereckém kraji 9,3 %, v Česku 9,9 % (relativně o 6,1 % nižší).</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Z27</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0606</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F32" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v Libereckém kraji 32,99 registrovaných subjektů oboru, v Česku 31,14 (relativně o 5,9 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Z28</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="E33" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="F33" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Na 1 000 obyvatel připadá v okrese Semily 31,61 registrovaných subjektů oboru, v Libereckém kraji 32,99 (relativně o 4,2 % nižší).</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Z29</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>rozdíly uvnitř území</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="E34" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="F34" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>V sekci F se počet zaměstnanců mezi lety 2018 a 2022 změnil v Libereckém kraji z 6 tis. na 6,4 tis. (index 1,07), v Česku z 207,9 tis. na 214,9 tis. (index 1,03); index je relativně o 3,9 % vyšší než v Česku.</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Z30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>mzdy a zaměstnanost</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Velikost FO – „Neuvedeno“: podíl na FO oboru je v Libereckém kraji 45,6 %, v Česku 44 % (relativně o 3,6 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Z31</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="E36" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>44</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Průměrná hrubá měsíční mzda v sekci F byla v roce 2022 v Libereckém kraji 33 623 Kč, v Česku 34 840 Kč (relativně o 3,5 % nižší).</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Z32</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>mzdy a zaměstnanost</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0349</v>
+      </c>
+      <c r="E37" t="n">
+        <v>33623</v>
+      </c>
+      <c r="F37" t="n">
+        <v>34840</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Velikost PO – „10–49 zaměstnanců“: podíl na PO oboru je v Libereckém kraji 9,5 %, v Česku 9,2 % (relativně o 3,3 % vyšší).</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Z33</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>odchylka od ČR</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="E38" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Síla = |hodnota / srovnání − 1|; u divergence pořadí |p1 − p2| / (počet území − 1). Rozdíly pod 3 % relativně se nehlásí. Položky struktury s podílem pod 5 % v území i v ČR se nehlásí. Popisy jsou věcné, bez interpretace.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7062,8 +8099,464 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MZDY_ZAM_OBOR</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Zaměstnanci v oboru a kraji (tis. osob, přepočtené počty)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Průměrný evidenční počet zaměstnanců přepočtený na plný úvazek v sekci CZ-NACE oboru a v kraji (pracovištní metoda) nebo v ČR.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>převzato (MZDCRRT2 kraje × sekce, MZDCRRT1 ČR × sekce; ukazatele 299AQ / 299A), zaokrouhleno na 0,1 tis.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, roční zjišťování (sada MZDCRR)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Jen jednotlivé sekce CZ-NACE (oddíl a nižší úrovně → sekce s označením); okresy ČSÚ nepublikuje (→ kraj s označením); kraj × sekce jen 2010–2022 (2022 předběžně).</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Zaměstnanci v pracovním poměru, ne podnikající fyzické osoby; nesrovnává se s počtem registrovaných subjektů.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
     <row r="48">
       <c r="A48" t="inlineStr">
+        <is>
+          <t>MZDY_ZAM_PODIL_CR</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Podíl kraje na zaměstnancích oboru v ČR (%)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Zaměstnanci oboru v kraji / zaměstnanci oboru v ČR × 100, obojí z ročního zjišťování.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>100 × MZDY_ZAM_OBOR(kraj) / MZDY_ZAM_OBOR(ČR)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>kraj</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Srovnávejte s podílem kraje na registrovaných subjektech oboru (REG_PODIL_CR).</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MZDY_ZAM_PODIL_UZEMI</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Podíl oboru na zaměstnancích území (%)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Zaměstnanci oboru / zaměstnanci všech odvětví v témže území × 100.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>100 × MZDY_ZAM_OBOR / zaměstnanci celkem (sekce „Celkem“)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Váha oboru na trhu práce území; srovnání kraje s ČR ukazuje specializaci podle zaměstnanosti.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MZDY_MZDA_OBOR</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Průměrná hrubá měsíční mzda v oboru a kraji (Kč)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Průměrná hrubá měsíční mzda na přepočtené počty zaměstnanců v sekci CZ-NACE oboru a v kraji nebo v ČR.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>převzato (MZDCRRT2, MZDCRRT1; ukazatel 5958P), zaokrouhleno na celé Kč</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, roční zjišťování (sada MZDCRR)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Jako MZDY_ZAM_OBOR. Medián za kraj × odvětví ČSÚ nepublikuje (za kraje jen podle pohlaví).</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Průměr je citlivý na vysoké mzdy; medián pro kraj × odvětví není k dispozici.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MZDY_MZDA_INDEX_CR</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mzda v oboru a kraji proti oboru v ČR (ČR = 100)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Průměrná mzda oboru v kraji / průměrná mzda oboru v ČR × 100.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>100 × MZDY_MZDA_OBOR(kraj) / MZDY_MZDA_OBOR(ČR)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>kraj</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Pod 100 = obor v kraji platí méně než obor v ČR.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MZDY_MZDA_INDEX_UZEMI</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Mzda v oboru proti všem odvětvím území (= 100)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Průměrná mzda oboru / průměrná mzda všech odvětví v témže území × 100.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>100 × MZDY_MZDA_OBOR / mzda celkem (sekce „Celkem“)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Postavení oboru mezi odvětvími téhož území.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MZDY_ZAM_UROVEN</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Zaměstnanci v nejbližší publikované úrovni (tis. osob, přepočtené počty)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Kraj za všechna odvětví nebo ČR za sekci oboru – pro roky, za které ČSÚ obor × kraj nepublikuje.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>převzato (MZDRT5, MZDRT2; ukazatel 299A), zaokrouhleno na 0,1 tis.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, čtvrtletní zjišťování (sada MZDR), kumulace za rok</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kraj × odvětví čtvrtletní zjišťování nepublikuje.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Jiné zjišťování než MZDY_ZAM_OBOR; řady se nespojují.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MZDY_MZDA_UROVEN</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Průměrná mzda v nejbližší publikované úrovni (Kč)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Kraj za všechna odvětví nebo ČR za sekci oboru – pro roky, za které ČSÚ obor × kraj nepublikuje.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>převzato (MZDRT5, MZDRT2; ukazatel 5958P), zaokrouhleno na celé Kč</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, čtvrtletní zjišťování (sada MZDR), kumulace za rok</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kraj × odvětví čtvrtletní zjišťování nepublikuje.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Jiné zjišťování než MZDY_MZDA_OBOR; řady se nespojují.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Pravidla ochrany malých buněk: buňky pod prahem se v každém členění slučují do „ostatní“; je-li „ostatní“ pod prahem, přidá se další nejmenší buňka; skryté číslo nesmí jít dopočítat ze součtů ani z jiné tabulky (ověřeno kontrolou dopočtu). Podrobnosti: docs/report_metodika.md.</t>
         </is>
@@ -7074,13 +8567,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7198,24 +8691,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Povinnost</t>
+          <t>Další zdroj</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Upravené nebo odvozené údaje musí být označeny jako odvozené a nesmí být prezentovány jako nezměněné oficiální statistiky ČSÚ.</t>
+          <t>ČSÚ, DataStat, výběry MZDCRRT1, MZDCRRT2, MZDRT2, MZDRT5 – zaměstnanci a průměrné hrubé měsíční mzdy</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Povinnost</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Upravené nebo odvozené údaje musí být označeny jako odvozené a nesmí být prezentovány jako nezměněné oficiální statistiky ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Vygenerováno</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-10-01T10:58:04+00:00</t>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-01T11:16:16+00:00</t>
         </is>
       </c>
     </row>

--- a/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
+++ b/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
@@ -8720,7 +8720,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-01T11:16:16+00:00</t>
+          <t>2026-10-01T11:29:41+00:00</t>
         </is>
       </c>
     </row>

--- a/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
+++ b/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
@@ -22,15 +22,17 @@
     <sheet name="T15_bench_velikost_fo" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="T16_bench_velikost_po" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="T17_bench_vekova_struktura" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="T20_mzdy_obor" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="T21_mzdy_aktualni" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="T10_zaniky_po" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="T18_mira_zaniku_po" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="T11_dynamika_csu" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="T12_demografie_cr" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="T19_zjisteni" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Metodika" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Zdroj a licence" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="T22_ekonomika" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="T23_nahrady" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="T20_mzdy_obor" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="T21_mzdy_aktualni" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="T10_zaniky_po" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="T18_mira_zaniku_po" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="T11_dynamika_csu" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="T12_demografie_cr" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="T19_zjisteni" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Metodika" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Zdroj a licence" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -762,82 +764,106 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>T20_mzdy_obor</t>
+          <t>T22_ekonomika</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zaměstnanci a průměrné mzdy v oboru – kraje a ČR (ČSÚ, roční zjišťování)</t>
+          <t>Hrubá přidaná hodnota, zaměstnanost a produktivita – kraje a ČR (Eurostat, regionální účty) – Stavebnictví (F)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>T21_mzdy_aktualni</t>
+          <t>T23_nahrady</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zaměstnanci a průměrné mzdy – novější roky v nejbližších publikovaných úrovních (ČSÚ, čtvrtletní zjišťování)</t>
+          <t>Náhrady zaměstnancům a hrubá přidaná hodnota – regiony soudržnosti (Eurostat) – Stavebnictví (F)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T10_zaniky_po</t>
+          <t>T20_mzdy_obor</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES, od 2023)</t>
+          <t>Zaměstnanci a průměrné mzdy v oboru – kraje a ČR (ČSÚ, roční zjišťování)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>T18_mira_zaniku_po</t>
+          <t>T21_mzdy_aktualni</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Míra zániku právnických osob v oboru (RES, 2023–2026)</t>
+          <t>Zaměstnanci a průměrné mzdy – novější roky v nejbližších publikovaných úrovních (ČSÚ, čtvrtletní zjišťování)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>T11_dynamika_csu</t>
+          <t>T10_zaniky_po</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
+          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES, od 2023)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>T12_demografie_cr</t>
+          <t>T18_mira_zaniku_po</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+          <t>Míra zániku právnických osob v oboru (RES, 2023–2026)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>T11_dynamika_csu</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T12_demografie_cr</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>T19_zjisteni</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Zjištění detektoru (seřazeno podle síly)</t>
         </is>
@@ -2165,6 +2191,1163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hrubá přidaná hodnota, zaměstnanost a produktivita – kraje a ČR (Eurostat, regionální účty) – Stavebnictví (F)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>HPH skupiny (mil. Kč, běžné ceny)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Podíl na HPH území (%)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Podíl na HPH skupiny v ČR (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Objemová změna HPH (%)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Objem HPH (1. rok = 100)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Zaměstnaní (tis.)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Sebezaměst­naní (%)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>HPH na zaměst­naného (tis. Kč)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Produktivita (ČR = 100)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2020</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9364</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="H6" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>734</v>
+      </c>
+      <c r="J6" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2021</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>9810</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="H7" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>753</v>
+      </c>
+      <c r="J7" t="n">
+        <v>95.90000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2022</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>11251</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="H8" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>850</v>
+      </c>
+      <c r="J8" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2023</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>12173</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="H9" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>935</v>
+      </c>
+      <c r="J9" t="n">
+        <v>100.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2024</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>12598</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>965</v>
+      </c>
+      <c r="J10" t="n">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Česko – 2020</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>292311</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="F11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G11" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Česko – 2021</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>312154</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>397.13</v>
+      </c>
+      <c r="H12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Česko – 2022</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>350966</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>404.22</v>
+      </c>
+      <c r="H13" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Česko – 2023</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>394052</v>
+      </c>
+      <c r="C14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>423.03</v>
+      </c>
+      <c r="H14" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Česko – 2024</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>409647</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>420.98</v>
+      </c>
+      <c r="H15" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2020</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>12134</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>773</v>
+      </c>
+      <c r="J16" t="n">
+        <v>102.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2021</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>12405</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="H17" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>786</v>
+      </c>
+      <c r="J17" t="n">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2022</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>13788</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="H18" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>864</v>
+      </c>
+      <c r="J18" t="n">
+        <v>99.59999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2023</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>15229</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="H19" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>898</v>
+      </c>
+      <c r="J19" t="n">
+        <v>96.40000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2024</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>16336</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>90</v>
+      </c>
+      <c r="G20" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="H20" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" t="n">
+        <v>995</v>
+      </c>
+      <c r="J20" t="n">
+        <v>102.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2020</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5039</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>100</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="H21" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>581</v>
+      </c>
+      <c r="J21" t="n">
+        <v>76.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2021</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5330</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="H22" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>639</v>
+      </c>
+      <c r="J22" t="n">
+        <v>81.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2022</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5968</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>671</v>
+      </c>
+      <c r="J23" t="n">
+        <v>77.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2023</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6599</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>722</v>
+      </c>
+      <c r="J24" t="n">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2024</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>6313</v>
+      </c>
+      <c r="C25" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I25" t="n">
+        <v>701</v>
+      </c>
+      <c r="J25" t="n">
+        <v>72.09999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Skupina odvětví A*10 regionálních účtů: Stavebnictví (F). Odpovídá sekci oboru přesně.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Zaměstnaní = zaměstnanost podle národních účtů (zaměstnanci i sebezaměstnaní, včetně podnikajících fyzických osob, místo pracoviště); liší se proto od přepočtených zaměstnanců ČSÚ v kapitole Zaměstnanost a mzdy (jen zaměstnanci, přepočet na plný úvazek) i od počtu registrovaných subjektů.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Objemová změna = HPH v cenách předchozího roku / HPH v běžných cenách předchozího roku − 1; objem (první rok = 100) je řetězením těchto změn. Produktivita = HPH v běžných cenách / zaměstnaní.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Eurostat u údajů neuvádí příznak předběžnosti; poslední publikovaný rok 2024 se při revizích regionálních účtů může změnit.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Náhrady zaměstnancům a hrubá přidaná hodnota – regiony soudržnosti (Eurostat) – Stavebnictví (F)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Náhrady zaměstnancům (mil. Kč)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>HPH (mil. Kč, běžné ceny)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Náhrady zaměstnancům / HPH skupiny (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Náhrady / HPH, všechna odvětví (%)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Severovýchod (region soudržnosti: Liberecký kraj, Královéhradecký kraj, Pardubický kraj) – 2020</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>14238</v>
+      </c>
+      <c r="C6" t="n">
+        <v>35275</v>
+      </c>
+      <c r="D6" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>49.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Severovýchod (region soudržnosti: Liberecký kraj, Královéhradecký kraj, Pardubický kraj) – 2021</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>15471</v>
+      </c>
+      <c r="C7" t="n">
+        <v>36783</v>
+      </c>
+      <c r="D7" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Severovýchod (region soudržnosti: Liberecký kraj, Královéhradecký kraj, Pardubický kraj) – 2022</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>16567</v>
+      </c>
+      <c r="C8" t="n">
+        <v>41505</v>
+      </c>
+      <c r="D8" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Severovýchod (region soudržnosti: Liberecký kraj, Královéhradecký kraj, Pardubický kraj) – 2023</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>18255</v>
+      </c>
+      <c r="C9" t="n">
+        <v>45320</v>
+      </c>
+      <c r="D9" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Severovýchod (region soudržnosti: Liberecký kraj, Královéhradecký kraj, Pardubický kraj) – 2024</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>19919</v>
+      </c>
+      <c r="C10" t="n">
+        <v>47385</v>
+      </c>
+      <c r="D10" t="n">
+        <v>42</v>
+      </c>
+      <c r="E10" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Česko – 2020</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>127981</v>
+      </c>
+      <c r="C11" t="n">
+        <v>292311</v>
+      </c>
+      <c r="D11" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Česko – 2021</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>137713</v>
+      </c>
+      <c r="C12" t="n">
+        <v>312154</v>
+      </c>
+      <c r="D12" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Česko – 2022</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>150038</v>
+      </c>
+      <c r="C13" t="n">
+        <v>350966</v>
+      </c>
+      <c r="D13" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Česko – 2023</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>164001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>394052</v>
+      </c>
+      <c r="D14" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>46.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Česko – 2024</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>176048</v>
+      </c>
+      <c r="C15" t="n">
+        <v>409647</v>
+      </c>
+      <c r="D15" t="n">
+        <v>43</v>
+      </c>
+      <c r="E15" t="n">
+        <v>47.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Severozápad (region soudržnosti: Karlovarský kraj, Ústecký kraj) – 2020</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>11759</v>
+      </c>
+      <c r="C16" t="n">
+        <v>25720</v>
+      </c>
+      <c r="D16" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>53.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Severozápad (region soudržnosti: Karlovarský kraj, Ústecký kraj) – 2021</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>12292</v>
+      </c>
+      <c r="C17" t="n">
+        <v>25708</v>
+      </c>
+      <c r="D17" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Severozápad (region soudržnosti: Karlovarský kraj, Ústecký kraj) – 2022</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12719</v>
+      </c>
+      <c r="C18" t="n">
+        <v>27487</v>
+      </c>
+      <c r="D18" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Severozápad (region soudržnosti: Karlovarský kraj, Ústecký kraj) – 2023</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>13610</v>
+      </c>
+      <c r="C19" t="n">
+        <v>30790</v>
+      </c>
+      <c r="D19" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Severozápad (region soudržnosti: Karlovarský kraj, Ústecký kraj) – 2024</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>14888</v>
+      </c>
+      <c r="C20" t="n">
+        <v>32359</v>
+      </c>
+      <c r="D20" t="n">
+        <v>46</v>
+      </c>
+      <c r="E20" t="n">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Nejbližší publikovaná úroveň: region soudržnosti (NUTS 2) – náhrady zaměstnancům Eurostat za kraje nepublikuje. Region zahrnuje více krajů; srovnávací kraj ze stejného regionu má stejné hodnoty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Podíl náhrad zaměstnancům na HPH ukazuje, jaká část přidané hodnoty připadá na mzdy a pojistné zaměstnanců; zbytek tvoří hlavně hrubý provozní přebytek a smíšený důchod (příjem podnikatelů).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2757,7 +3940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3046,571 +4229,6 @@
       <c r="A23" t="inlineStr">
         <is>
           <t>Zdroj: ČSÚ, DataStat, výběry MZDRT5 (ČR a kraje, pracovištní metoda) a MZDRT2 (ČR × sekce) – čtvrtletní zjišťování, kumulace za rok. Hodnoty se od ročního zjišťování mírně liší; obě řady se nespojují.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES, od 2023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Položka</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Počet zaniklých PO</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Poznámka</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026 (do data snímku)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>celkem</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Jen PO: zaniklé FO mají v otevřených datech jen IČO a datum zániku (GDPR). Zaniklé subjekty jsou v RES jen 4 roky po zániku.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Míra zániku právnických osob v oboru (RES, 2023–2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Položka</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Stav PO k 1. 1.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Zaniklé PO za rok</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Míra zániku za rok (%)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Zaniklé PO 1. 1.–15. 9.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Míra zániku 1. 1.–15. 9. (%)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Poznámka</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Liberecký kraj – 2023</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1684</v>
-      </c>
-      <c r="C6" t="n">
-        <v>35</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>část skryta (práh, dopočet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Liberecký kraj – 2024</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1740</v>
-      </c>
-      <c r="C7" t="n">
-        <v>51</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E7" t="n">
-        <v>33</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Liberecký kraj – 2025</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1759</v>
-      </c>
-      <c r="C8" t="n">
-        <v>103</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="E8" t="n">
-        <v>79</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Liberecký kraj – 2026</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1727</v>
-      </c>
-      <c r="E9" t="n">
-        <v>60</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>neúplný rok – jen srovnatelné období</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Česko – 2023</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>51800</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1333</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E10" t="n">
-        <v>927</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Česko – 2024</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>53523</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1387</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E11" t="n">
-        <v>911</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Česko – 2025</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>55375</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1454</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1017</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Česko – 2026</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>57730</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1059</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>neúplný rok – jen srovnatelné období</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Královéhradecký kraj – 2023</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1641</v>
-      </c>
-      <c r="C14" t="n">
-        <v>31</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>část skryta (práh, dopočet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Královéhradecký kraj – 2024</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1680</v>
-      </c>
-      <c r="C15" t="n">
-        <v>29</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>část skryta (práh, dopočet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Královéhradecký kraj – 2025</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1731</v>
-      </c>
-      <c r="C16" t="n">
-        <v>52</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" t="n">
-        <v>34</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Královéhradecký kraj – 2026</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1770</v>
-      </c>
-      <c r="E17" t="n">
-        <v>33</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>neúplný rok – jen srovnatelné období</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Karlovarský kraj – 2023</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>945</v>
-      </c>
-      <c r="C18" t="n">
-        <v>22</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>část skryta (práh, dopočet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Karlovarský kraj – 2024</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>959</v>
-      </c>
-      <c r="C19" t="n">
-        <v>21</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>část skryta (práh, dopočet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Karlovarský kraj – 2025</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>978</v>
-      </c>
-      <c r="C20" t="n">
-        <v>20</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>část skryta (práh, dopočet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Karlovarský kraj – 2026</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1010</v>
-      </c>
-      <c r="E21" t="n">
-        <v>28</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>neúplný rok – jen srovnatelné období</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Pomlčka = skryto: počet pod prahem nebo by z něj šlo dopočítat skrytý počet (zániky ve zbytku roku, vzniky mezi dvěma stavy).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Míra zániku PO = zaniklé PO v roce / stav PO k 1. 1. téhož roku × 100. Stav je rekonstruován ze snímku RES: existující PO se vznikem před 1. 1. + PO zaniklé 1. 1. nebo později.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Rok 2026 je neúplný (snímek k 15. 9. 2026); pro srovnání se proto počítá i srovnatelné období 1. 1.–15. 9. každého roku.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Omezení: jen právnické osoby – zaniklé FO mají v otevřených datech jen IČO a datum zániku. Okno 4 let (2023–2026): RES uchovává zaniklé subjekty jen 4 roky po zániku. Obor a sídlo jsou podle snímku (u zaniklých poslední známé), jejich změny v čase se nepromítají.</t>
         </is>
       </c>
     </row>
@@ -3844,6 +4462,571 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES, od 2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Počet zaniklých PO</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026 (do data snímku)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>celkem</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Jen PO: zaniklé FO mají v otevřených datech jen IČO a datum zániku (GDPR). Zaniklé subjekty jsou v RES jen 4 roky po zániku.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Míra zániku právnických osob v oboru (RES, 2023–2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Stav PO k 1. 1.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Zaniklé PO za rok</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Míra zániku za rok (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Zaniklé PO 1. 1.–15. 9.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Míra zániku 1. 1.–15. 9. (%)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2023</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1684</v>
+      </c>
+      <c r="C6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>část skryta (práh, dopočet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2024</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1740</v>
+      </c>
+      <c r="C7" t="n">
+        <v>51</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E7" t="n">
+        <v>33</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2025</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1759</v>
+      </c>
+      <c r="C8" t="n">
+        <v>103</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="E8" t="n">
+        <v>79</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2026</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1727</v>
+      </c>
+      <c r="E9" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>neúplný rok – jen srovnatelné období</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Česko – 2023</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>51800</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1333</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E10" t="n">
+        <v>927</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Česko – 2024</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>53523</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1387</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E11" t="n">
+        <v>911</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Česko – 2025</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>55375</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1454</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1017</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Česko – 2026</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>57730</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1059</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>neúplný rok – jen srovnatelné období</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2023</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1641</v>
+      </c>
+      <c r="C14" t="n">
+        <v>31</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>část skryta (práh, dopočet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2024</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C15" t="n">
+        <v>29</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>část skryta (práh, dopočet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2025</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1731</v>
+      </c>
+      <c r="C16" t="n">
+        <v>52</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>34</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2026</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1770</v>
+      </c>
+      <c r="E17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>neúplný rok – jen srovnatelné období</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2023</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>945</v>
+      </c>
+      <c r="C18" t="n">
+        <v>22</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>část skryta (práh, dopočet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2024</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>959</v>
+      </c>
+      <c r="C19" t="n">
+        <v>21</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>část skryta (práh, dopočet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2025</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>978</v>
+      </c>
+      <c r="C20" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>část skryta (práh, dopočet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E21" t="n">
+        <v>28</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>neúplný rok – jen srovnatelné období</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pomlčka = skryto: počet pod prahem nebo by z něj šlo dopočítat skrytý počet (zániky ve zbytku roku, vzniky mezi dvěma stavy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Míra zániku PO = zaniklé PO v roce / stav PO k 1. 1. téhož roku × 100. Stav je rekonstruován ze snímku RES: existující PO se vznikem před 1. 1. + PO zaniklé 1. 1. nebo později.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Rok 2026 je neúplný (snímek k 15. 9. 2026); pro srovnání se proto počítá i srovnatelné období 1. 1.–15. 9. každého roku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Omezení: jen právnické osoby – zaniklé FO mají v otevřených datech jen IČO a datum zániku. Okno 4 let (2023–2026): RES uchovává zaniklé subjekty jen 4 roky po zániku. Obor a sídlo jsou podle snímku (u zaniklých poslední známé), jejich změny v čase se nepromítají.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4057,7 +5240,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4411,13 +5594,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -5392,7 +6575,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Průměrná hrubá měsíční mzda v sekci F byla v roce 2022 v Libereckém kraji 33 623 Kč, v Česku 34 840 Kč (relativně o 3,5 % nižší).</t>
+          <t>Objem hrubé přidané hodnoty skupiny Stavebnictví (F) se mezi lety 2020 a 2024 změnil v Libereckém kraji na 89,8 % (rok 2020 = 100), v Česku na 93,1 % (relativně o 3,5 % nižší).</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5402,17 +6585,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mzdy a zaměstnanost</t>
+          <t>ekonomika</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.0349</v>
+        <v>0.0354</v>
       </c>
       <c r="E37" t="n">
-        <v>33623</v>
+        <v>89.8</v>
       </c>
       <c r="F37" t="n">
-        <v>34840</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G37" t="n">
         <v>3.5</v>
@@ -5421,34 +6604,63 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Průměrná hrubá měsíční mzda v sekci F byla v roce 2022 v Libereckém kraji 33 623 Kč, v Česku 34 840 Kč (relativně o 3,5 % nižší).</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Z33</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>mzdy a zaměstnanost</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.0349</v>
+      </c>
+      <c r="E38" t="n">
+        <v>33623</v>
+      </c>
+      <c r="F38" t="n">
+        <v>34840</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Velikost PO – „10–49 zaměstnanců“: podíl na PO oboru je v Libereckém kraji 9,5 %, v Česku 9,2 % (relativně o 3,3 % vyšší).</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Z33</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Z34</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>odchylka od ČR</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D39" t="n">
         <v>0.0326</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E39" t="n">
         <v>9.5</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F39" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G39" t="n">
         <v>3.3</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Síla = |hodnota / srovnání − 1|; u divergence pořadí |p1 − p2| / (počet území − 1). Rozdíly pod 3 % relativně se nehlásí. Položky struktury s podílem pod 5 % v území i v ČR se nehlásí. Popisy jsou věcné, bez interpretace.</t>
         </is>
@@ -5459,13 +6671,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8555,8 +9767,635 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EKON_HPH</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Hrubá přidaná hodnota skupiny odvětví (mil. Kč, běžné ceny)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Hrubá přidaná hodnota v základních cenách ve skupině odvětví A*10, do níž patří obor, v kraji, regionu soudržnosti nebo ČR.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>převzato (Eurostat nama_10r_3gva, unit CP_MNAC), zaokrouhleno na celé mil. Kč</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Eurostat, regionální účty (nama_10r_3gva)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Jen skupiny A*10 (oddíl a nižší úrovně → skupina s označením; B, D, E → B–E; G, H, I → G–I; M, N → M–N; O–Q; R–U); okresy neexistují (→ kraj s označením).</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota podle místa pracoviště jednotek, ne podle sídla subjektu.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
     <row r="56">
       <c r="A56" t="inlineStr">
+        <is>
+          <t>EKON_HPH_PODIL_UZEMI</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Podíl skupiny odvětví na HPH území (%)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HPH skupiny / HPH všech odvětví téhož území a roku × 100.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>100 × EKON_HPH / HPH TOTAL</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Váha oboru v ekonomice území; srovnání kraje s ČR ukazuje specializaci podle přidané hodnoty.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EKON_HPH_PODIL_CR</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Podíl kraje na HPH skupiny odvětví v ČR (%)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>HPH skupiny v kraji / HPH skupiny v ČR × 100.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>100 × EKON_HPH(kraj) / EKON_HPH(ČR)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>kraj</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Srovnávejte s podílem kraje na registrovaných subjektech oboru (REG_PODIL_CR).</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>EKON_HPH_RUST</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Objemová změna HPH proti předchozímu roku (%)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>HPH v cenách předchozího roku / HPH v běžných cenách předchozího roku − 1, × 100.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>100 × (HPH_PYP(t) / HPH_CP(t−1) − 1)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (nama_10r_3gva, unit PYP_MNAC a CP_MNAC)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Reálná (objemová) změna bez vlivu cen.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EKON_HPH_OBJEM_INDEX</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Objem HPH (první rok tabulky = 100)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Řetězení meziročních objemových změn HPH od prvního roku tabulky.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>100 × Π (HPH_PYP(t) / HPH_CP(t−1))</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány všechny roky.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Reálný vývoj za celé období tabulky.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EKON_ZAM</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Zaměstnaní ve skupině odvětví (tis. osob, národní účty)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Zaměstnanost podle národních účtů – zaměstnanci i sebezaměstnaní (včetně podnikajících fyzických osob), podle místa pracoviště.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>převzato (Eurostat nama_10r_3empers, wstatus EMP)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Eurostat, regionální účty (nama_10r_3empers)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Jako EKON_HPH.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Liší se od přepočtených zaměstnanců ČSÚ (MZDY_ZAM_OBOR) – zahrnuje sebezaměstnané a počítá osoby, ne plné úvazky.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EKON_ZAM_PODIL_SELF</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Podíl sebezaměstnaných na zaměstnaných (%)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Sebezaměstnaní / zaměstnaní celkem × 100 (národní účty).</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>100 × ZAM_SELF / ZAM_EMP</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (nama_10r_3empers)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Váha samostatně podnikajících v pracovní síle oboru.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>EKON_PRODUKTIVITA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hrubá přidaná hodnota na zaměstnaného (tis. Kč)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>HPH v běžných cenách / zaměstnaní (obojí Eurostat, regionální účty), zaokrouhleno na celé tis. Kč.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>EKON_HPH / EKON_ZAM (mil. Kč / tis. osob = tis. Kč)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (nama_10r_3gva, nama_10r_3empers)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Nominální produktivita na osobu (ne na odpracovanou hodinu).</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EKON_PRODUKTIVITA_INDEX_CR</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Produktivita proti ČR (ČR = 100)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Produktivita skupiny v kraji / produktivita skupiny v ČR × 100.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>100 × EKON_PRODUKTIVITA(kraj) / EKON_PRODUKTIVITA(ČR)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>kraj</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány všechny údaje.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Pod 100 = nižší přidaná hodnota na zaměstnaného než v oboru v ČR.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>EKON_NAHRADY</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Náhrady zaměstnancům ve skupině odvětví (mil. Kč)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Mzdy a platy a sociální příspěvky zaměstnavatelů ve skupině A*10, region soudržnosti nebo ČR.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>převzato (Eurostat nama_10r_2coe, currency MIO_NAC)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Eurostat, regionální účty (nama_10r_2coe)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>CR, region soudržnosti</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Za kraje Eurostat nepublikuje – uvádí se region soudržnosti (NUTS 2) s označením.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Region zahrnuje více krajů.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EKON_NAHRADY_PODIL</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Podíl náhrad zaměstnancům na HPH (%)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Náhrady zaměstnancům / HPH v běžných cenách × 100, týž region a rok.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>100 × EKON_NAHRADY / EKON_HPH (NUTS 2)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (nama_10r_2coe, nama_10r_3gva)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>CR, region soudržnosti</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Jen region soudržnosti a ČR.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Nízký podíl = větší část přidané hodnoty připadá na provozní přebytek a příjmy podnikatelů.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Pravidla ochrany malých buněk: buňky pod prahem se v každém členění slučují do „ostatní“; je-li „ostatní“ pod prahem, přidá se další nejmenší buňka; skryté číslo nesmí jít dopočítat ze součtů ani z jiné tabulky (ověřeno kontrolou dopočtu). Podrobnosti: docs/report_metodika.md.</t>
         </is>
@@ -8567,13 +10406,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8703,24 +10542,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Povinnost</t>
+          <t>Další zdroj</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Upravené nebo odvozené údaje musí být označeny jako odvozené a nesmí být prezentovány jako nezměněné oficiální statistiky ČSÚ.</t>
+          <t>Eurostat, regionální účty: nama_10r_3gva, nama_10r_3empers, nama_10r_2coe (https://ec.europa.eu/eurostat/databrowser/view/&lt;kód sady&gt;/default/table), staženo 2026-10-01; upraveno (výběr, podíly, poměry, řetězení objemových změn) – za úpravy Eurostat neodpovídá.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Povinnost</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Upravené nebo odvozené údaje musí být označeny jako odvozené a nesmí být prezentovány jako nezměněné oficiální statistiky ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Vygenerováno</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-10-01T11:29:41+00:00</t>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-01T19:50:39+00:00</t>
         </is>
       </c>
     </row>

--- a/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
+++ b/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
@@ -5684,7 +5684,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Z01</t>
+          <t>ZTR-IMTV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Z02</t>
+          <t>ZTR-CISP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Z03</t>
+          <t>ZTR-LQXC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Z04</t>
+          <t>ZTR-YGEL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Z05</t>
+          <t>ZPO-QDHA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Z06</t>
+          <t>ZUZ-EGWN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Z07</t>
+          <t>ZOD-SXHQ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Z08</t>
+          <t>ZOD-SRRX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Z09</t>
+          <t>ZOD-CAID</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Z10</t>
+          <t>ZUZ-OWLP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Z11</t>
+          <t>ZOD-PUOD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Z12</t>
+          <t>ZOD-YZQO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Z13</t>
+          <t>ZUZ-ADGK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Z14</t>
+          <t>ZMZ-ULLF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Z15</t>
+          <t>ZUZ-DHYT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Z16</t>
+          <t>ZUZ-OXBR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Z17</t>
+          <t>ZOD-TOQY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Z18</t>
+          <t>ZOD-NDPG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Z19</t>
+          <t>ZUZ-CLRE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Z20</t>
+          <t>ZUZ-HFUA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Z21</t>
+          <t>ZOD-DWBZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Z22</t>
+          <t>ZTR-RMDL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Z23</t>
+          <t>ZOD-SMOT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Z24</t>
+          <t>ZOD-KHDN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Z25</t>
+          <t>ZMZ-TZVU</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Z26</t>
+          <t>ZAK-CUQD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Z27</t>
+          <t>ZOD-DKSF</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Z28</t>
+          <t>ZOD-YNST</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Z29</t>
+          <t>ZUZ-LRXD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Z30</t>
+          <t>ZMZ-MXTD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Z31</t>
+          <t>ZOD-DHJV</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Z32</t>
+          <t>ZEK-YCEY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Z33</t>
+          <t>ZMZ-KWKY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Z34</t>
+          <t>ZOD-JLNI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-01T19:50:39+00:00</t>
+          <t>2026-10-01T20:14:34+00:00</t>
         </is>
       </c>
     </row>

--- a/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
+++ b/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
@@ -10571,7 +10571,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-01T20:14:34+00:00</t>
+          <t>2026-10-01T20:21:56+00:00</t>
         </is>
       </c>
     </row>

--- a/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
+++ b/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
@@ -24,15 +24,19 @@
     <sheet name="T17_bench_vekova_struktura" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="T22_ekonomika" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="T23_nahrady" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="T20_mzdy_obor" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="T21_mzdy_aktualni" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="T10_zaniky_po" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="T18_mira_zaniku_po" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="T11_dynamika_csu" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="T12_demografie_cr" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="T19_zjisteni" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Metodika" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Zdroj a licence" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="T24_model_velikost" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="T25_model_koncentrace" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="T26_sbs_cr" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="T27_model_kontrola" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="T20_mzdy_obor" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="T21_mzdy_aktualni" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="T10_zaniky_po" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="T18_mira_zaniku_po" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="T11_dynamika_csu" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="T12_demografie_cr" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="T19_zjisteni" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Metodika" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Zdroj a licence" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -788,82 +792,130 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T20_mzdy_obor</t>
+          <t>T24_model_velikost</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Zaměstnanci a průměrné mzdy v oboru – kraje a ČR (ČSÚ, roční zjišťování)</t>
+          <t>Modelový odhad: přidaná hodnota a obrat oboru podle velikosti subjektů – Liberecký kraj, 2024</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>T21_mzdy_aktualni</t>
+          <t>T25_model_koncentrace</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zaměstnanci a průměrné mzdy – novější roky v nejbližších publikovaných úrovních (ČSÚ, čtvrtletní zjišťování)</t>
+          <t>Modelový odhad: koncentrace – podíl subjektů s 10+ a 50+ zaměstnanými osobami – Liberecký kraj, 2024</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>T10_zaniky_po</t>
+          <t>T26_sbs_cr</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES, od 2023)</t>
+          <t>Statistika podniků za ČR podle velikosti: typický obrat a marže (fakt za ČR, Eurostat SBS) – sekce F, 2024</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>T18_mira_zaniku_po</t>
+          <t>T27_model_kontrola</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Míra zániku právnických osob v oboru (RES, 2023–2026)</t>
+          <t>Kontrola konzistence: model použitý na celou ČR proti statistice podniků (SBS) – sekce F, 2024</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>T11_dynamika_csu</t>
+          <t>T20_mzdy_obor</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
+          <t>Zaměstnanci a průměrné mzdy v oboru – kraje a ČR (ČSÚ, roční zjišťování)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>T12_demografie_cr</t>
+          <t>T21_mzdy_aktualni</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+          <t>Zaměstnanci a průměrné mzdy – novější roky v nejbližších publikovaných úrovních (ČSÚ, čtvrtletní zjišťování)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>T10_zaniky_po</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES, od 2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T18_mira_zaniku_po</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Míra zániku právnických osob v oboru (RES, 2023–2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T11_dynamika_csu</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T12_demografie_cr</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>T19_zjisteni</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Zjištění detektoru (seřazeno podle síly)</t>
         </is>
@@ -3348,7 +3400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3364,7 +3416,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zaměstnanci a průměrné mzdy v oboru – kraje a ČR (ČSÚ, roční zjišťování)</t>
+          <t>Modelový odhad: přidaná hodnota a obrat oboru podle velikosti subjektů – Liberecký kraj, 2024</t>
         </is>
       </c>
     </row>
@@ -3390,32 +3442,32 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Zaměstnanci v oboru (tis., přepočtené)</t>
+          <t>Přidaná hodnota – dolní mez (mil. Kč)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Podíl na zaměstnancích oboru v ČR (%)</t>
+          <t>Přidaná hodnota – horní mez (mil. Kč)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Podíl oboru na zaměstnancích území (%)</t>
+          <t>Podíl na přidané hodnotě – dolní (%)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Průměrná mzda v oboru (Kč)</t>
+          <t>Podíl na přidané hodnotě – horní (%)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Mzda proti oboru v ČR (ČR = 100)</t>
+          <t>Obrat – dolní mez (mil. Kč)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Mzda proti všem odvětvím území (= 100)</t>
+          <t>Obrat – horní mez (mil. Kč)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -3427,511 +3479,178 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Liberecký kraj – 2018</t>
+          <t>0–9 osob</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>6124</v>
       </c>
       <c r="C6" t="n">
-        <v>2.89</v>
+        <v>7996</v>
       </c>
       <c r="D6" t="n">
-        <v>4.07</v>
+        <v>48.6</v>
       </c>
       <c r="E6" t="n">
-        <v>27419</v>
+        <v>63.5</v>
       </c>
       <c r="F6" t="n">
-        <v>96.90000000000001</v>
+        <v>25342</v>
       </c>
       <c r="G6" t="n">
-        <v>91.59999999999999</v>
+        <v>33088</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Liberecký kraj – 2019</t>
+          <t>10–19 osob</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.2</v>
+        <v>1061</v>
       </c>
       <c r="C7" t="n">
-        <v>2.96</v>
+        <v>1493</v>
       </c>
       <c r="D7" t="n">
-        <v>4.23</v>
+        <v>8.4</v>
       </c>
       <c r="E7" t="n">
-        <v>29459</v>
+        <v>11.9</v>
       </c>
       <c r="F7" t="n">
-        <v>97.59999999999999</v>
+        <v>4615</v>
       </c>
       <c r="G7" t="n">
-        <v>91.2</v>
+        <v>6497</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Liberecký kraj – 2020</t>
+          <t>20–49 osob</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.3</v>
+        <v>1434</v>
       </c>
       <c r="C8" t="n">
-        <v>3.01</v>
+        <v>2017</v>
       </c>
       <c r="D8" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="E8" t="n">
-        <v>30489</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>97</v>
+        <v>5961</v>
       </c>
       <c r="G8" t="n">
-        <v>91.90000000000001</v>
+        <v>8386</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Liberecký kraj – 2021</t>
+          <t>50 a více osob</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.4</v>
+        <v>2108</v>
       </c>
       <c r="C9" t="n">
-        <v>2.99</v>
+        <v>2965</v>
       </c>
       <c r="D9" t="n">
-        <v>4.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="n">
-        <v>31437</v>
+        <v>23.5</v>
       </c>
       <c r="F9" t="n">
-        <v>96.5</v>
+        <v>9543</v>
       </c>
       <c r="G9" t="n">
-        <v>90.8</v>
+        <v>13419</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Liberecký kraj – 2022</t>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>celkem (Liberecký kraj)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.4</v>
+        <v>12598</v>
       </c>
       <c r="C10" t="n">
-        <v>2.98</v>
+        <v>12598</v>
       </c>
       <c r="D10" t="n">
-        <v>4.44</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>33623</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>96.5</v>
+        <v>53207</v>
       </c>
       <c r="G10" t="n">
-        <v>91.5</v>
+        <v>53644</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>předběžné hodnoty</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Česko – 2018</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>207.9</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>28298</v>
-      </c>
-      <c r="G11" t="n">
-        <v>88.2</v>
+          <t>přidaná hodnota celkem = fakt (Eurostat); obrat = modelový odhad</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Česko – 2019</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>209.8</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="E12" t="n">
-        <v>30187</v>
-      </c>
-      <c r="G12" t="n">
-        <v>87.2</v>
+          <t>Modelový odhad, ne statistika. Přidaná hodnota skupiny v kraji (Eurostat, regionální účty) je rozpočítána mezi velikostní třídy podle počtu subjektů oboru v kraji (RES, KATPO, zúženo na podíl se zjištěnou aktivitou podle ČSÚ) a celostátní přidané hodnoty na podnik třídy (Eurostat SBS); obrat = přidaná hodnota třídy × celostátní poměr obrat / přidaná hodnota v třídě. Pásmo: „Neuvedeno“ v KATPO do nejmenší třídy (FO i PO), nebo poměrně podle známé struktury FO, resp. PO.</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Česko – 2020</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>209.3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="E13" t="n">
-        <v>31444</v>
-      </c>
-      <c r="G13" t="n">
-        <v>86.90000000000001</v>
+          <t>Rok: ekonomika (regionální účty a SBS) 2024; struktura subjektů z RES ke dni snímku. Spojení různých let je součástí modelu.</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Česko – 2021</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>214.2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="E14" t="n">
-        <v>32582</v>
-      </c>
-      <c r="G14" t="n">
-        <v>85.09999999999999</v>
+          <t>KATPO udává počet zaměstnanců, třídy SBS počet zaměstnaných osob včetně majitelů – na hranicích tříd se mohou lišit. Třídy pod prahem 10 subjektů jsou sloučeny s vyšší třídou.</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Česko – 2022</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>214.9</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="E15" t="n">
-        <v>34840</v>
-      </c>
-      <c r="G15" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>předběžné hodnoty</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Královéhradecký kraj – 2018</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E16" t="n">
-        <v>26064</v>
-      </c>
-      <c r="F16" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="G16" t="n">
-        <v>87.2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Královéhradecký kraj – 2019</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="D17" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="E17" t="n">
-        <v>28413</v>
-      </c>
-      <c r="F17" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="G17" t="n">
-        <v>87.40000000000001</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Královéhradecký kraj – 2020</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E18" t="n">
-        <v>29419</v>
-      </c>
-      <c r="F18" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="G18" t="n">
-        <v>86.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Královéhradecký kraj – 2021</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="E19" t="n">
-        <v>30779</v>
-      </c>
-      <c r="F19" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>85.40000000000001</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Královéhradecký kraj – 2022</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="E20" t="n">
-        <v>33274</v>
-      </c>
-      <c r="F20" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>předběžné hodnoty</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Karlovarský kraj – 2018</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="D21" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="E21" t="n">
-        <v>24923</v>
-      </c>
-      <c r="F21" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="G21" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Karlovarský kraj – 2019</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="D22" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="E22" t="n">
-        <v>27237</v>
-      </c>
-      <c r="F22" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="G22" t="n">
-        <v>90.2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Karlovarský kraj – 2020</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="C23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="D23" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="E23" t="n">
-        <v>28492</v>
-      </c>
-      <c r="F23" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="G23" t="n">
-        <v>91.3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Karlovarský kraj – 2021</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>4</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="D24" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="E24" t="n">
-        <v>29271</v>
-      </c>
-      <c r="F24" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="G24" t="n">
-        <v>88.09999999999999</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Karlovarský kraj – 2022</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="D25" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="E25" t="n">
-        <v>31502</v>
-      </c>
-      <c r="F25" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="G25" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>předběžné hodnoty</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Zdroj: ČSÚ, DataStat, výběry MZDCRRT2 (kraje × sekce CZ-NACE) a MZDCRRT1 (ČR × sekce) – roční zjišťování, pracovištní metoda (kraj podle místa pracoviště). ČSÚ je publikuje za roky 2010–2022.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Zaměstnanci = průměrný evidenční počet zaměstnanců přepočtený na plný úvazek; mzda = průměrná hrubá měsíční mzda na přepočtené počty. Nezahrnuje podnikající fyzické osoby bez pracovního poměru, proto se nesrovnává s počty registrovaných subjektů.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Průměr, ne medián: medián mezd ČSÚ za kraje publikuje jen podle pohlaví a bez členění podle odvětví.</t>
+          <t>Obrat vychází z přidané hodnoty národních účtů, která je vyšší než přidaná hodnota SBS (zahrnuje i neregistrovanou ekonomiku a jiné ocenění); model proto obrat nadhodnocuje – viz kontrola konzistence.</t>
         </is>
       </c>
     </row>
@@ -3946,19 +3665,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zaměstnanci a průměrné mzdy – novější roky v nejbližších publikovaných úrovních (ČSÚ, čtvrtletní zjišťování)</t>
+          <t>Modelový odhad: koncentrace – podíl subjektů s 10+ a 50+ zaměstnanými osobami – Liberecký kraj, 2024</t>
         </is>
       </c>
     </row>
@@ -3984,15 +3705,25 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Zaměstnanci (tis., přepočtené)</t>
+          <t>Podíl na přidané hodnotě – dolní (%)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Průměrná mzda (Kč)</t>
+          <t>Podíl na přidané hodnotě – horní (%)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Podíl na obratu – dolní (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Podíl na obratu – horní (%)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Poznámka</t>
         </is>
@@ -4001,234 +3732,69 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Liberecký kraj – všechna odvětví – 2023</t>
+          <t>Subjekty s 10 a více osob</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>143.3</v>
+        <v>36.5</v>
       </c>
       <c r="C6" t="n">
-        <v>38599</v>
+        <v>51.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Liberecký kraj – všechna odvětví – 2024</t>
+          <t>Subjekty s 50 a více osob</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>146.2</v>
+        <v>16.7</v>
       </c>
       <c r="C7" t="n">
-        <v>41450</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Liberecký kraj – všechna odvětví – 2025</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>148.6</v>
-      </c>
-      <c r="C8" t="n">
-        <v>44006</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>předběžné hodnoty</t>
+        <v>23.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Královéhradecký kraj – všechna odvětví – 2023</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>197.4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>39788</v>
+          <t>Modelový odhad, ne statistika. Přidaná hodnota skupiny v kraji (Eurostat, regionální účty) je rozpočítána mezi velikostní třídy podle počtu subjektů oboru v kraji (RES, KATPO, zúženo na podíl se zjištěnou aktivitou podle ČSÚ) a celostátní přidané hodnoty na podnik třídy (Eurostat SBS); obrat = přidaná hodnota třídy × celostátní poměr obrat / přidaná hodnota v třídě. Pásmo: „Neuvedeno“ v KATPO do nejmenší třídy (FO i PO), nebo poměrně podle známé struktury FO, resp. PO.</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Královéhradecký kraj – všechna odvětví – 2024</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>196.7</v>
-      </c>
-      <c r="C10" t="n">
-        <v>42122</v>
+          <t>Rok: ekonomika (regionální účty a SBS) 2024; struktura subjektů z RES ke dni snímku. Spojení různých let je součástí modelu.</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Královéhradecký kraj – všechna odvětví – 2025</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>197.5</v>
-      </c>
-      <c r="C11" t="n">
-        <v>44862</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>předběžné hodnoty</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Karlovarský kraj – všechna odvětví – 2023</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="C12" t="n">
-        <v>37041</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Karlovarský kraj – všechna odvětví – 2024</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="C13" t="n">
-        <v>39257</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Karlovarský kraj – všechna odvětví – 2025</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="C14" t="n">
-        <v>41903</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>předběžné hodnoty</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Česko – všechna odvětví – 2023</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>4047.6</v>
-      </c>
-      <c r="C15" t="n">
-        <v>42801</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Česko – všechna odvětví – 2024</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>4048.6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>45643</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Česko – všechna odvětví – 2025</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>4034.5</v>
-      </c>
-      <c r="C17" t="n">
-        <v>48670</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>předběžné hodnoty</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Česko – sekce F – 2023</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>217.4</v>
-      </c>
-      <c r="C18" t="n">
-        <v>36084</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Česko – sekce F – 2024</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>217.5</v>
-      </c>
-      <c r="C19" t="n">
-        <v>39153</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Česko – sekce F – 2025</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>216.8</v>
-      </c>
-      <c r="C20" t="n">
-        <v>42337</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>předběžné hodnoty</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Obor × kraj ČSÚ za roky po 2022 nepublikuje: roční zjišťování podle krajů a sekcí končí rokem 2022 a čtvrtletní zjišťování kombinaci kraj × odvětví nepublikuje. Uvádějí se proto nejbližší publikované úrovně: kraje za všechna odvětví a ČR za sekci F.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Zdroj: ČSÚ, DataStat, výběry MZDRT5 (ČR a kraje, pracovištní metoda) a MZDRT2 (ČR × sekce) – čtvrtletní zjišťování, kumulace za rok. Hodnoty se od ročního zjišťování mírně liší; obě řady se nespojují.</t>
+          <t>Koncentrace podle velikostních tříd, ne podle jednotlivých subjektů; podíl největších firem by vyžadoval účetní závěrky (Sbírka listin).</t>
         </is>
       </c>
     </row>
@@ -4462,6 +4028,1416 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Statistika podniků za ČR podle velikosti: typický obrat a marže (fakt za ČR, Eurostat SBS) – sekce F, 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Podniky</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Zaměstnané osoby</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Obrat na podnik (mil. Kč)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Obrat na podnik, oddíly – min. (mil. Kč)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Obrat na podnik, oddíly – max. (mil. Kč)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Hrubý provozní přebytek / obrat (%)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0–9 osob</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>202896</v>
+      </c>
+      <c r="C6" t="n">
+        <v>243996</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="G6" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10–19 osob</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2966</v>
+      </c>
+      <c r="C7" t="n">
+        <v>40604</v>
+      </c>
+      <c r="D7" t="n">
+        <v>44.78</v>
+      </c>
+      <c r="E7" t="n">
+        <v>38.16</v>
+      </c>
+      <c r="F7" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20–49 osob</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1646</v>
+      </c>
+      <c r="C8" t="n">
+        <v>47573</v>
+      </c>
+      <c r="D8" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>89.51000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>127.79</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>50–249 osob</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>510</v>
+      </c>
+      <c r="C9" t="n">
+        <v>47016</v>
+      </c>
+      <c r="D9" t="n">
+        <v>461.61</v>
+      </c>
+      <c r="E9" t="n">
+        <v>334.36</v>
+      </c>
+      <c r="F9" t="n">
+        <v>576.66</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>250 a více osob</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>52</v>
+      </c>
+      <c r="C10" t="n">
+        <v>33544</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4647.87</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1135.11</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5450.62</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>celkem</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>208070</v>
+      </c>
+      <c r="C11" t="n">
+        <v>412733</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>186.89</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fakt za ČR, ne odhad za kraj. Zdroj: Eurostat, sbs_sc_ovw (podniky, zaměstnané osoby, čistý obrat, hrubý provozní přebytek; mil. EUR převedeno ročním průměrným kurzem 25,12 Kč/EUR, ert_bil_eur_a). Rok 2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Obrat na podnik je průměr třídy (ne medián); pásmo min.–max. ukazuje rozdíly mezi oddíly (41, 42, 43). Podniky SBS jsou aktivní podniky, ne registrované subjekty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Peněžní údaje SBS jsou jen za třídy 0–9, 10–19, 20–49, 50–249 a 250+; rozdělení 0–1 a 2–9 osob Eurostat publikuje jen u počtů.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kontrola konzistence: model použitý na celou ČR proti statistice podniků (SBS) – sekce F, 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Model – dolní</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Model – horní</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>SBS (fakt)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Vzdálenost faktu od pásma (p. b. nebo %)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Podíl třídy 0–9 osob na přidané hodnotě (%)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>fakt SBS uvnitř pásma</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Podíl třídy 10–19 osob na přidané hodnotě (%)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>fakt SBS uvnitř pásma</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Podíl třídy 20–49 osob na přidané hodnotě (%)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>fakt SBS uvnitř pásma</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Podíl třídy 50–249 osob na přidané hodnotě (%)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>fakt SBS uvnitř pásma</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Podíl třídy 250 a více osob na přidané hodnotě (%)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>fakt SBS uvnitř pásma</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Obrat sekce celkem (mil. Kč)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1762447</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1783878</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1299398</v>
+      </c>
+      <c r="E11" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>model nadhodnocuje (% od bližší meze)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota sekce celkem (mil. Kč)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>409647</v>
+      </c>
+      <c r="C12" t="n">
+        <v>409647</v>
+      </c>
+      <c r="D12" t="n">
+        <v>300901</v>
+      </c>
+      <c r="E12" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>vstup modelu (národní účty) proti SBS, rozdíl v %; příčina nadhodnocení obratu</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Model se stejnými vstupy, ale za celou ČR (RES ČR, podíl se zjištěnou aktivitou za ČR, přidaná hodnota sekce v ČR z regionálních účtů), porovnaný s celostátními hodnotami SBS. Odchylky ukazují, jak přesný model je i tam, kde fakt známe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rok: ekonomika (regionální účty a SBS) 2024; struktura subjektů z RES ke dni snímku. Spojení různých let je součástí modelu.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Zaměstnanci a průměrné mzdy v oboru – kraje a ČR (ČSÚ, roční zjišťování)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Zaměstnanci v oboru (tis., přepočtené)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Podíl na zaměstnancích oboru v ČR (%)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Podíl oboru na zaměstnancích území (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Průměrná mzda v oboru (Kč)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Mzda proti oboru v ČR (ČR = 100)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Mzda proti všem odvětvím území (= 100)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2018</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>27419</v>
+      </c>
+      <c r="F6" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>91.59999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2019</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="E7" t="n">
+        <v>29459</v>
+      </c>
+      <c r="F7" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>91.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2020</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>30489</v>
+      </c>
+      <c r="F8" t="n">
+        <v>97</v>
+      </c>
+      <c r="G8" t="n">
+        <v>91.90000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2021</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>31437</v>
+      </c>
+      <c r="F9" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>90.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – 2022</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="E10" t="n">
+        <v>33623</v>
+      </c>
+      <c r="F10" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Česko – 2018</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>207.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>28298</v>
+      </c>
+      <c r="G11" t="n">
+        <v>88.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Česko – 2019</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="E12" t="n">
+        <v>30187</v>
+      </c>
+      <c r="G12" t="n">
+        <v>87.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Česko – 2020</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>209.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="E13" t="n">
+        <v>31444</v>
+      </c>
+      <c r="G13" t="n">
+        <v>86.90000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Česko – 2021</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="E14" t="n">
+        <v>32582</v>
+      </c>
+      <c r="G14" t="n">
+        <v>85.09999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Česko – 2022</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>214.9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="E15" t="n">
+        <v>34840</v>
+      </c>
+      <c r="G15" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2018</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E16" t="n">
+        <v>26064</v>
+      </c>
+      <c r="F16" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>87.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2019</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="E17" t="n">
+        <v>28413</v>
+      </c>
+      <c r="F17" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>87.40000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2020</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E18" t="n">
+        <v>29419</v>
+      </c>
+      <c r="F18" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>86.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2021</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="E19" t="n">
+        <v>30779</v>
+      </c>
+      <c r="F19" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>85.40000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – 2022</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="E20" t="n">
+        <v>33274</v>
+      </c>
+      <c r="F20" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2018</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="E21" t="n">
+        <v>24923</v>
+      </c>
+      <c r="F21" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2019</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="E22" t="n">
+        <v>27237</v>
+      </c>
+      <c r="F22" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>90.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2020</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="E23" t="n">
+        <v>28492</v>
+      </c>
+      <c r="F23" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>91.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2021</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="E24" t="n">
+        <v>29271</v>
+      </c>
+      <c r="F24" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>88.09999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – 2022</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="E25" t="n">
+        <v>31502</v>
+      </c>
+      <c r="F25" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Zdroj: ČSÚ, DataStat, výběry MZDCRRT2 (kraje × sekce CZ-NACE) a MZDCRRT1 (ČR × sekce) – roční zjišťování, pracovištní metoda (kraj podle místa pracoviště). ČSÚ je publikuje za roky 2010–2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Zaměstnanci = průměrný evidenční počet zaměstnanců přepočtený na plný úvazek; mzda = průměrná hrubá měsíční mzda na přepočtené počty. Nezahrnuje podnikající fyzické osoby bez pracovního poměru, proto se nesrovnává s počty registrovaných subjektů.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Průměr, ne medián: medián mezd ČSÚ za kraje publikuje jen podle pohlaví a bez členění podle odvětví.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Zaměstnanci a průměrné mzdy – novější roky v nejbližších publikovaných úrovních (ČSÚ, čtvrtletní zjišťování)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Zaměstnanci (tis., přepočtené)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Průměrná mzda (Kč)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – všechna odvětví – 2023</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>143.3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>38599</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – všechna odvětví – 2024</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>41450</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Liberecký kraj – všechna odvětví – 2025</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>148.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>44006</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – všechna odvětví – 2023</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>197.4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>39788</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – všechna odvětví – 2024</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>196.7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>42122</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Královéhradecký kraj – všechna odvětví – 2025</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>44862</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – všechna odvětví – 2023</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>37041</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – všechna odvětví – 2024</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>39257</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Karlovarský kraj – všechna odvětví – 2025</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>41903</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Česko – všechna odvětví – 2023</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4047.6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>42801</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Česko – všechna odvětví – 2024</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4048.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>45643</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Česko – všechna odvětví – 2025</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4034.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>48670</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Česko – sekce F – 2023</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>217.4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>36084</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Česko – sekce F – 2024</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>39153</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Česko – sekce F – 2025</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>216.8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>42337</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>předběžné hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Obor × kraj ČSÚ za roky po 2022 nepublikuje: roční zjišťování podle krajů a sekcí končí rokem 2022 a čtvrtletní zjišťování kombinaci kraj × odvětví nepublikuje. Uvádějí se proto nejbližší publikované úrovně: kraje za všechna odvětví a ČR za sekci F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Zdroj: ČSÚ, DataStat, výběry MZDRT5 (ČR a kraje, pracovištní metoda) a MZDRT2 (ČR × sekce) – čtvrtletní zjišťování, kumulace za rok. Hodnoty se od ročního zjišťování mírně liší; obě řady se nespojují.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4570,7 +5546,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5021,7 +5997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5240,7 +6216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5594,7 +6570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6671,13 +7647,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10394,184 +11370,523 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MODEL_HPH</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota oboru v kraji podle velikostní třídy (mil. Kč, modelový odhad)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>odhad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Krajská přidaná hodnota skupiny (Eurostat, regionální účty) rozpočítaná mezi třídy podle počtu subjektů (RES, KATPO, podíl se zjištěnou aktivitou podle ČSÚ) × celostátní přidané hodnoty na podnik třídy (Eurostat SBS).</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>HPH_kraj × n(c)·AV(c)/ENT(c) / Σ n·AV/ENT; pásmo podle zařazení KATPO „Neuvedeno“</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>modelový odhad (RES, ČSÚ RES02QT1, Eurostat nama_10r_3gva, sbs_sc_ovw)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Jen obor = celá sekce, která je samostatnou skupinou A*10; třídy pod prahem 10 subjektů sloučeny.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Modelový odhad, ne statistika. Součet tříd = krajský fakt.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>MODEL_HPH_PODIL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Podíl velikostní třídy na přidané hodnotě oboru v kraji (%, modelový odhad)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>odhad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>MODEL_HPH třídy / přidaná hodnota skupiny v kraji × 100.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>100 × MODEL_HPH / EKON_HPH</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Jako MODEL_HPH.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Modelový odhad.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MODEL_OBRAT</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Obrat oboru v kraji (mil. Kč, modelový odhad)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>odhad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MODEL_HPH třídy × celostátní poměr čistého obratu k přidané hodnotě v třídě (SBS).</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Σ MODEL_HPH(c) × NETTUR(c)/AV(c)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Jako MODEL_HPH.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Nadhodnocený – přidaná hodnota národních účtů je vyšší než v SBS (viz MODEL_KONTROLA).</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MODEL_KONCENTRACE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Podíl subjektů s 10+ a 50+ zaměstnanými osobami na přidané hodnotě a obratu (%, modelový odhad)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>odhad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Součet MODEL_HPH, resp. MODEL_OBRAT tříd nad hranicí / celek × 100.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>100 × Σ_{c ≥ hranice} MODEL_HPH(c) / Σ MODEL_HPH</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Nezveřejní se, pokud by hranice rozdělila sloučenou třídu pod prahem.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Koncentrace podle tříd, ne podle jednotlivých subjektů.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MODEL_KONTROLA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Kontrola konzistence modelu na celé ČR</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>odhad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Model se stejnými vstupy za celou ČR proti hodnotám SBS; odchylka v p. b. (podíly) nebo % (obrat).</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>report.tabulky_model</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>modelový odhad a Eurostat SBS</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Ukazuje přesnost modelu tam, kde fakt známe.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SBS_PODNIKY</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Počet podniků v ČR podle velikostní třídy (Eurostat SBS)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Aktivní podniky v sekci za ČR, třída podle počtu zaměstnaných osob.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>převzato (sbs_sc_ovw, ENT_NR)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Eurostat, sbs_sc_ovw</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Podniky, ne registrované subjekty.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SBS_OSOBY</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Zaměstnané osoby v ČR podle velikostní třídy (Eurostat SBS)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Zaměstnané osoby včetně majitelů a spolupracujících osob.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>převzato (sbs_sc_ovw, EMP_NR)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Eurostat, sbs_sc_ovw</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SBS_OBRAT_PODNIK</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Průměrný obrat podniku v ČR podle velikostní třídy (mil. Kč)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Čistý obrat / počet podniků, převedeno ročním průměrným kurzem CZK/EUR; pásmo min.–max. mezi oddíly sekce.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>NETTUR_MEUR / ENT_NR × kurz</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Eurostat, sbs_sc_ovw, ert_bil_eur_a</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Peněžní údaje jen za třídy 0–9, 10–19, 20–49, 50–249, 250+.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Průměr, ne medián; fakt za ČR.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SBS_MARZE</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Hrubý provozní přebytek / obrat v ČR podle velikostní třídy (%)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Hrubý provozní přebytek / čistý obrat × 100, za ČR.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>100 × GOS_MEUR / NETTUR_MEUR</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Eurostat, sbs_sc_ovw</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Fakt za ČR, ne odhad za kraj; hrubý provozní přebytek zahrnuje i odměnu podnikatelů bez zaměstnanců.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>Pravidla ochrany malých buněk: buňky pod prahem se v každém členění slučují do „ostatní“; je-li „ostatní“ pod prahem, přidá se další nejmenší buňka; skryté číslo nesmí jít dopočítat ze součtů ani z jiné tabulky (ověřeno kontrolou dopočtu). Podrobnosti: docs/report_metodika.md.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="140" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Zdroj</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Označení</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Licence</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CC BY 4.0 – https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Datum snímku RES</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Soubor RES</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://opendata.csu.gov.cz/soubory/od/od_org03/res_data.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Další zdroj</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada OBY02A – počet obyvatel k 31. 12. 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Další zdroj</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, výběr RES02QT1 – podíl subjektů se zjištěnou aktivitou, 2026-Q2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Další zdroj</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada RES05 – vznik a zánik ekonomických subjektů</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Další zdroj</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada RESDP00 – demografie podniků (jednotka podnik, jen ČR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Další zdroj</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, výběry MZDCRRT1, MZDCRRT2, MZDRT2, MZDRT5 – zaměstnanci a průměrné hrubé měsíční mzdy</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Další zdroj</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Eurostat, regionální účty: nama_10r_3gva, nama_10r_3empers, nama_10r_2coe (https://ec.europa.eu/eurostat/databrowser/view/&lt;kód sady&gt;/default/table), staženo 2026-10-01; upraveno (výběr, podíly, poměry, řetězení objemových změn) – za úpravy Eurostat neodpovídá.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Povinnost</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Upravené nebo odvozené údaje musí být označeny jako odvozené a nesmí být prezentovány jako nezměněné oficiální statistiky ČSÚ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Vygenerováno</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-10-01T20:21:56+00:00</t>
         </is>
       </c>
     </row>
@@ -10810,6 +12125,192 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="140" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Zdroj</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Označení</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Licence</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CC BY 4.0 – https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Datum snímku RES</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Soubor RES</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://opendata.csu.gov.cz/soubory/od/od_org03/res_data.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Další zdroj</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada OBY02A – počet obyvatel k 31. 12. 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Další zdroj</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, výběr RES02QT1 – podíl subjektů se zjištěnou aktivitou, 2026-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Další zdroj</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada RES05 – vznik a zánik ekonomických subjektů</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Další zdroj</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada RESDP00 – demografie podniků (jednotka podnik, jen ČR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Další zdroj</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, výběry MZDCRRT1, MZDCRRT2, MZDRT2, MZDRT5 – zaměstnanci a průměrné hrubé měsíční mzdy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Další zdroj</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Eurostat, regionální účty: nama_10r_3gva, nama_10r_3empers, nama_10r_2coe (https://ec.europa.eu/eurostat/databrowser/view/&lt;kód sady&gt;/default/table), staženo 2026-10-01; upraveno (výběr, podíly, poměry, řetězení objemových změn) – za úpravy Eurostat neodpovídá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Další zdroj</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Eurostat, statistika podniků podle velikosti (sbs_sc_ovw) a kurz CZK/EUR (ert_bil_eur_a), staženo 2026-10-02; použito pro modelové odhady – upraveno, za úpravy Eurostat neodpovídá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Povinnost</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Upravené nebo odvozené údaje musí být označeny jako odvozené a nesmí být prezentovány jako nezměněné oficiální statistiky ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Vygenerováno</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-02T06:43:18+00:00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
+++ b/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
@@ -24,19 +24,20 @@
     <sheet name="T17_bench_vekova_struktura" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="T22_ekonomika" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="T23_nahrady" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="T24_model_velikost" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="T25_model_koncentrace" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="T26_sbs_cr" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="T27_model_kontrola" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="T20_mzdy_obor" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="T21_mzdy_aktualni" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="T10_zaniky_po" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="T18_mira_zaniku_po" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="T11_dynamika_csu" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="T12_demografie_cr" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="T19_zjisteni" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Metodika" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Zdroj a licence" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="T28_model_prepocet" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="T24_model_velikost" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="T25_model_koncentrace" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="T26_sbs_cr" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="T27_model_kontrola" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="T20_mzdy_obor" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="T21_mzdy_aktualni" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="T10_zaniky_po" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="T18_mira_zaniku_po" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="T11_dynamika_csu" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="T12_demografie_cr" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="T19_zjisteni" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Metodika" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Zdroj a licence" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -449,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -792,130 +793,142 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T24_model_velikost</t>
+          <t>T28_model_prepocet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Modelový odhad: přidaná hodnota a obrat oboru podle velikosti subjektů – Liberecký kraj, 2024</t>
+          <t>Přepočet přidané hodnoty na úroveň statistiky podniků (vstup modelu) – Liberecký kraj, 2024</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>T25_model_koncentrace</t>
+          <t>T24_model_velikost</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Modelový odhad: koncentrace – podíl subjektů s 10+ a 50+ zaměstnanými osobami – Liberecký kraj, 2024</t>
+          <t>Modelový odhad: přidaná hodnota a obrat oboru podle velikosti subjektů – Liberecký kraj, 2024</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>T26_sbs_cr</t>
+          <t>T25_model_koncentrace</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Statistika podniků za ČR podle velikosti: typický obrat a marže (fakt za ČR, Eurostat SBS) – sekce F, 2024</t>
+          <t>Modelový odhad: koncentrace – podíl subjektů s 10+ a 50+ zaměstnanými osobami – Liberecký kraj, 2024</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>T27_model_kontrola</t>
+          <t>T26_sbs_cr</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kontrola konzistence: model použitý na celou ČR proti statistice podniků (SBS) – sekce F, 2024</t>
+          <t>Statistika podniků za ČR podle velikosti: typický obrat a marže (fakt za ČR, Eurostat SBS) – sekce F, 2024</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>T20_mzdy_obor</t>
+          <t>T27_model_kontrola</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zaměstnanci a průměrné mzdy v oboru – kraje a ČR (ČSÚ, roční zjišťování)</t>
+          <t>Kontrola konzistence: model použitý na celou ČR proti statistice podniků (SBS) – sekce F, 2024</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>T21_mzdy_aktualni</t>
+          <t>T20_mzdy_obor</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zaměstnanci a průměrné mzdy – novější roky v nejbližších publikovaných úrovních (ČSÚ, čtvrtletní zjišťování)</t>
+          <t>Zaměstnanci a průměrné mzdy v oboru – kraje a ČR (ČSÚ, roční zjišťování)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>T10_zaniky_po</t>
+          <t>T21_mzdy_aktualni</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES, od 2023)</t>
+          <t>Zaměstnanci a průměrné mzdy – novější roky v nejbližších publikovaných úrovních (ČSÚ, čtvrtletní zjišťování)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>T18_mira_zaniku_po</t>
+          <t>T10_zaniky_po</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Míra zániku právnických osob v oboru (RES, 2023–2026)</t>
+          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES, od 2023)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>T11_dynamika_csu</t>
+          <t>T18_mira_zaniku_po</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
+          <t>Míra zániku právnických osob v oboru (RES, 2023–2026)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>T12_demografie_cr</t>
+          <t>T11_dynamika_csu</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>T12_demografie_cr</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>T19_zjisteni</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Zjištění detektoru (seřazeno podle síly)</t>
         </is>
@@ -3400,6 +3413,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Přepočet přidané hodnoty na úroveň statistiky podniků (vstup modelu) – Liberecký kraj, 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hodnota</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota oboru – Liberecký kraj, národní účty (fakt, Eurostat, mil. Kč)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12598</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota oboru – Česko, národní účty (fakt, Eurostat, mil. Kč)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>409647</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota oboru – Česko, statistika podniků SBS (fakt, Eurostat, mil. Kč)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>300901</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Poměr SBS / národní účty za ČR</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.7345</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota oboru – Liberecký kraj, přepočtená na úroveň SBS (vstup modelu, mil. Kč)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9254</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota národních účtů (regionální účty, kapitola Ekonomický profil) zahrnuje i neregistrovanou ekonomiku a oceňuje jinak než statistika podniků (SBS), z níž model bere poměry obratu. Před výpočtem obratu se proto krajská přidaná hodnota přepočte poměrem SBS / národní účty za ČR pro týž obor a rok (rozhodnutí 14).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Předpoklad: podíl neregistrované ekonomiky a rozdílů v ocenění je v kraji stejný jako v ČR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota SBS převedena z mil. EUR ročním průměrným kurzem 25,12 Kč/EUR (Eurostat ert_bil_eur_a). Rok 2024.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3442,12 +3588,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Přidaná hodnota – dolní mez (mil. Kč)</t>
+          <t>Přidaná hodnota na úrovni SBS – dolní (mil. Kč)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Přidaná hodnota – horní mez (mil. Kč)</t>
+          <t>Přidaná hodnota na úrovni SBS – horní (mil. Kč)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -3483,10 +3629,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6124</v>
+        <v>4498</v>
       </c>
       <c r="C6" t="n">
-        <v>7996</v>
+        <v>5873</v>
       </c>
       <c r="D6" t="n">
         <v>48.6</v>
@@ -3495,10 +3641,10 @@
         <v>63.5</v>
       </c>
       <c r="F6" t="n">
-        <v>25342</v>
+        <v>18615</v>
       </c>
       <c r="G6" t="n">
-        <v>33088</v>
+        <v>24304</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -3513,10 +3659,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1061</v>
+        <v>779</v>
       </c>
       <c r="C7" t="n">
-        <v>1493</v>
+        <v>1097</v>
       </c>
       <c r="D7" t="n">
         <v>8.4</v>
@@ -3525,10 +3671,10 @@
         <v>11.9</v>
       </c>
       <c r="F7" t="n">
-        <v>4615</v>
+        <v>3390</v>
       </c>
       <c r="G7" t="n">
-        <v>6497</v>
+        <v>4773</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3543,10 +3689,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1434</v>
+        <v>1053</v>
       </c>
       <c r="C8" t="n">
-        <v>2017</v>
+        <v>1481</v>
       </c>
       <c r="D8" t="n">
         <v>11.4</v>
@@ -3555,10 +3701,10 @@
         <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>5961</v>
+        <v>4379</v>
       </c>
       <c r="G8" t="n">
-        <v>8386</v>
+        <v>6160</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3573,10 +3719,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2108</v>
+        <v>1549</v>
       </c>
       <c r="C9" t="n">
-        <v>2965</v>
+        <v>2178</v>
       </c>
       <c r="D9" t="n">
         <v>16.7</v>
@@ -3585,10 +3731,10 @@
         <v>23.5</v>
       </c>
       <c r="F9" t="n">
-        <v>9543</v>
+        <v>7009</v>
       </c>
       <c r="G9" t="n">
-        <v>13419</v>
+        <v>9856</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3603,10 +3749,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12598</v>
+        <v>9254</v>
       </c>
       <c r="C10" t="n">
-        <v>12598</v>
+        <v>9254</v>
       </c>
       <c r="D10" t="n">
         <v>100</v>
@@ -3615,21 +3761,21 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>53207</v>
+        <v>39083</v>
       </c>
       <c r="G10" t="n">
-        <v>53644</v>
+        <v>39403</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>přidaná hodnota celkem = fakt (Eurostat); obrat = modelový odhad</t>
+          <t>přidaná hodnota na úrovni SBS (vstup modelu, tab. přepočtu); obrat = modelový odhad</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Modelový odhad, ne statistika. Přidaná hodnota skupiny v kraji (Eurostat, regionální účty) je rozpočítána mezi velikostní třídy podle počtu subjektů oboru v kraji (RES, KATPO, zúženo na podíl se zjištěnou aktivitou podle ČSÚ) a celostátní přidané hodnoty na podnik třídy (Eurostat SBS); obrat = přidaná hodnota třídy × celostátní poměr obrat / přidaná hodnota v třídě. Pásmo: „Neuvedeno“ v KATPO do nejmenší třídy (FO i PO), nebo poměrně podle známé struktury FO, resp. PO.</t>
+          <t>Modelový odhad, ne statistika. Přidaná hodnota skupiny v kraji (Eurostat, regionální účty) je přepočtena na úroveň statistiky podniků (SBS) a rozpočítána mezi velikostní třídy podle počtu subjektů oboru v kraji (RES, KATPO, zúženo na podíl se zjištěnou aktivitou podle ČSÚ) a celostátní přidané hodnoty na podnik třídy (Eurostat SBS); obrat = přidaná hodnota třídy × celostátní poměr obrat / přidaná hodnota v třídě. Pásmo: „Neuvedeno“ v KATPO do nejmenší třídy (FO i PO), nebo poměrně podle známé struktury FO, resp. PO.</t>
         </is>
       </c>
     </row>
@@ -3650,151 +3796,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Obrat vychází z přidané hodnoty národních účtů, která je vyšší než přidaná hodnota SBS (zahrnuje i neregistrovanou ekonomiku a jiné ocenění); model proto obrat nadhodnocuje – viz kontrola konzistence.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Modelový odhad: koncentrace – podíl subjektů s 10+ a 50+ zaměstnanými osobami – Liberecký kraj, 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Položka</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Podíl na přidané hodnotě – dolní (%)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Podíl na přidané hodnotě – horní (%)</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Podíl na obratu – dolní (%)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Podíl na obratu – horní (%)</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Poznámka</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Subjekty s 10 a více osob</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="E6" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>modelový odhad</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Subjekty s 50 a více osob</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="E7" t="n">
-        <v>25</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>modelový odhad</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Modelový odhad, ne statistika. Přidaná hodnota skupiny v kraji (Eurostat, regionální účty) je rozpočítána mezi velikostní třídy podle počtu subjektů oboru v kraji (RES, KATPO, zúženo na podíl se zjištěnou aktivitou podle ČSÚ) a celostátní přidané hodnoty na podnik třídy (Eurostat SBS); obrat = přidaná hodnota třídy × celostátní poměr obrat / přidaná hodnota v třídě. Pásmo: „Neuvedeno“ v KATPO do nejmenší třídy (FO i PO), nebo poměrně podle známé struktury FO, resp. PO.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Rok: ekonomika (regionální účty a SBS) 2024; struktura subjektů z RES ke dni snímku. Spojení různých let je součástí modelu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Koncentrace podle velikostních tříd, ne podle jednotlivých subjektů; podíl největších firem by vyžadoval účetní závěrky (Sbírka listin).</t>
+          <t>Přidaná hodnota v této tabulce je na úrovni SBS: krajská přidaná hodnota z národních účtů (12598 mil. Kč, fakt) × poměr SBS / národní účty za ČR. Předpoklad: podíl neregistrované ekonomiky a rozdílů v ocenění je v kraji stejný jako v ČR. Podíly tříd se přepočtem nemění (jde jen o měřítko).</t>
         </is>
       </c>
     </row>
@@ -4028,6 +4030,150 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Modelový odhad: koncentrace – podíl subjektů s 10+ a 50+ zaměstnanými osobami – Liberecký kraj, 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Podíl na přidané hodnotě – dolní (%)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Podíl na přidané hodnotě – horní (%)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Podíl na obratu – dolní (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Podíl na obratu – horní (%)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Subjekty s 10 a více osob</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Subjekty s 50 a více osob</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Modelový odhad, ne statistika. Přidaná hodnota skupiny v kraji (Eurostat, regionální účty) je přepočtena na úroveň statistiky podniků (SBS) a rozpočítána mezi velikostní třídy podle počtu subjektů oboru v kraji (RES, KATPO, zúženo na podíl se zjištěnou aktivitou podle ČSÚ) a celostátní přidané hodnoty na podnik třídy (Eurostat SBS); obrat = přidaná hodnota třídy × celostátní poměr obrat / přidaná hodnota v třídě. Pásmo: „Neuvedeno“ v KATPO do nejmenší třídy (FO i PO), nebo poměrně podle známé struktury FO, resp. PO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rok: ekonomika (regionální účty a SBS) 2024; struktura subjektů z RES ke dni snímku. Spojení různých let je součástí modelu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Koncentrace podle velikostních tříd, ne podle jednotlivých subjektů; podíl největších firem by vyžadoval účetní závěrky (Sbírka listin).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4280,7 +4426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4477,44 +4623,44 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1762447</v>
+        <v>1294582</v>
       </c>
       <c r="C11" t="n">
-        <v>1783878</v>
+        <v>1310324</v>
       </c>
       <c r="D11" t="n">
         <v>1299398</v>
       </c>
       <c r="E11" t="n">
-        <v>35.6</v>
+        <v>0.84</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>model nadhodnocuje (% od bližší meze)</t>
+          <t>kritérium splněno: SBS v pásmu, obě meze do ±1 % (větší odchylka v %)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Přidaná hodnota sekce celkem (mil. Kč)</t>
+          <t>Přidaná hodnota sekce celkem, vstup modelu po přepočtu (mil. Kč)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>409647</v>
+        <v>300901</v>
       </c>
       <c r="C12" t="n">
-        <v>409647</v>
+        <v>300901</v>
       </c>
       <c r="D12" t="n">
         <v>300901</v>
       </c>
       <c r="E12" t="n">
-        <v>36.1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>vstup modelu (národní účty) proti SBS, rozdíl v %; příčina nadhodnocení obratu</t>
+          <t>přepočet na úroveň SBS (odchylka v %)</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4683,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5135,7 +5281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5432,7 +5578,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5546,7 +5692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5997,7 +6143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6216,7 +6362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6570,7 +6716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7639,4254 +7785,6 @@
       <c r="A41" t="inlineStr">
         <is>
           <t>Síla = |hodnota / srovnání − 1|; u divergence pořadí |p1 − p2| / (počet území − 1). Rozdíly pod 3 % relativně se nehlásí. Položky struktury s podílem pod 5 % v území i v ČR se nehlásí. Popisy jsou věcné, bez interpretace.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K76"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Kód</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Název</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Typ</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Definice</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Vzorec</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Zdroj</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Úroveň</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Ošetření chybějících hodnot</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Poznámka k výkladu</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Stav</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Použit v této příloze</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>REG_POCET</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Počet registrovaných subjektů v oboru a území</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Registrované ekonomické subjekty bez data zániku s převažující činností v oboru a sídlem v území.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>count(subjekt) where ddatzan is null and nace ∈ obor and okres/kraj(sídlo) ∈ území</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data (res_data.csv), snímek k datu</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Subjekty bez NACE sekce (pseudokód 00) a subjekty zařazené jen do vyšší úrovně klasifikace se do oboru nepočítají, uvádějí se zvlášť (DOPL_OBOR_NEURCEN, DOPL_JEN_VYSSI). Zaniklé subjekty se nepočítají.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Jde o registrované subjekty; podle ČSÚ má zjištěnou aktivitu (daně, pojistné) jen asi 60 % z nich (AKTIVNI_PODIL_KRAJ).</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REG_POCET_CR</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Počet registrovaných subjektů v oboru v ČR</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>REG_POCET za celou ČR.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>count(subjekt) where ddatzan is null and nace ∈ obor</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>jako REG_POCET</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Jmenovatel podílu území na ČR.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REG_PODIL_CR</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Podíl území na registrovaných subjektech oboru v ČR (%)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Kolik procent registrovaných subjektů oboru v ČR má sídlo v území.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>100 × REG_POCET(území) / REG_POCET_CR</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>kraj, okres</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Srovnávejte s podílem území na všech subjektech (viz LQ).</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REG_POCET_VSE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Počet všech registrovaných subjektů v území</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Registrované subjekty bez data zániku se sídlem v území, všechny obory včetně pseudokódu 00.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>count(subjekt) where ddatzan is null and sídlo ∈ území</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Jmenovatel podílu oboru v území a lokalizačního koeficientu.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REG_PODIL_OBOR</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Podíl oboru na registrovaných subjektech území (%)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Kolik procent všech registrovaných subjektů území má převažující činnost v oboru.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>100 × REG_POCET / REG_POCET_VSE</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Jmenovatel obsahuje i subjekty s pseudokódem 00 (obor neurčen), shodně v čitateli ČR i území.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LQ</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Lokalizační koeficient</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Podíl oboru na subjektech území dělený podílem oboru na subjektech ČR.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>(REG_POCET / REG_POCET_VSE) / (REG_POCET_CR / REG_POCET_VSE(ČR))</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>kraj, okres</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>&gt;1 = obor je v území zastoupen víc než v průměru ČR. Počítá registrované subjekty, ne zaměstnanost ani výkon.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>OBYVATELE</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Počet obyvatel území</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Počet obyvatel k 31. 12. posledního zveřejněného roku.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>převzato</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada OBY02A (ukazatel 2406K2)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Praha nemá okres v datech obyvatelstva; okres Praha (CZ0100) = kraj Hlavní město Praha.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Rok stavu obyvatel se liší od data snímku RES.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HUSTOTA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Registrované subjekty oboru na 1 000 obyvatel</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Počet registrovaných subjektů oboru na 1 000 obyvatel území.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1000 × REG_POCET / OBYVATELE</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>odvozeno z RES a ČSÚ OBY02A</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sídlo subjektu nemusí být místem činnosti; v Praze je hustota zvýšena sídly bez činnosti v Praze.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PORADI_POCET</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Pořadí podle počtu registrovaných subjektů oboru</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>poradi</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Pořadí kraje mezi 14 kraji (u okresu mezi okresy téhož kraje) podle REG_POCET, 1 = nejvíce.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>rank() over (order by REG_POCET desc)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>kraj, okres</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Pořadí se počítá ze skutečných počtů všech území; zveřejní se jen u zveřejněných počtů.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Automaticky se srovnává jen s ČR a pořadím mezi všemi kraji; srovnávací kraje volí člověk.</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PORADI_HUSTOTA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pořadí podle hustoty na 1 000 obyvatel</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>poradi</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Pořadí kraje mezi 14 kraji (u okresu mezi okresy téhož kraje) podle HUSTOTA, 1 = nejvyšší.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>rank() over (order by HUSTOTA desc)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>odvozeno z RES a ČSÚ OBY02A</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>kraj, okres</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>jako PORADI_POCET</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Odstraňuje vliv velikosti území.</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>FOPO_POCET</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Registrované subjekty podle typu osoby (FO/PO)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>FO = statistická právní forma (FORMA) 101–108, 424, 425 (podnikající fyzické osoby včetně zahraničních); PO = ostatní formy.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>count(subjekt) group by FO/PO</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data; vymezení FO podle metodiky ČSÚ (statistiky z RES)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Je-li FO nebo PO pod prahem, rozdělení se nezveřejní (a s ním ani velikostní profily FO/PO).</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>FO jsou většinou OSVČ; název subjektu je u nich jméno osoby.</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>FOPO_PODIL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Podíl FO/PO (%)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Podíl FO resp. PO na REG_POCET.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>100 × FOPO_POCET / REG_POCET</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>jako FOPO_POCET</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>FORMA_POCET</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Registrované subjekty podle právní formy</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Počet podle statistické právní formy (FORMA, číselník ČSÚ 56).</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>count(subjekt) group by forma</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data; číselník 56</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Formy pod prahem se slučují do „ostatní formy FO“ / „ostatní formy PO“ (v rámci skupiny); je-li skryté rozdělení FO/PO, do jednoho „ostatní“.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>FORMA_PODIL</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Podíl právní formy (%)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Podíl na REG_POCET.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>100 × FORMA_POCET / REG_POCET</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>jako FORMA_POCET</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>VEL_FO_POCET</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Velikostní profil FO – počet podle kategorie zaměstnanců</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>FO podle KATPO (číselník 579) seskupené do pásem: bez zaměstnanců (110), 1–9 (120, 130), 10–49 (210–230), 50–249 (240–320), 250 a více (330–510), Neuvedeno (000).</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>count(subjekt FO) group by pásmo(KATPO)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data; číselník 579</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>„Neuvedeno“ (000) je vždy samostatný řádek, nikdy se neslučuje s „bez zaměstnanců“; pásma pod prahem se slučují do „ostatní“.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>U FO znamená 110 bez zaměstnanců; od 7/2024 se do zaměstnanců počítají i DPP.</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>VEL_FO_PODIL</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Velikostní profil FO – podíl (%)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Podíl pásma na FO celkem; podíl „Neuvedeno“ se zobrazuje vždy (je-li zveřejnitelný).</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>100 × VEL_FO_POCET / FOPO_POCET(FO)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>jako VEL_FO_POCET</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>VEL_PO_POCET</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Velikostní profil PO – počet podle kategorie zaměstnanců</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>PO podle KATPO v týchž pásmech jako VEL_FO_POCET.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>count(subjekt PO) group by pásmo(KATPO)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data; číselník 579</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>jako VEL_FO_POCET</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>U PO se kód 110 prakticky nepoužívá; PO bez hlášených zaměstnanců mají „Neuvedeno“ (000). Neuvedeno ≠ bez zaměstnanců.</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>VEL_PO_PODIL</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Velikostní profil PO – podíl (%)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Podíl pásma na PO celkem.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>100 × VEL_PO_POCET / FOPO_POCET(PO)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>jako VEL_PO_POCET</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>VEK_PRUMER</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Průměrný věk existujících subjektů (roky)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>prumer</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Průměr (datum snímku − datum vzniku) v letech u registrovaných subjektů oboru v území.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>avg((datum_snimku − ddatvzn) / 365.25)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Věková struktura existujících subjektů, ne dynamika vzniku (zaniklé subjekty nejsou zahrnuty).</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>VEK_MEDIAN</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Mediánový věk existujících subjektů (roky)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>prumer</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Medián (datum snímku − datum vzniku) v letech.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>percentile_cont(0.5)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>jako VEK_PRUMER</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>jako VEK_PRUMER</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>VEK_PASMO_POCET</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Věková struktura existujících subjektů – počet v pásmu</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Pásma věku: méně než 3 roky, 3–5, 6–10, 11–20, 21–30, 31 a více let.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>count(subjekt) group by pásmo(věk)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Pásma pod prahem se slučují do „ostatní“.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Není to počet vzniků v jednotlivých letech.</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>VEK_PASMO_PODIL</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Věková struktura existujících subjektů – podíl pásma (%)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Podíl pásma na REG_POCET.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>100 × VEK_PASMO_POCET / REG_POCET</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>jako VEK_PASMO_POCET</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>DOPL_JEN_VYSSI</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Zařazeno jen do vyšší úrovně klasifikace (např. „zařazeno jen do sekce“)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Registrované subjekty v území, jejichž NACE je nadřazený kód zkoumaného oboru (např. jen „J“ u oddílu 62) – do oboru mohou, ale nemusí patřit.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>count(subjekt) where nace ∈ předci(obor)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Samostatné číslo; pod prahem se nezveřejní. Jen pro obor na úrovni oddílu a nižší.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Horní mez nejistoty počtu v oboru.</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>ne</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>DOPL_OBOR_NEURCEN</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Obor neurčen (pseudokód 00)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Registrované subjekty v území s pseudokódem 00 („výroba, obchod a služby neuvedené v přílohách 1 až 3 živnostenského zákona“).</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>count(subjekt) where nace = '00'</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Samostatné číslo; pod prahem se nezveřejní.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Tyto subjekty nejde přiřadit žádnému oboru; ČSÚ je vykazuje jako „X Nezjištěno“.</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AKTIVNI_PODIL_KRAJ</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Podíl subjektů se zjištěnou aktivitou v kraji podle ČSÚ (%, všechny obory)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Počet ekonomických subjektů se zjištěnou aktivitou / počet ekonomických subjektů celkem, kraj (u okresu jeho kraj), všechny obory, poslední čtvrtletí.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>100 × 4958_akt / 4958_reg (RES02QT1, NACE celkem)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, výběr RES02QT1</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Za okres ČSÚ podíl v členění podle převažující činnosti nepublikuje; uvádí se krajský.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Jen kontext. Aktivitu po subjektech nedopočítáváme; počty v reportu jsou registrované subjekty.</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AKTIVNI_PODIL_SEKCE_KRAJ</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Podíl subjektů se zjištěnou aktivitou v sekci a kraji podle ČSÚ (%)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Jako AKTIVNI_PODIL_KRAJ, ale jen pro sekci CZ-NACE zkoumaného oboru.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>100 × 4958_akt / 4958_reg (RES02QT1, sekce)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, výběr RES02QT1</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Jen je-li obor přesně jedna sekce, kterou ČSÚ publikuje samostatně (ne B, C, D, E – ty jen jako B–E); jinak nelze naplnit.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Jen kontext.</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ZANIK_PO_RES</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>PO s datem zániku od 1. 1. 2023 do data snímku, s převažující činností v oboru a sídlem v území.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>count(subjekt PO) where ddatzan &gt;= 2023-01-01 group by year(ddatzan)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Zaniklé FO mají v otevřených datech jen IČO a datum zániku (GDPR) – do oboru ani území je přiřadit nelze. Zaniklé více než 4 roky v RES nejsou; proto jen od roku 2023. Poslední rok je neúplný.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Jen PO. Míru zániku (normalizovanou stavem PO) uvádí MIRA_ZANIKU_PO.</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>DYN_VZNIK_CSU</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Vzniklé ekonomické subjekty v území podle ČSÚ (všechny obory)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Počet vzniklých ekonomických subjektů v roce (součet čtvrtletí), FO a PO, území celkem.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>sum(4962) over čtvrtletí roku (RES05)</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada RES05</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>ČSÚ vznik a zánik v členění podle oboru (kraj × sekce ani ČR × obor) z RES nepublikuje – dynamiku oboru nelze naplnit. Poslední rok je neúplný (jen zveřejněná čtvrtletí).</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Dynamika celého území, ne oboru.</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>DYN_ZANIK_CSU</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Zaniklé ekonomické subjekty v území podle ČSÚ (všechny obory)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Počet zaniklých ekonomických subjektů v roce (součet čtvrtletí), FO a PO, území celkem.</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>sum(4963) over čtvrtletí roku (RES05)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada RES05</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>jako DYN_VZNIK_CSU. Rok 2023 u FO obsahuje mimořádný výkyv (1. čtvrtletí 2023 hromadný zánik FO, v ČR 200 977 zániků FO proti obvyklým 15–45 tis.).</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Dynamika celého území, ne oboru.</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>DYN_OBOR_CSU</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Vznik a zánik subjektů v oboru a území podle ČSÚ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Počet vzniklých a zaniklých subjektů v oboru × kraji.</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ČSÚ DataStat – tabulka v tomto členění neexistuje (RES05 jen území × FO/PO; RES06 registrace a RESDP00 demografie podniků jen za ČR podle odvětví)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Nelze naplnit.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Mimo v0 (rozhodnutí 10) – vznikne později z archivu snímků RES. Náhradou je dynamika území (RES05), kontext ČR z demografie podniků (RESDP00), ZANIK_PO_RES a věková struktura.</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>nelze naplnit</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>ne</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>SPOLEHLIVOST_JEN_SEKCE</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Spolehlivost zařazení – subjekty zařazené jen do sekce vůči počtu oboru (%)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Registrované subjekty v území s převažující činností uvedenou jen písmenem sekce oboru (např. „J“ u oddílu 62) děleno počtem oboru v území (rozhodnutí 9).</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>100 × DOPL_JEN_VYSSI(sekce) / REG_POCET</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Jen pro obor na úrovni oddílu a nižší. Nezveřejní se, je-li počet „jen do sekce“ pod prahem (pak je podíl nutně malý).</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Nad 25 % nese report varování na titulní straně i v metodické poznámce: skutečný počet oboru může být výrazně vyšší.</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>ne</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>DEMOGR_AKTIVNI</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Aktivní podniky v ČR (demografie podniků)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Počet aktivních podniků podle statistiky demografie podniků ČSÚ, FO a PO zvlášť, odvětví oboru a všechna odvětví.</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>převzato (RESDP00, ukazatel 6594_RESDP)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada RESDP00</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Odvětví jen B–R (K = peněžní zprostředkování, S = osobní služby); A, O, T, U v RESDP00 nejsou. Poslední rok bývá předběžný.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Jiná jednotka (aktivní podnik), nesrovnatelné s registrovanými subjekty RES; jen kontext za ČR (rozhodnutí 10).</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>DEMOGR_MIRA_VZNIKU</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Míra vzniků podniků v ČR (%)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Vzniklé podniky / aktivní podniky × 100 podle ČSÚ, FO a PO zvlášť.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>převzato (RESDP00, ukazatel 9507)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada RESDP00</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>jako DEMOGR_AKTIVNI</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Kontext dynamiky oboru za ČR; dynamika obor × území je mimo v0 (vznikne z archivu snímků RES).</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>DEMOGR_MIRA_ZANIKU</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Míra zániků podniků v ČR (%)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Zaniklé podniky / aktivní podniky × 100 podle ČSÚ, FO a PO zvlášť.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>převzato (RESDP00, ukazatel 9508)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, sada RESDP00</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Zánik se zjišťuje se zpožděním; poslední rok bez zániků se nezobrazuje.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>jako DEMOGR_MIRA_VZNIKU</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>BENCH_PODIL</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Podíl položky struktury – zkoumané území, ČR a srovnávací kraje (%)</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Podíl položky (typ osoby, právní forma, velikostní pásmo, věkové pásmo, „Neuvedeno“) na registrovaných subjektech téhož oboru v daném území.</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>100 × počet(položka, obor, území) / počet(obor, území); u velikosti jmenovatel FO, resp. PO</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Práh a slučování platí pro každé území zvlášť; položky sloučené ve zkoumaném území jsou předem sloučené i v ostatních sloupcích; položka pod prahem v benchmarkovém území je sloučena do „ostatní“ (pomlčka).</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Srovnává strukturu oboru, ne velikost území. Rozdíl menší než 3 % relativně se popisuje jako „srovnatelné“.</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>BENCH_ROZDIL_PB</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Rozdíl podílu zkoumaného území proti ČR (procentní body)</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Podíl položky ve zkoumaném území minus týž podíl v ČR.</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>BENCH_PODIL(území) − BENCH_PODIL(ČR), z hodnot zaokrouhlených na 0,1</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>kraj, okres</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Jen jsou-li zveřejněné oba podíly.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Procentní body, ne procenta; relativní rozdíl uvádí detektor zjištění.</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ZANIK_PO_STAV</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Stav právnických osob v oboru a území k 1. 1. (rekonstruovaný z RES)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>PO s převažující činností v oboru a sídlem v území, které k 1. 1. roku existovaly.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>count(PO bez zániku, ddatvzn &lt; 1. 1. Y) + count(PO zaniklé, ddatvzn &lt; 1. 1. Y, ddatzan &gt;= 1. 1. Y)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data (jeden snímek)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Zaniklé subjekty jsou v RES jen 4 roky po zániku, proto stav lze rekonstruovat jen od 2023. Obor a sídlo podle snímku. Nezveřejní se pod prahem ani tehdy, když by z po sobě jdoucích stavů šel dopočítat počet vzniků pod prahem.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Jmenovatel míry zániku PO.</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ZANIK_PO_OBD</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Zaniklé právnické osoby ve srovnatelném období roku (1. 1.–den snímku)</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>pocet</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>PO v oboru a území s datem zániku od 1. 1. do dne a měsíce snímku téhož roku.</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>count(PO) where 1. 1. Y &lt;= ddatzan &lt;= (Y, měsíc a den snímku)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>ČSÚ, RES – otevřená data</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Nezveřejní se pod prahem ani tehdy, když by šel dopočítat zbytek roku pod prahem.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Umožňuje srovnat neúplný poslední rok s předchozími.</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>MIRA_ZANIKU_PO</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Míra zániku právnických osob v oboru za rok (%)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Zaniklé PO v roce / stav PO k 1. 1. téhož roku × 100.</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>100 × ZANIK_PO_RES(Y) / ZANIK_PO_STAV(Y)</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Jen úplné roky; jen jsou-li oba počty zveřejněné.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Jen PO, okno 4 let. Normalizuje zániky velikostí populace, takže je srovnatelná mezi územími.</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>MIRA_ZANIKU_PO_OBD</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Míra zániku právnických osob ve srovnatelném období (%)</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Zaniklé PO od 1. 1. do dne a měsíce snímku / stav PO k 1. 1. × 100.</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>100 × ZANIK_PO_OBD(Y) / ZANIK_PO_STAV(Y)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>odvozeno z RES</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Jen jsou-li oba počty zveřejněné.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Jediná srovnatelná míra pro neúplný poslední rok.</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ZJ_TYP</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Typ zjištění</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>zjisteni</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Odchylka od ČR, změna trendu, rozdíly uvnitř území, aktivita oboru vůči kraji, divergence pořadí.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>report_zjisteni</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>odvozeno z tabulek reportu</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Popis bez interpretace; „proč“ píše analytik.</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ZJ_SILA</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Síla zjištění</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>zjisteni</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Absolutní relativní rozdíl |a / b − 1| (u divergence pořadí |p1 − p2| / (počet území − 1)).</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>report_zjisteni</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>odvozeno ze zveřejněných čísel tabulek</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Zjištění pod 0,03 (3 %) se nehlásí.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Bezrozměrné číslo, zjištění se podle něj řadí.</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ZJ_HODNOTA</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Hodnota zkoumaného území ve zjištění</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>zjisteni</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Číslo z tabulky reportu, k níž zjištění odkazuje (nebo průměr čísel z ní).</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>report_zjisteni</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>tabulky reportu</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ZJ_SROVNANI</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Srovnávací hodnota ve zjištění</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>zjisteni</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Číslo, s nímž se hodnota srovnává (ČR, kraj, předchozí roky – průměr, druhé pořadí).</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>report_zjisteni</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>tabulky reportu</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>ZJ_ROZDIL_PCT</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Relativní rozdíl (%)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>zjisteni</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Absolutní hodnota 100 × (hodnota / srovnání − 1), zaokrouhleno na 0,1; směr (vyšší / nižší) je ve větě zjištění.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>report_zjisteni</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>odvozeno</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>CR, kraj, okres</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>U divergence pořadí se neuvádí.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Pod 3 % se rozdíl nehlásí a v textu se popisuje jako „srovnatelné“.</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MZDY_ZAM_OBOR</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Zaměstnanci v oboru a kraji (tis. osob, přepočtené počty)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Průměrný evidenční počet zaměstnanců přepočtený na plný úvazek v sekci CZ-NACE oboru a v kraji (pracovištní metoda) nebo v ČR.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>převzato (MZDCRRT2 kraje × sekce, MZDCRRT1 ČR × sekce; ukazatele 299AQ / 299A), zaokrouhleno na 0,1 tis.</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, roční zjišťování (sada MZDCRR)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Jen jednotlivé sekce CZ-NACE (oddíl a nižší úrovně → sekce s označením); okresy ČSÚ nepublikuje (→ kraj s označením); kraj × sekce jen 2010–2022 (2022 předběžně).</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Zaměstnanci v pracovním poměru, ne podnikající fyzické osoby; nesrovnává se s počtem registrovaných subjektů.</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MZDY_ZAM_PODIL_CR</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Podíl kraje na zaměstnancích oboru v ČR (%)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Zaměstnanci oboru v kraji / zaměstnanci oboru v ČR × 100, obojí z ročního zjišťování.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>100 × MZDY_ZAM_OBOR(kraj) / MZDY_ZAM_OBOR(ČR)</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>kraj</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Srovnávejte s podílem kraje na registrovaných subjektech oboru (REG_PODIL_CR).</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MZDY_ZAM_PODIL_UZEMI</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Podíl oboru na zaměstnancích území (%)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Zaměstnanci oboru / zaměstnanci všech odvětví v témže území × 100.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>100 × MZDY_ZAM_OBOR / zaměstnanci celkem (sekce „Celkem“)</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Váha oboru na trhu práce území; srovnání kraje s ČR ukazuje specializaci podle zaměstnanosti.</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>MZDY_MZDA_OBOR</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Průměrná hrubá měsíční mzda v oboru a kraji (Kč)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Průměrná hrubá měsíční mzda na přepočtené počty zaměstnanců v sekci CZ-NACE oboru a v kraji nebo v ČR.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>převzato (MZDCRRT2, MZDCRRT1; ukazatel 5958P), zaokrouhleno na celé Kč</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, roční zjišťování (sada MZDCRR)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Jako MZDY_ZAM_OBOR. Medián za kraj × odvětví ČSÚ nepublikuje (za kraje jen podle pohlaví).</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Průměr je citlivý na vysoké mzdy; medián pro kraj × odvětví není k dispozici.</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>MZDY_MZDA_INDEX_CR</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Mzda v oboru a kraji proti oboru v ČR (ČR = 100)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Průměrná mzda oboru v kraji / průměrná mzda oboru v ČR × 100.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>100 × MZDY_MZDA_OBOR(kraj) / MZDY_MZDA_OBOR(ČR)</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>kraj</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Pod 100 = obor v kraji platí méně než obor v ČR.</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>MZDY_MZDA_INDEX_UZEMI</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Mzda v oboru proti všem odvětvím území (= 100)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Průměrná mzda oboru / průměrná mzda všech odvětví v témže území × 100.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>100 × MZDY_MZDA_OBOR / mzda celkem (sekce „Celkem“)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Postavení oboru mezi odvětvími téhož území.</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>MZDY_ZAM_UROVEN</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Zaměstnanci v nejbližší publikované úrovni (tis. osob, přepočtené počty)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Kraj za všechna odvětví nebo ČR za sekci oboru – pro roky, za které ČSÚ obor × kraj nepublikuje.</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>převzato (MZDRT5, MZDRT2; ukazatel 299A), zaokrouhleno na 0,1 tis.</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, čtvrtletní zjišťování (sada MZDR), kumulace za rok</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kraj × odvětví čtvrtletní zjišťování nepublikuje.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Jiné zjišťování než MZDY_ZAM_OBOR; řady se nespojují.</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MZDY_MZDA_UROVEN</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Průměrná mzda v nejbližší publikované úrovni (Kč)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Kraj za všechna odvětví nebo ČR za sekci oboru – pro roky, za které ČSÚ obor × kraj nepublikuje.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>převzato (MZDRT5, MZDRT2; ukazatel 5958P), zaokrouhleno na celé Kč</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>ČSÚ, DataStat, čtvrtletní zjišťování (sada MZDR), kumulace za rok</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kraj × odvětví čtvrtletní zjišťování nepublikuje.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Jiné zjišťování než MZDY_MZDA_OBOR; řady se nespojují.</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>EKON_HPH</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Hrubá přidaná hodnota skupiny odvětví (mil. Kč, běžné ceny)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Hrubá přidaná hodnota v základních cenách ve skupině odvětví A*10, do níž patří obor, v kraji, regionu soudržnosti nebo ČR.</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>převzato (Eurostat nama_10r_3gva, unit CP_MNAC), zaokrouhleno na celé mil. Kč</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Eurostat, regionální účty (nama_10r_3gva)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Jen skupiny A*10 (oddíl a nižší úrovně → skupina s označením; B, D, E → B–E; G, H, I → G–I; M, N → M–N; O–Q; R–U); okresy neexistují (→ kraj s označením).</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Přidaná hodnota podle místa pracoviště jednotek, ne podle sídla subjektu.</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>EKON_HPH_PODIL_UZEMI</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Podíl skupiny odvětví na HPH území (%)</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>HPH skupiny / HPH všech odvětví téhož území a roku × 100.</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>100 × EKON_HPH / HPH TOTAL</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Váha oboru v ekonomice území; srovnání kraje s ČR ukazuje specializaci podle přidané hodnoty.</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>EKON_HPH_PODIL_CR</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Podíl kraje na HPH skupiny odvětví v ČR (%)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>HPH skupiny v kraji / HPH skupiny v ČR × 100.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>100 × EKON_HPH(kraj) / EKON_HPH(ČR)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>kraj</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Srovnávejte s podílem kraje na registrovaných subjektech oboru (REG_PODIL_CR).</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>EKON_HPH_RUST</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Objemová změna HPH proti předchozímu roku (%)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>HPH v cenách předchozího roku / HPH v běžných cenách předchozího roku − 1, × 100.</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>100 × (HPH_PYP(t) / HPH_CP(t−1) − 1)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>odvozeno z Eurostatu (nama_10r_3gva, unit PYP_MNAC a CP_MNAC)</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Reálná (objemová) změna bez vlivu cen.</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>EKON_HPH_OBJEM_INDEX</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Objem HPH (první rok tabulky = 100)</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Řetězení meziročních objemových změn HPH od prvního roku tabulky.</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>100 × Π (HPH_PYP(t) / HPH_CP(t−1))</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Jen jsou-li publikovány všechny roky.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Reálný vývoj za celé období tabulky.</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>EKON_ZAM</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Zaměstnaní ve skupině odvětví (tis. osob, národní účty)</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Zaměstnanost podle národních účtů – zaměstnanci i sebezaměstnaní (včetně podnikajících fyzických osob), podle místa pracoviště.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>převzato (Eurostat nama_10r_3empers, wstatus EMP)</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Eurostat, regionální účty (nama_10r_3empers)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Jako EKON_HPH.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Liší se od přepočtených zaměstnanců ČSÚ (MZDY_ZAM_OBOR) – zahrnuje sebezaměstnané a počítá osoby, ne plné úvazky.</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>EKON_ZAM_PODIL_SELF</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Podíl sebezaměstnaných na zaměstnaných (%)</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Sebezaměstnaní / zaměstnaní celkem × 100 (národní účty).</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>100 × ZAM_SELF / ZAM_EMP</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>odvozeno z Eurostatu (nama_10r_3empers)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Váha samostatně podnikajících v pracovní síle oboru.</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>EKON_PRODUKTIVITA</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Hrubá přidaná hodnota na zaměstnaného (tis. Kč)</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>HPH v běžných cenách / zaměstnaní (obojí Eurostat, regionální účty), zaokrouhleno na celé tis. Kč.</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>EKON_HPH / EKON_ZAM (mil. Kč / tis. osob = tis. Kč)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>odvozeno z Eurostatu (nama_10r_3gva, nama_10r_3empers)</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Jen jsou-li publikovány oba údaje.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Nominální produktivita na osobu (ne na odpracovanou hodinu).</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>EKON_PRODUKTIVITA_INDEX_CR</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Produktivita proti ČR (ČR = 100)</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Produktivita skupiny v kraji / produktivita skupiny v ČR × 100.</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>100 × EKON_PRODUKTIVITA(kraj) / EKON_PRODUKTIVITA(ČR)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>odvozeno z Eurostatu</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>kraj</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Jen jsou-li publikovány všechny údaje.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Pod 100 = nižší přidaná hodnota na zaměstnaného než v oboru v ČR.</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>EKON_NAHRADY</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Náhrady zaměstnancům ve skupině odvětví (mil. Kč)</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Mzdy a platy a sociální příspěvky zaměstnavatelů ve skupině A*10, region soudržnosti nebo ČR.</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>převzato (Eurostat nama_10r_2coe, currency MIO_NAC)</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Eurostat, regionální účty (nama_10r_2coe)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>CR, region soudržnosti</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Za kraje Eurostat nepublikuje – uvádí se region soudržnosti (NUTS 2) s označením.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Region zahrnuje více krajů.</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>EKON_NAHRADY_PODIL</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Podíl náhrad zaměstnancům na HPH (%)</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>podil</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Náhrady zaměstnancům / HPH v běžných cenách × 100, týž region a rok.</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>100 × EKON_NAHRADY / EKON_HPH (NUTS 2)</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>odvozeno z Eurostatu (nama_10r_2coe, nama_10r_3gva)</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>CR, region soudržnosti</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Jen region soudržnosti a ČR.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Nízký podíl = větší část přidané hodnoty připadá na provozní přebytek a příjmy podnikatelů.</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>MODEL_HPH</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Přidaná hodnota oboru v kraji podle velikostní třídy (mil. Kč, modelový odhad)</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>odhad</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Krajská přidaná hodnota skupiny (Eurostat, regionální účty) rozpočítaná mezi třídy podle počtu subjektů (RES, KATPO, podíl se zjištěnou aktivitou podle ČSÚ) × celostátní přidané hodnoty na podnik třídy (Eurostat SBS).</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>HPH_kraj × n(c)·AV(c)/ENT(c) / Σ n·AV/ENT; pásmo podle zařazení KATPO „Neuvedeno“</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>modelový odhad (RES, ČSÚ RES02QT1, Eurostat nama_10r_3gva, sbs_sc_ovw)</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Jen obor = celá sekce, která je samostatnou skupinou A*10; třídy pod prahem 10 subjektů sloučeny.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Modelový odhad, ne statistika. Součet tříd = krajský fakt.</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>MODEL_HPH_PODIL</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Podíl velikostní třídy na přidané hodnotě oboru v kraji (%, modelový odhad)</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>odhad</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>MODEL_HPH třídy / přidaná hodnota skupiny v kraji × 100.</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>100 × MODEL_HPH / EKON_HPH</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>modelový odhad</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Jako MODEL_HPH.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Modelový odhad.</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>MODEL_OBRAT</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Obrat oboru v kraji (mil. Kč, modelový odhad)</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>odhad</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>MODEL_HPH třídy × celostátní poměr čistého obratu k přidané hodnotě v třídě (SBS).</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Σ MODEL_HPH(c) × NETTUR(c)/AV(c)</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>modelový odhad</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Jako MODEL_HPH.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Nadhodnocený – přidaná hodnota národních účtů je vyšší než v SBS (viz MODEL_KONTROLA).</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>MODEL_KONCENTRACE</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Podíl subjektů s 10+ a 50+ zaměstnanými osobami na přidané hodnotě a obratu (%, modelový odhad)</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>odhad</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Součet MODEL_HPH, resp. MODEL_OBRAT tříd nad hranicí / celek × 100.</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>100 × Σ_{c ≥ hranice} MODEL_HPH(c) / Σ MODEL_HPH</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>modelový odhad</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>CR, kraj</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Nezveřejní se, pokud by hranice rozdělila sloučenou třídu pod prahem.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Koncentrace podle tříd, ne podle jednotlivých subjektů.</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>částečně</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>MODEL_KONTROLA</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Kontrola konzistence modelu na celé ČR</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>odhad</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Model se stejnými vstupy za celou ČR proti hodnotám SBS; odchylka v p. b. (podíly) nebo % (obrat).</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>report.tabulky_model</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>modelový odhad a Eurostat SBS</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Ukazuje přesnost modelu tam, kde fakt známe.</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>SBS_PODNIKY</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Počet podniků v ČR podle velikostní třídy (Eurostat SBS)</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Aktivní podniky v sekci za ČR, třída podle počtu zaměstnaných osob.</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>převzato (sbs_sc_ovw, ENT_NR)</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Eurostat, sbs_sc_ovw</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Podniky, ne registrované subjekty.</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>SBS_OSOBY</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Zaměstnané osoby v ČR podle velikostní třídy (Eurostat SBS)</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Zaměstnané osoby včetně majitelů a spolupracujících osob.</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>převzato (sbs_sc_ovw, EMP_NR)</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Eurostat, sbs_sc_ovw</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>SBS_OBRAT_PODNIK</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Průměrný obrat podniku v ČR podle velikostní třídy (mil. Kč)</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Čistý obrat / počet podniků, převedeno ročním průměrným kurzem CZK/EUR; pásmo min.–max. mezi oddíly sekce.</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>NETTUR_MEUR / ENT_NR × kurz</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Eurostat, sbs_sc_ovw, ert_bil_eur_a</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Peněžní údaje jen za třídy 0–9, 10–19, 20–49, 50–249, 250+.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Průměr, ne medián; fakt za ČR.</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>SBS_MARZE</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Hrubý provozní přebytek / obrat v ČR podle velikostní třídy (%)</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>kontext</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Hrubý provozní přebytek / čistý obrat × 100, za ČR.</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>100 × GOS_MEUR / NETTUR_MEUR</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Eurostat, sbs_sc_ovw</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Fakt za ČR, ne odhad za kraj; hrubý provozní přebytek zahrnuje i odměnu podnikatelů bez zaměstnanců.</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>naplněno</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Pravidla ochrany malých buněk: buňky pod prahem se v každém členění slučují do „ostatní“; je-li „ostatní“ pod prahem, přidá se další nejmenší buňka; skryté číslo nesmí jít dopočítat ze součtů ani z jiné tabulky (ověřeno kontrolou dopočtu). Podrobnosti: docs/report_metodika.md.</t>
         </is>
       </c>
     </row>
@@ -12131,6 +8029,4368 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kód</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Název</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Definice</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Vzorec</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Zdroj</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Úroveň</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Ošetření chybějících hodnot</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Poznámka k výkladu</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Stav</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Použit v této příloze</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REG_POCET</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Počet registrovaných subjektů v oboru a území</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Registrované ekonomické subjekty bez data zániku s převažující činností v oboru a sídlem v území.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>count(subjekt) where ddatzan is null and nace ∈ obor and okres/kraj(sídlo) ∈ území</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data (res_data.csv), snímek k datu</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Subjekty bez NACE sekce (pseudokód 00) a subjekty zařazené jen do vyšší úrovně klasifikace se do oboru nepočítají, uvádějí se zvlášť (DOPL_OBOR_NEURCEN, DOPL_JEN_VYSSI). Zaniklé subjekty se nepočítají.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Jde o registrované subjekty; podle ČSÚ má zjištěnou aktivitu (daně, pojistné) jen asi 60 % z nich (AKTIVNI_PODIL_KRAJ).</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REG_POCET_CR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Počet registrovaných subjektů v oboru v ČR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>REG_POCET za celou ČR.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>count(subjekt) where ddatzan is null and nace ∈ obor</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>jako REG_POCET</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Jmenovatel podílu území na ČR.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REG_PODIL_CR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Podíl území na registrovaných subjektech oboru v ČR (%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kolik procent registrovaných subjektů oboru v ČR má sídlo v území.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>100 × REG_POCET(území) / REG_POCET_CR</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>kraj, okres</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Srovnávejte s podílem území na všech subjektech (viz LQ).</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REG_POCET_VSE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Počet všech registrovaných subjektů v území</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Registrované subjekty bez data zániku se sídlem v území, všechny obory včetně pseudokódu 00.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>count(subjekt) where ddatzan is null and sídlo ∈ území</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Jmenovatel podílu oboru v území a lokalizačního koeficientu.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REG_PODIL_OBOR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Podíl oboru na registrovaných subjektech území (%)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Kolik procent všech registrovaných subjektů území má převažující činnost v oboru.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>100 × REG_POCET / REG_POCET_VSE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Jmenovatel obsahuje i subjekty s pseudokódem 00 (obor neurčen), shodně v čitateli ČR i území.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LQ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lokalizační koeficient</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Podíl oboru na subjektech území dělený podílem oboru na subjektech ČR.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>(REG_POCET / REG_POCET_VSE) / (REG_POCET_CR / REG_POCET_VSE(ČR))</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>kraj, okres</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>&gt;1 = obor je v území zastoupen víc než v průměru ČR. Počítá registrované subjekty, ne zaměstnanost ani výkon.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OBYVATELE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Počet obyvatel území</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Počet obyvatel k 31. 12. posledního zveřejněného roku.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>převzato</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada OBY02A (ukazatel 2406K2)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Praha nemá okres v datech obyvatelstva; okres Praha (CZ0100) = kraj Hlavní město Praha.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Rok stavu obyvatel se liší od data snímku RES.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HUSTOTA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Registrované subjekty oboru na 1 000 obyvatel</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Počet registrovaných subjektů oboru na 1 000 obyvatel území.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1000 × REG_POCET / OBYVATELE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>odvozeno z RES a ČSÚ OBY02A</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sídlo subjektu nemusí být místem činnosti; v Praze je hustota zvýšena sídly bez činnosti v Praze.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PORADI_POCET</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pořadí podle počtu registrovaných subjektů oboru</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>poradi</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pořadí kraje mezi 14 kraji (u okresu mezi okresy téhož kraje) podle REG_POCET, 1 = nejvíce.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>rank() over (order by REG_POCET desc)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>kraj, okres</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pořadí se počítá ze skutečných počtů všech území; zveřejní se jen u zveřejněných počtů.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Automaticky se srovnává jen s ČR a pořadím mezi všemi kraji; srovnávací kraje volí člověk.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PORADI_HUSTOTA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pořadí podle hustoty na 1 000 obyvatel</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>poradi</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Pořadí kraje mezi 14 kraji (u okresu mezi okresy téhož kraje) podle HUSTOTA, 1 = nejvyšší.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>rank() over (order by HUSTOTA desc)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>odvozeno z RES a ČSÚ OBY02A</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>kraj, okres</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>jako PORADI_POCET</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Odstraňuje vliv velikosti území.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FOPO_POCET</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Registrované subjekty podle typu osoby (FO/PO)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FO = statistická právní forma (FORMA) 101–108, 424, 425 (podnikající fyzické osoby včetně zahraničních); PO = ostatní formy.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>count(subjekt) group by FO/PO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data; vymezení FO podle metodiky ČSÚ (statistiky z RES)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Je-li FO nebo PO pod prahem, rozdělení se nezveřejní (a s ním ani velikostní profily FO/PO).</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>FO jsou většinou OSVČ; název subjektu je u nich jméno osoby.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FOPO_PODIL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Podíl FO/PO (%)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Podíl FO resp. PO na REG_POCET.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>100 × FOPO_POCET / REG_POCET</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>jako FOPO_POCET</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FORMA_POCET</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Registrované subjekty podle právní formy</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Počet podle statistické právní formy (FORMA, číselník ČSÚ 56).</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>count(subjekt) group by forma</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data; číselník 56</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Formy pod prahem se slučují do „ostatní formy FO“ / „ostatní formy PO“ (v rámci skupiny); je-li skryté rozdělení FO/PO, do jednoho „ostatní“.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FORMA_PODIL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Podíl právní formy (%)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Podíl na REG_POCET.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>100 × FORMA_POCET / REG_POCET</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>jako FORMA_POCET</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VEL_FO_POCET</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Velikostní profil FO – počet podle kategorie zaměstnanců</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FO podle KATPO (číselník 579) seskupené do pásem: bez zaměstnanců (110), 1–9 (120, 130), 10–49 (210–230), 50–249 (240–320), 250 a více (330–510), Neuvedeno (000).</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>count(subjekt FO) group by pásmo(KATPO)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data; číselník 579</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>„Neuvedeno“ (000) je vždy samostatný řádek, nikdy se neslučuje s „bez zaměstnanců“; pásma pod prahem se slučují do „ostatní“.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>U FO znamená 110 bez zaměstnanců; od 7/2024 se do zaměstnanců počítají i DPP.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>VEL_FO_PODIL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Velikostní profil FO – podíl (%)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Podíl pásma na FO celkem; podíl „Neuvedeno“ se zobrazuje vždy (je-li zveřejnitelný).</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>100 × VEL_FO_POCET / FOPO_POCET(FO)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>jako VEL_FO_POCET</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>VEL_PO_POCET</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Velikostní profil PO – počet podle kategorie zaměstnanců</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PO podle KATPO v týchž pásmech jako VEL_FO_POCET.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>count(subjekt PO) group by pásmo(KATPO)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data; číselník 579</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>jako VEL_FO_POCET</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>U PO se kód 110 prakticky nepoužívá; PO bez hlášených zaměstnanců mají „Neuvedeno“ (000). Neuvedeno ≠ bez zaměstnanců.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>VEL_PO_PODIL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Velikostní profil PO – podíl (%)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Podíl pásma na PO celkem.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>100 × VEL_PO_POCET / FOPO_POCET(PO)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>jako VEL_PO_POCET</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VEK_PRUMER</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Průměrný věk existujících subjektů (roky)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>prumer</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Průměr (datum snímku − datum vzniku) v letech u registrovaných subjektů oboru v území.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>avg((datum_snimku − ddatvzn) / 365.25)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Nezveřejní se, je-li REG_POCET skrytý.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Věková struktura existujících subjektů, ne dynamika vzniku (zaniklé subjekty nejsou zahrnuty).</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VEK_MEDIAN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mediánový věk existujících subjektů (roky)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>prumer</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Medián (datum snímku − datum vzniku) v letech.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>percentile_cont(0.5)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>jako VEK_PRUMER</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>jako VEK_PRUMER</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>VEK_PASMO_POCET</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Věková struktura existujících subjektů – počet v pásmu</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Pásma věku: méně než 3 roky, 3–5, 6–10, 11–20, 21–30, 31 a více let.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>count(subjekt) group by pásmo(věk)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Pásma pod prahem se slučují do „ostatní“.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Není to počet vzniků v jednotlivých letech.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VEK_PASMO_PODIL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Věková struktura existujících subjektů – podíl pásma (%)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Podíl pásma na REG_POCET.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>100 × VEK_PASMO_POCET / REG_POCET</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>jako VEK_PASMO_POCET</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DOPL_JEN_VYSSI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Zařazeno jen do vyšší úrovně klasifikace (např. „zařazeno jen do sekce“)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Registrované subjekty v území, jejichž NACE je nadřazený kód zkoumaného oboru (např. jen „J“ u oddílu 62) – do oboru mohou, ale nemusí patřit.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>count(subjekt) where nace ∈ předci(obor)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Samostatné číslo; pod prahem se nezveřejní. Jen pro obor na úrovni oddílu a nižší.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Horní mez nejistoty počtu v oboru.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DOPL_OBOR_NEURCEN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Obor neurčen (pseudokód 00)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Registrované subjekty v území s pseudokódem 00 („výroba, obchod a služby neuvedené v přílohách 1 až 3 živnostenského zákona“).</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>count(subjekt) where nace = '00'</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Samostatné číslo; pod prahem se nezveřejní.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Tyto subjekty nejde přiřadit žádnému oboru; ČSÚ je vykazuje jako „X Nezjištěno“.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AKTIVNI_PODIL_KRAJ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Podíl subjektů se zjištěnou aktivitou v kraji podle ČSÚ (%, všechny obory)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Počet ekonomických subjektů se zjištěnou aktivitou / počet ekonomických subjektů celkem, kraj (u okresu jeho kraj), všechny obory, poslední čtvrtletí.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>100 × 4958_akt / 4958_reg (RES02QT1, NACE celkem)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, výběr RES02QT1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Za okres ČSÚ podíl v členění podle převažující činnosti nepublikuje; uvádí se krajský.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Jen kontext. Aktivitu po subjektech nedopočítáváme; počty v reportu jsou registrované subjekty.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AKTIVNI_PODIL_SEKCE_KRAJ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Podíl subjektů se zjištěnou aktivitou v sekci a kraji podle ČSÚ (%)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Jako AKTIVNI_PODIL_KRAJ, ale jen pro sekci CZ-NACE zkoumaného oboru.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>100 × 4958_akt / 4958_reg (RES02QT1, sekce)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, výběr RES02QT1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Jen je-li obor přesně jedna sekce, kterou ČSÚ publikuje samostatně (ne B, C, D, E – ty jen jako B–E); jinak nelze naplnit.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Jen kontext.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ZANIK_PO_RES</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PO s datem zániku od 1. 1. 2023 do data snímku, s převažující činností v oboru a sídlem v území.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>count(subjekt PO) where ddatzan &gt;= 2023-01-01 group by year(ddatzan)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Zaniklé FO mají v otevřených datech jen IČO a datum zániku (GDPR) – do oboru ani území je přiřadit nelze. Zaniklé více než 4 roky v RES nejsou; proto jen od roku 2023. Poslední rok je neúplný.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Jen PO. Míru zániku (normalizovanou stavem PO) uvádí MIRA_ZANIKU_PO.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DYN_VZNIK_CSU</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Vzniklé ekonomické subjekty v území podle ČSÚ (všechny obory)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Počet vzniklých ekonomických subjektů v roce (součet čtvrtletí), FO a PO, území celkem.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>sum(4962) over čtvrtletí roku (RES05)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada RES05</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ČSÚ vznik a zánik v členění podle oboru (kraj × sekce ani ČR × obor) z RES nepublikuje – dynamiku oboru nelze naplnit. Poslední rok je neúplný (jen zveřejněná čtvrtletí).</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Dynamika celého území, ne oboru.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DYN_ZANIK_CSU</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Zaniklé ekonomické subjekty v území podle ČSÚ (všechny obory)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Počet zaniklých ekonomických subjektů v roce (součet čtvrtletí), FO a PO, území celkem.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>sum(4963) over čtvrtletí roku (RES05)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada RES05</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>jako DYN_VZNIK_CSU. Rok 2023 u FO obsahuje mimořádný výkyv (1. čtvrtletí 2023 hromadný zánik FO, v ČR 200 977 zániků FO proti obvyklým 15–45 tis.).</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Dynamika celého území, ne oboru.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DYN_OBOR_CSU</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Vznik a zánik subjektů v oboru a území podle ČSÚ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Počet vzniklých a zaniklých subjektů v oboru × kraji.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ČSÚ DataStat – tabulka v tomto členění neexistuje (RES05 jen území × FO/PO; RES06 registrace a RESDP00 demografie podniků jen za ČR podle odvětví)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Nelze naplnit.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Mimo v0 (rozhodnutí 10) – vznikne později z archivu snímků RES. Náhradou je dynamika území (RES05), kontext ČR z demografie podniků (RESDP00), ZANIK_PO_RES a věková struktura.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>nelze naplnit</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SPOLEHLIVOST_JEN_SEKCE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Spolehlivost zařazení – subjekty zařazené jen do sekce vůči počtu oboru (%)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Registrované subjekty v území s převažující činností uvedenou jen písmenem sekce oboru (např. „J“ u oddílu 62) děleno počtem oboru v území (rozhodnutí 9).</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>100 × DOPL_JEN_VYSSI(sekce) / REG_POCET</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Jen pro obor na úrovni oddílu a nižší. Nezveřejní se, je-li počet „jen do sekce“ pod prahem (pak je podíl nutně malý).</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Nad 25 % nese report varování na titulní straně i v metodické poznámce: skutečný počet oboru může být výrazně vyšší.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DEMOGR_AKTIVNI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Aktivní podniky v ČR (demografie podniků)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Počet aktivních podniků podle statistiky demografie podniků ČSÚ, FO a PO zvlášť, odvětví oboru a všechna odvětví.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>převzato (RESDP00, ukazatel 6594_RESDP)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada RESDP00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Odvětví jen B–R (K = peněžní zprostředkování, S = osobní služby); A, O, T, U v RESDP00 nejsou. Poslední rok bývá předběžný.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Jiná jednotka (aktivní podnik), nesrovnatelné s registrovanými subjekty RES; jen kontext za ČR (rozhodnutí 10).</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DEMOGR_MIRA_VZNIKU</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Míra vzniků podniků v ČR (%)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Vzniklé podniky / aktivní podniky × 100 podle ČSÚ, FO a PO zvlášť.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>převzato (RESDP00, ukazatel 9507)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada RESDP00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>jako DEMOGR_AKTIVNI</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Kontext dynamiky oboru za ČR; dynamika obor × území je mimo v0 (vznikne z archivu snímků RES).</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DEMOGR_MIRA_ZANIKU</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Míra zániků podniků v ČR (%)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Zaniklé podniky / aktivní podniky × 100 podle ČSÚ, FO a PO zvlášť.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>převzato (RESDP00, ukazatel 9508)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, sada RESDP00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Zánik se zjišťuje se zpožděním; poslední rok bez zániků se nezobrazuje.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>jako DEMOGR_MIRA_VZNIKU</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BENCH_PODIL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Podíl položky struktury – zkoumané území, ČR a srovnávací kraje (%)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Podíl položky (typ osoby, právní forma, velikostní pásmo, věkové pásmo, „Neuvedeno“) na registrovaných subjektech téhož oboru v daném území.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>100 × počet(položka, obor, území) / počet(obor, území); u velikosti jmenovatel FO, resp. PO</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Práh a slučování platí pro každé území zvlášť; položky sloučené ve zkoumaném území jsou předem sloučené i v ostatních sloupcích; položka pod prahem v benchmarkovém území je sloučena do „ostatní“ (pomlčka).</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Srovnává strukturu oboru, ne velikost území. Rozdíl menší než 3 % relativně se popisuje jako „srovnatelné“.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BENCH_ROZDIL_PB</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rozdíl podílu zkoumaného území proti ČR (procentní body)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Podíl položky ve zkoumaném území minus týž podíl v ČR.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BENCH_PODIL(území) − BENCH_PODIL(ČR), z hodnot zaokrouhlených na 0,1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>kraj, okres</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Jen jsou-li zveřejněné oba podíly.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Procentní body, ne procenta; relativní rozdíl uvádí detektor zjištění.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ZANIK_PO_STAV</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Stav právnických osob v oboru a území k 1. 1. (rekonstruovaný z RES)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PO s převažující činností v oboru a sídlem v území, které k 1. 1. roku existovaly.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>count(PO bez zániku, ddatvzn &lt; 1. 1. Y) + count(PO zaniklé, ddatvzn &lt; 1. 1. Y, ddatzan &gt;= 1. 1. Y)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data (jeden snímek)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Zaniklé subjekty jsou v RES jen 4 roky po zániku, proto stav lze rekonstruovat jen od 2023. Obor a sídlo podle snímku. Nezveřejní se pod prahem ani tehdy, když by z po sobě jdoucích stavů šel dopočítat počet vzniků pod prahem.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Jmenovatel míry zániku PO.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ZANIK_PO_OBD</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Zaniklé právnické osoby ve srovnatelném období roku (1. 1.–den snímku)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>pocet</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PO v oboru a území s datem zániku od 1. 1. do dne a měsíce snímku téhož roku.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>count(PO) where 1. 1. Y &lt;= ddatzan &lt;= (Y, měsíc a den snímku)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ČSÚ, RES – otevřená data</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Nezveřejní se pod prahem ani tehdy, když by šel dopočítat zbytek roku pod prahem.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Umožňuje srovnat neúplný poslední rok s předchozími.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MIRA_ZANIKU_PO</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Míra zániku právnických osob v oboru za rok (%)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Zaniklé PO v roce / stav PO k 1. 1. téhož roku × 100.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>100 × ZANIK_PO_RES(Y) / ZANIK_PO_STAV(Y)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Jen úplné roky; jen jsou-li oba počty zveřejněné.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Jen PO, okno 4 let. Normalizuje zániky velikostí populace, takže je srovnatelná mezi územími.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MIRA_ZANIKU_PO_OBD</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Míra zániku právnických osob ve srovnatelném období (%)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Zaniklé PO od 1. 1. do dne a měsíce snímku / stav PO k 1. 1. × 100.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>100 × ZANIK_PO_OBD(Y) / ZANIK_PO_STAV(Y)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>odvozeno z RES</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Jen jsou-li oba počty zveřejněné.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Jediná srovnatelná míra pro neúplný poslední rok.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ZJ_TYP</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Typ zjištění</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>zjisteni</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Odchylka od ČR, změna trendu, rozdíly uvnitř území, aktivita oboru vůči kraji, divergence pořadí.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>report_zjisteni</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>odvozeno z tabulek reportu</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Popis bez interpretace; „proč“ píše analytik.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ZJ_SILA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Síla zjištění</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>zjisteni</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Absolutní relativní rozdíl |a / b − 1| (u divergence pořadí |p1 − p2| / (počet území − 1)).</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>report_zjisteni</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>odvozeno ze zveřejněných čísel tabulek</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Zjištění pod 0,03 (3 %) se nehlásí.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Bezrozměrné číslo, zjištění se podle něj řadí.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ZJ_HODNOTA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Hodnota zkoumaného území ve zjištění</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>zjisteni</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Číslo z tabulky reportu, k níž zjištění odkazuje (nebo průměr čísel z ní).</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>report_zjisteni</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>tabulky reportu</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ZJ_SROVNANI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Srovnávací hodnota ve zjištění</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>zjisteni</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Číslo, s nímž se hodnota srovnává (ČR, kraj, předchozí roky – průměr, druhé pořadí).</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>report_zjisteni</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>tabulky reportu</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ZJ_ROZDIL_PCT</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Relativní rozdíl (%)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>zjisteni</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Absolutní hodnota 100 × (hodnota / srovnání − 1), zaokrouhleno na 0,1; směr (vyšší / nižší) je ve větě zjištění.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>report_zjisteni</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>odvozeno</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>CR, kraj, okres</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>U divergence pořadí se neuvádí.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Pod 3 % se rozdíl nehlásí a v textu se popisuje jako „srovnatelné“.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MZDY_ZAM_OBOR</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Zaměstnanci v oboru a kraji (tis. osob, přepočtené počty)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Průměrný evidenční počet zaměstnanců přepočtený na plný úvazek v sekci CZ-NACE oboru a v kraji (pracovištní metoda) nebo v ČR.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>převzato (MZDCRRT2 kraje × sekce, MZDCRRT1 ČR × sekce; ukazatele 299AQ / 299A), zaokrouhleno na 0,1 tis.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, roční zjišťování (sada MZDCRR)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Jen jednotlivé sekce CZ-NACE (oddíl a nižší úrovně → sekce s označením); okresy ČSÚ nepublikuje (→ kraj s označením); kraj × sekce jen 2010–2022 (2022 předběžně).</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Zaměstnanci v pracovním poměru, ne podnikající fyzické osoby; nesrovnává se s počtem registrovaných subjektů.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MZDY_ZAM_PODIL_CR</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Podíl kraje na zaměstnancích oboru v ČR (%)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Zaměstnanci oboru v kraji / zaměstnanci oboru v ČR × 100, obojí z ročního zjišťování.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>100 × MZDY_ZAM_OBOR(kraj) / MZDY_ZAM_OBOR(ČR)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>kraj</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Srovnávejte s podílem kraje na registrovaných subjektech oboru (REG_PODIL_CR).</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MZDY_ZAM_PODIL_UZEMI</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Podíl oboru na zaměstnancích území (%)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Zaměstnanci oboru / zaměstnanci všech odvětví v témže území × 100.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>100 × MZDY_ZAM_OBOR / zaměstnanci celkem (sekce „Celkem“)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Váha oboru na trhu práce území; srovnání kraje s ČR ukazuje specializaci podle zaměstnanosti.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MZDY_MZDA_OBOR</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Průměrná hrubá měsíční mzda v oboru a kraji (Kč)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Průměrná hrubá měsíční mzda na přepočtené počty zaměstnanců v sekci CZ-NACE oboru a v kraji nebo v ČR.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>převzato (MZDCRRT2, MZDCRRT1; ukazatel 5958P), zaokrouhleno na celé Kč</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, roční zjišťování (sada MZDCRR)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Jako MZDY_ZAM_OBOR. Medián za kraj × odvětví ČSÚ nepublikuje (za kraje jen podle pohlaví).</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Průměr je citlivý na vysoké mzdy; medián pro kraj × odvětví není k dispozici.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MZDY_MZDA_INDEX_CR</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mzda v oboru a kraji proti oboru v ČR (ČR = 100)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Průměrná mzda oboru v kraji / průměrná mzda oboru v ČR × 100.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>100 × MZDY_MZDA_OBOR(kraj) / MZDY_MZDA_OBOR(ČR)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>kraj</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Pod 100 = obor v kraji platí méně než obor v ČR.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MZDY_MZDA_INDEX_UZEMI</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Mzda v oboru proti všem odvětvím území (= 100)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Průměrná mzda oboru / průměrná mzda všech odvětví v témže území × 100.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>100 × MZDY_MZDA_OBOR / mzda celkem (sekce „Celkem“)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>odvozeno z publikovaných údajů ČSÚ (MZDCRR)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Postavení oboru mezi odvětvími téhož území.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MZDY_ZAM_UROVEN</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Zaměstnanci v nejbližší publikované úrovni (tis. osob, přepočtené počty)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Kraj za všechna odvětví nebo ČR za sekci oboru – pro roky, za které ČSÚ obor × kraj nepublikuje.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>převzato (MZDRT5, MZDRT2; ukazatel 299A), zaokrouhleno na 0,1 tis.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, čtvrtletní zjišťování (sada MZDR), kumulace za rok</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kraj × odvětví čtvrtletní zjišťování nepublikuje.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Jiné zjišťování než MZDY_ZAM_OBOR; řady se nespojují.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MZDY_MZDA_UROVEN</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Průměrná mzda v nejbližší publikované úrovni (Kč)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Kraj za všechna odvětví nebo ČR za sekci oboru – pro roky, za které ČSÚ obor × kraj nepublikuje.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>převzato (MZDRT5, MZDRT2; ukazatel 5958P), zaokrouhleno na celé Kč</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ČSÚ, DataStat, čtvrtletní zjišťování (sada MZDR), kumulace za rok</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kraj × odvětví čtvrtletní zjišťování nepublikuje.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Jiné zjišťování než MZDY_MZDA_OBOR; řady se nespojují.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EKON_HPH</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Hrubá přidaná hodnota skupiny odvětví (mil. Kč, běžné ceny)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Hrubá přidaná hodnota v základních cenách ve skupině odvětví A*10, do níž patří obor, v kraji, regionu soudržnosti nebo ČR.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>převzato (Eurostat nama_10r_3gva, unit CP_MNAC), zaokrouhleno na celé mil. Kč</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Eurostat, regionální účty (nama_10r_3gva)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Jen skupiny A*10 (oddíl a nižší úrovně → skupina s označením; B, D, E → B–E; G, H, I → G–I; M, N → M–N; O–Q; R–U); okresy neexistují (→ kraj s označením).</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota podle místa pracoviště jednotek, ne podle sídla subjektu.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>EKON_HPH_PODIL_UZEMI</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Podíl skupiny odvětví na HPH území (%)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HPH skupiny / HPH všech odvětví téhož území a roku × 100.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>100 × EKON_HPH / HPH TOTAL</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Váha oboru v ekonomice území; srovnání kraje s ČR ukazuje specializaci podle přidané hodnoty.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EKON_HPH_PODIL_CR</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Podíl kraje na HPH skupiny odvětví v ČR (%)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>HPH skupiny v kraji / HPH skupiny v ČR × 100.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>100 × EKON_HPH(kraj) / EKON_HPH(ČR)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>kraj</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Srovnávejte s podílem kraje na registrovaných subjektech oboru (REG_PODIL_CR).</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>EKON_HPH_RUST</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Objemová změna HPH proti předchozímu roku (%)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>HPH v cenách předchozího roku / HPH v běžných cenách předchozího roku − 1, × 100.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>100 × (HPH_PYP(t) / HPH_CP(t−1) − 1)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (nama_10r_3gva, unit PYP_MNAC a CP_MNAC)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Reálná (objemová) změna bez vlivu cen.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EKON_HPH_OBJEM_INDEX</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Objem HPH (první rok tabulky = 100)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Řetězení meziročních objemových změn HPH od prvního roku tabulky.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>100 × Π (HPH_PYP(t) / HPH_CP(t−1))</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (nama_10r_3gva)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány všechny roky.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Reálný vývoj za celé období tabulky.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EKON_ZAM</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Zaměstnaní ve skupině odvětví (tis. osob, národní účty)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Zaměstnanost podle národních účtů – zaměstnanci i sebezaměstnaní (včetně podnikajících fyzických osob), podle místa pracoviště.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>převzato (Eurostat nama_10r_3empers, wstatus EMP)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Eurostat, regionální účty (nama_10r_3empers)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Jako EKON_HPH.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Liší se od přepočtených zaměstnanců ČSÚ (MZDY_ZAM_OBOR) – zahrnuje sebezaměstnané a počítá osoby, ne plné úvazky.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EKON_ZAM_PODIL_SELF</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Podíl sebezaměstnaných na zaměstnaných (%)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Sebezaměstnaní / zaměstnaní celkem × 100 (národní účty).</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>100 × ZAM_SELF / ZAM_EMP</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (nama_10r_3empers)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Váha samostatně podnikajících v pracovní síle oboru.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>EKON_PRODUKTIVITA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hrubá přidaná hodnota na zaměstnaného (tis. Kč)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>HPH v běžných cenách / zaměstnaní (obojí Eurostat, regionální účty), zaokrouhleno na celé tis. Kč.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>EKON_HPH / EKON_ZAM (mil. Kč / tis. osob = tis. Kč)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (nama_10r_3gva, nama_10r_3empers)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány oba údaje.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Nominální produktivita na osobu (ne na odpracovanou hodinu).</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EKON_PRODUKTIVITA_INDEX_CR</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Produktivita proti ČR (ČR = 100)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Produktivita skupiny v kraji / produktivita skupiny v ČR × 100.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>100 × EKON_PRODUKTIVITA(kraj) / EKON_PRODUKTIVITA(ČR)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>kraj</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány všechny údaje.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Pod 100 = nižší přidaná hodnota na zaměstnaného než v oboru v ČR.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>EKON_NAHRADY</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Náhrady zaměstnancům ve skupině odvětví (mil. Kč)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Mzdy a platy a sociální příspěvky zaměstnavatelů ve skupině A*10, region soudržnosti nebo ČR.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>převzato (Eurostat nama_10r_2coe, currency MIO_NAC)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Eurostat, regionální účty (nama_10r_2coe)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>CR, region soudržnosti</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Za kraje Eurostat nepublikuje – uvádí se region soudržnosti (NUTS 2) s označením.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Region zahrnuje více krajů.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EKON_NAHRADY_PODIL</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Podíl náhrad zaměstnancům na HPH (%)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>podil</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Náhrady zaměstnancům / HPH v běžných cenách × 100, týž region a rok.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>100 × EKON_NAHRADY / EKON_HPH (NUTS 2)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (nama_10r_2coe, nama_10r_3gva)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>CR, region soudržnosti</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Jen region soudržnosti a ČR.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Nízký podíl = větší část přidané hodnoty připadá na provozní přebytek a příjmy podnikatelů.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MODEL_HPH</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota oboru v kraji podle velikostní třídy (mil. Kč, modelový odhad)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>odhad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Krajská přidaná hodnota skupiny (Eurostat, regionální účty) přepočtená na úroveň statistiky podniků (MODEL_POMER_SBS) a rozpočítaná mezi třídy podle počtu subjektů (RES, KATPO, podíl se zjištěnou aktivitou podle ČSÚ) × celostátní přidané hodnoty na podnik třídy (Eurostat SBS).</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>HPH_kraj × MODEL_POMER_SBS × n(c)·AV(c)/ENT(c) / Σ n·AV/ENT; pásmo podle zařazení KATPO „Neuvedeno“</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>modelový odhad (RES, ČSÚ RES02QT1, Eurostat nama_10r_3gva, sbs_sc_ovw)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Jen obor = celá sekce, která je samostatnou skupinou A*10; třídy pod prahem 10 subjektů sloučeny.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Modelový odhad, ne statistika. Součet tříd = krajský fakt.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MODEL_HPH_PODIL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Podíl velikostní třídy na přidané hodnotě oboru v kraji (%, modelový odhad)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>odhad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>MODEL_HPH třídy / přidaná hodnota skupiny v kraji × 100.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>100 × MODEL_HPH / EKON_HPH</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Jako MODEL_HPH.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Modelový odhad.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MODEL_OBRAT</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Obrat oboru v kraji (mil. Kč, modelový odhad)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>odhad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MODEL_HPH třídy × celostátní poměr čistého obratu k přidané hodnotě v třídě (SBS).</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Σ MODEL_HPH(c) × NETTUR(c)/AV(c)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Jako MODEL_HPH.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Vychází z přidané hodnoty přepočtené na úroveň SBS; kontrola na ČR viz MODEL_KONTROLA.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MODEL_KONCENTRACE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Podíl subjektů s 10+ a 50+ zaměstnanými osobami na přidané hodnotě a obratu (%, modelový odhad)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>odhad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Součet MODEL_HPH, resp. MODEL_OBRAT tříd nad hranicí / celek × 100.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>100 × Σ_{c ≥ hranice} MODEL_HPH(c) / Σ MODEL_HPH</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>modelový odhad</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>CR, kraj</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Nezveřejní se, pokud by hranice rozdělila sloučenou třídu pod prahem.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Koncentrace podle tříd, ne podle jednotlivých subjektů.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>částečně</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MODEL_KONTROLA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Kontrola konzistence modelu na celé ČR</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>odhad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Model se stejnými vstupy za celou ČR proti hodnotám SBS; odchylka v p. b. (podíly) nebo % (obrat).</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>report.tabulky_model</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>modelový odhad a Eurostat SBS</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Ukazuje přesnost modelu tam, kde fakt známe.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SBS_PODNIKY</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Počet podniků v ČR podle velikostní třídy (Eurostat SBS)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Aktivní podniky v sekci za ČR, třída podle počtu zaměstnaných osob.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>převzato (sbs_sc_ovw, ENT_NR)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Eurostat, sbs_sc_ovw</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Podniky, ne registrované subjekty.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SBS_OSOBY</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Zaměstnané osoby v ČR podle velikostní třídy (Eurostat SBS)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Zaměstnané osoby včetně majitelů a spolupracujících osob.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>převzato (sbs_sc_ovw, EMP_NR)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Eurostat, sbs_sc_ovw</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SBS_OBRAT_PODNIK</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Průměrný obrat podniku v ČR podle velikostní třídy (mil. Kč)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Čistý obrat / počet podniků, převedeno ročním průměrným kurzem CZK/EUR; pásmo min.–max. mezi oddíly sekce.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>NETTUR_MEUR / ENT_NR × kurz</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Eurostat, sbs_sc_ovw, ert_bil_eur_a</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Peněžní údaje jen za třídy 0–9, 10–19, 20–49, 50–249, 250+.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Průměr, ne medián; fakt za ČR.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SBS_MARZE</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Hrubý provozní přebytek / obrat v ČR podle velikostní třídy (%)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Hrubý provozní přebytek / čistý obrat × 100, za ČR.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>100 × GOS_MEUR / NETTUR_MEUR</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Eurostat, sbs_sc_ovw</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Fakt za ČR, ne odhad za kraj; hrubý provozní přebytek zahrnuje i odměnu podnikatelů bez zaměstnanců.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MODEL_POMER_SBS</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Poměr přidané hodnoty SBS a národních účtů za ČR (týž obor a rok)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>odhad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota sekce za ČR ze statistiky podniků (SBS, v Kč) / přidaná hodnota téže sekce za ČR z národních (regionálních) účtů.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AV_MEUR(ČR) × kurz / HPH_CP(ČR)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>odvozeno z Eurostatu (sbs_sc_ovw, ert_bil_eur_a, nama_10r_3gva)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Jen jsou-li publikovány obě hodnoty pro týž rok.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Měřítko přepočtu krajské přidané hodnoty pro model (rozhodnutí 14); předpokládá stejný podíl neregistrované ekonomiky v kraji jako v ČR.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SBS_HPH</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota sekce za ČR podle statistiky podniků (mil. Kč)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>kontext</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Přidaná hodnota v nákladech na výrobní činitele (SBS), mil. EUR převedené ročním průměrným kurzem.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AV_MEUR × kurz</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Eurostat, sbs_sc_ovw, ert_bil_eur_a</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Nižší než přidaná hodnota národních účtů (bez neregistrované ekonomiky, jiné ocenění).</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>naplněno</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Pravidla ochrany malých buněk: buňky pod prahem se v každém členění slučují do „ostatní“; je-li „ostatní“ pod prahem, přidá se další nejmenší buňka; skryté číslo nesmí jít dopočítat ze součtů ani z jiné tabulky (ověřeno kontrolou dopočtu). Podrobnosti: docs/report_metodika.md.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12302,7 +12562,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02T06:43:18+00:00</t>
+          <t>2026-10-02T07:13:38+00:00</t>
         </is>
       </c>
     </row>

--- a/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
+++ b/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
@@ -12562,7 +12562,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02T07:13:38+00:00</t>
+          <t>2026-10-02T07:32:34+00:00</t>
         </is>
       </c>
     </row>

--- a/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
+++ b/reporty/vystupy/F__CZ051__2026-09-15/priloha.xlsx
@@ -1,43 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Přehled" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="T01_zakladni" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="T02_srovnani" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="T03_kraje" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="T04_okresy" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="T05_fo_po" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="T06_pravni_forma" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="T07_velikost_fo" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="T08_velikost_po" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="T09_vekova_struktura" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="T13_bench_fo_po" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="T14_bench_pravni_forma" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="T15_bench_velikost_fo" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="T16_bench_velikost_po" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="T17_bench_vekova_struktura" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="T22_ekonomika" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="T23_nahrady" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="T28_model_prepocet" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="T24_model_velikost" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="T25_model_koncentrace" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="T26_sbs_cr" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="T27_model_kontrola" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="T20_mzdy_obor" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="T21_mzdy_aktualni" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="T10_zaniky_po" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="T18_mira_zaniku_po" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="T11_dynamika_csu" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="T12_demografie_cr" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="T19_zjisteni" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Metodika" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Zdroj a licence" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Přehled" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T01_zakladni" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T02_srovnani" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T03_kraje" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T04_okresy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T05_fo_po" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T06_pravni_forma" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T07_velikost_fo" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T08_velikost_po" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T09_vekova_struktura" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T13_bench_fo_po" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T14_bench_pravni_forma" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T15_bench_velikost_fo" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T16_bench_velikost_po" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T17_bench_vekova_struktura" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T22_ekonomika" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T23_nahrady" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T28_model_prepocet" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T24_model_velikost" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T25_model_koncentrace" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T26_sbs_cr" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T27_model_kontrola" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T20_mzdy_obor" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T21_mzdy_aktualni" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T10_zaniky_po" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T18_mira_zaniku_po" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T11_dynamika_csu" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T12_demografie_cr" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T19_zjisteni" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodika" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zdroj a licence" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -467,468 +467,480 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Obor</t>
+          <t>Archiv</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F Stavebnictví</t>
+          <t>CZ-NACE 2008, nahrazeno: výstup podle CZ-NACE Rev. 2 (rozhodnutí 5) – archiv. Od 19. 10. 2026 report počítá podle CZ-NACE 2025 (rozhodnutí 15); náhrada: reporty/vystupy/F__CZ051__2026-10-15.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Klasifikace</t>
+          <t>Obor</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CZ-NACE Rev. 2 (klasifikace ČSÚ 80004, sloupec NACE)</t>
+          <t>F Stavebnictví</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Území</t>
+          <t>Klasifikace</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Liberecký kraj (CZ051)</t>
+          <t>CZ-NACE Rev. 2 (klasifikace ČSÚ 80004, sloupec NACE)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Datum snímku RES</t>
+          <t>Území</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>Liberecký kraj (CZ051)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Populace</t>
+          <t>Datum snímku RES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>registrované ekonomické subjekty bez data zániku (sídlo v území, převažující činnost v oboru)</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Srovnávací kraje (zadal uživatel)</t>
+          <t>Populace</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CZ052, CZ041</t>
+          <t>registrované ekonomické subjekty bez data zániku (sídlo v území, převažující činnost v oboru)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Práh zveřejnění (subjektů)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>10</v>
+          <t>Srovnávací kraje (zadal uživatel)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CZ052, CZ041</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Minimální rozsah reportu (subjektů)</t>
+          <t>Práh zveřejnění (subjektů)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Práh spolehlivosti zařazení (%)</t>
+          <t>Minimální rozsah reportu (subjektů)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Citace</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
-        </is>
+          <t>Práh spolehlivosti zařazení (%)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Citace</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Zdroj: Český statistický úřad, Registr ekonomických subjektů (RES) – otevřená data, stav k 15. 9. 2026; licence CC BY 4.0 (https://csu.gov.cz/podminky_pro_vyuzivani_a_dalsi_zverejnovani_statistickych_udaju_csu); vlastní výpočet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Označení</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Odvozené údaje, nejde o oficiální statistiku ČSÚ.</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Tabulky</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T01_zakladni</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Základní ukazatele</t>
+          <t>Tabulky</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T02_srovnani</t>
+          <t>T01_zakladni</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Srovnání s ČR a se zadanými kraji</t>
+          <t>Základní ukazatele</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T03_kraje</t>
+          <t>T02_srovnani</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pořadí krajů (všech 14)</t>
+          <t>Srovnání s ČR a se zadanými kraji</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T04_okresy</t>
+          <t>T03_kraje</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Okresy kraje Liberecký kraj</t>
+          <t>Pořadí krajů (všech 14)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T05_fo_po</t>
+          <t>T04_okresy</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Registrované subjekty podle typu osoby</t>
+          <t>Okresy kraje Liberecký kraj</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T06_pravni_forma</t>
+          <t>T05_fo_po</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Registrované subjekty podle právní formy (číselník ČSÚ 56)</t>
+          <t>Registrované subjekty podle typu osoby</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T07_velikost_fo</t>
+          <t>T06_pravni_forma</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Velikostní profil FO podle počtu zaměstnanců (KATPO)</t>
+          <t>Registrované subjekty podle právní formy (číselník ČSÚ 56)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T08_velikost_po</t>
+          <t>T07_velikost_fo</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Velikostní profil PO podle počtu zaměstnanců (KATPO)</t>
+          <t>Velikostní profil FO podle počtu zaměstnanců (KATPO)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T09_vekova_struktura</t>
+          <t>T08_velikost_po</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Věková struktura existujících subjektů</t>
+          <t>Velikostní profil PO podle počtu zaměstnanců (KATPO)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T13_bench_fo_po</t>
+          <t>T09_vekova_struktura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Typ osoby – srovnání s ČR a se srovnávacími kraji (podíl, %)</t>
+          <t>Věková struktura existujících subjektů</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T14_bench_pravni_forma</t>
+          <t>T13_bench_fo_po</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Právní forma – srovnání s ČR a se srovnávacími kraji (podíl z celku, %)</t>
+          <t>Typ osoby – srovnání s ČR a se srovnávacími kraji (podíl, %)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>T15_bench_velikost_fo</t>
+          <t>T14_bench_pravni_forma</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Velikostní profil FO – srovnání s ČR a se srovnávacími kraji (podíl z FO, %)</t>
+          <t>Právní forma – srovnání s ČR a se srovnávacími kraji (podíl z celku, %)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>T16_bench_velikost_po</t>
+          <t>T15_bench_velikost_fo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Velikostní profil PO – srovnání s ČR a se srovnávacími kraji (podíl z PO, %)</t>
+          <t>Velikostní profil FO – srovnání s ČR a se srovnávacími kraji (podíl z FO, %)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>T17_bench_vekova_struktura</t>
+          <t>T16_bench_velikost_po</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Věková struktura existujících subjektů – srovnání s ČR a se srovnávacími kraji (podíl, %)</t>
+          <t>Velikostní profil PO – srovnání s ČR a se srovnávacími kraji (podíl z PO, %)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>T22_ekonomika</t>
+          <t>T17_bench_vekova_struktura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hrubá přidaná hodnota, zaměstnanost a produktivita – kraje a ČR (Eurostat, regionální účty) – Stavebnictví (F)</t>
+          <t>Věková struktura existujících subjektů – srovnání s ČR a se srovnávacími kraji (podíl, %)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>T23_nahrady</t>
+          <t>T22_ekonomika</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Náhrady zaměstnancům a hrubá přidaná hodnota – regiony soudržnosti (Eurostat) – Stavebnictví (F)</t>
+          <t>Hrubá přidaná hodnota, zaměstnanost a produktivita – kraje a ČR (Eurostat, regionální účty) – Stavebnictví (F)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T28_model_prepocet</t>
+          <t>T23_nahrady</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Přepočet přidané hodnoty na úroveň statistiky podniků (vstup modelu) – Liberecký kraj, 2024</t>
+          <t>Náhrady zaměstnancům a hrubá přidaná hodnota – regiony soudržnosti (Eurostat) – Stavebnictví (F)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>T24_model_velikost</t>
+          <t>T28_model_prepocet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Modelový odhad: přidaná hodnota a obrat oboru podle velikosti subjektů – Liberecký kraj, 2024</t>
+          <t>Přepočet přidané hodnoty na úroveň statistiky podniků (vstup modelu) – Liberecký kraj, 2024</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>T25_model_koncentrace</t>
+          <t>T24_model_velikost</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Modelový odhad: koncentrace – podíl subjektů s 10+ a 50+ zaměstnanými osobami – Liberecký kraj, 2024</t>
+          <t>Modelový odhad: přidaná hodnota a obrat oboru podle velikosti subjektů – Liberecký kraj, 2024</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>T26_sbs_cr</t>
+          <t>T25_model_koncentrace</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Statistika podniků za ČR podle velikosti: typický obrat a marže (fakt za ČR, Eurostat SBS) – sekce F, 2024</t>
+          <t>Modelový odhad: koncentrace – podíl subjektů s 10+ a 50+ zaměstnanými osobami – Liberecký kraj, 2024</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>T27_model_kontrola</t>
+          <t>T26_sbs_cr</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kontrola konzistence: model použitý na celou ČR proti statistice podniků (SBS) – sekce F, 2024</t>
+          <t>Statistika podniků za ČR podle velikosti: typický obrat a marže (fakt za ČR, Eurostat SBS) – sekce F, 2024</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>T20_mzdy_obor</t>
+          <t>T27_model_kontrola</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zaměstnanci a průměrné mzdy v oboru – kraje a ČR (ČSÚ, roční zjišťování)</t>
+          <t>Kontrola konzistence: model použitý na celou ČR proti statistice podniků (SBS) – sekce F, 2024</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>T21_mzdy_aktualni</t>
+          <t>T20_mzdy_obor</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zaměstnanci a průměrné mzdy – novější roky v nejbližších publikovaných úrovních (ČSÚ, čtvrtletní zjišťování)</t>
+          <t>Zaměstnanci a průměrné mzdy v oboru – kraje a ČR (ČSÚ, roční zjišťování)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>T10_zaniky_po</t>
+          <t>T21_mzdy_aktualni</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES, od 2023)</t>
+          <t>Zaměstnanci a průměrné mzdy – novější roky v nejbližších publikovaných úrovních (ČSÚ, čtvrtletní zjišťování)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>T18_mira_zaniku_po</t>
+          <t>T10_zaniky_po</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Míra zániku právnických osob v oboru (RES, 2023–2026)</t>
+          <t>Zaniklé právnické osoby v oboru a území podle roku zániku (RES, od 2023)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>T11_dynamika_csu</t>
+          <t>T18_mira_zaniku_po</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
+          <t>Míra zániku právnických osob v oboru (RES, 2023–2026)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>T12_demografie_cr</t>
+          <t>T11_dynamika_csu</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+          <t>Vznik a zánik ekonomických subjektů v území – všechny obory (ČSÚ, RES05)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>T12_demografie_cr</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Demografie podniků v ČR – kontext (ČSÚ, RESDP00; jednotka podnik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>T19_zjisteni</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Zjištění detektoru (seřazeno podle síly)</t>
         </is>
@@ -9786,7 +9798,6 @@
           <t>ČSÚ DataStat – tabulka v tomto členění neexistuje (RES05 jen území × FO/PO; RES06 registrace a RESDP00 demografie podniků jen za ČR podle odvětví)</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Nelze naplnit.</t>
